--- a/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
+++ b/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\2_responsibilities\nvi_etl\nvi_etl\survey\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E8025B-5365-4FC6-B6D5-CF2E8400D767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9010E939-80D2-41E7-B9BD-3279ACA84ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="2880" windowWidth="19200" windowHeight="11710" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="3220" yWindow="3220" windowWidth="19200" windowHeight="11710" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_main!$A$1:$T$730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_main!$A$1:$T$721</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6221" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6149" uniqueCount="742">
   <si>
     <t>indicator_include</t>
   </si>
@@ -2266,9 +2266,6 @@
   </si>
   <si>
     <t>Have you wanted to move somewhere else in the city but not been able to find housing that you could afford?</t>
-  </si>
-  <si>
-    <t>Have financial concerns prevented you or someone in your family from getting the level of healthcare or medicine that you need?</t>
   </si>
   <si>
     <t>survey_question_type</t>
@@ -2872,15 +2869,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3324,7 +3313,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
   <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:U730"/>
+  <dimension ref="A1:U721"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="25.453125" style="3" customWidth="1"/>
@@ -3409,7 +3398,7 @@
         <v>11</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
@@ -6412,7 +6401,7 @@
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>508</v>
@@ -22118,7 +22107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>62</v>
       </c>
@@ -22177,7 +22166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>62</v>
       </c>
@@ -23220,7 +23209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>62</v>
       </c>
@@ -23283,7 +23272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>62</v>
       </c>
@@ -37472,7 +37461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:21" ht="18" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
         <v>83</v>
       </c>
@@ -37535,7 +37524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:21" ht="18" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
         <v>83</v>
       </c>
@@ -37598,7 +37587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:21" ht="18" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
         <v>83</v>
       </c>
@@ -44806,35 +44795,35 @@
         <v>1</v>
       </c>
       <c r="D685" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E685" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F685" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G685" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="H685" s="7" t="s">
-        <v>124</v>
+        <v>701</v>
+      </c>
+      <c r="H685" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="I685" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J685" s="2">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="K685" s="7">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="L685" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M685" s="2"/>
       <c r="N685" s="2" t="s">
-        <v>348</v>
+        <v>553</v>
       </c>
       <c r="O685" s="2" t="s">
         <v>15</v>
@@ -44865,35 +44854,35 @@
         <v>1</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E686" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F686" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G686" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="H686" s="7" t="s">
-        <v>122</v>
+        <v>701</v>
+      </c>
+      <c r="H686" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="I686" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J686" s="2">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="K686" s="7">
-        <v>37</v>
+        <v>135</v>
       </c>
       <c r="L686" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M686" s="2"/>
       <c r="N686" s="2" t="s">
-        <v>348</v>
+        <v>553</v>
       </c>
       <c r="O686" s="2" t="s">
         <v>15</v>
@@ -44924,35 +44913,35 @@
         <v>1</v>
       </c>
       <c r="D687" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E687" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F687" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G687" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="H687" s="7" t="s">
-        <v>125</v>
+        <v>701</v>
+      </c>
+      <c r="H687" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="I687" s="2">
         <v>3</v>
       </c>
       <c r="J687" s="2">
-        <v>16</v>
+        <v>177</v>
       </c>
       <c r="K687" s="7">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="L687" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M687" s="2"/>
       <c r="N687" s="2" t="s">
-        <v>348</v>
+        <v>553</v>
       </c>
       <c r="O687" s="2" t="s">
         <v>15</v>
@@ -44983,35 +44972,35 @@
         <v>1</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E688" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F688" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G688" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="H688" s="7" t="s">
-        <v>124</v>
+        <v>701</v>
+      </c>
+      <c r="H688" s="2" t="s">
+        <v>550</v>
       </c>
       <c r="I688" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J688" s="2">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="K688" s="7">
-        <v>36</v>
+        <v>180</v>
       </c>
       <c r="L688" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M688" s="2"/>
       <c r="N688" s="2" t="s">
-        <v>349</v>
+        <v>553</v>
       </c>
       <c r="O688" s="2" t="s">
         <v>15</v>
@@ -45042,35 +45031,35 @@
         <v>1</v>
       </c>
       <c r="D689" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E689" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F689" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G689" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="H689" s="7" t="s">
-        <v>122</v>
+        <v>701</v>
+      </c>
+      <c r="H689" s="2" t="s">
+        <v>551</v>
       </c>
       <c r="I689" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J689" s="2">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="K689" s="7">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="L689" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M689" s="2"/>
       <c r="N689" s="2" t="s">
-        <v>349</v>
+        <v>553</v>
       </c>
       <c r="O689" s="2" t="s">
         <v>15</v>
@@ -45101,35 +45090,35 @@
         <v>1</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E690" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F690" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G690" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="H690" s="7" t="s">
-        <v>125</v>
+        <v>702</v>
+      </c>
+      <c r="H690" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="I690" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J690" s="2">
-        <v>17</v>
+        <v>178</v>
       </c>
       <c r="K690" s="7">
-        <v>39</v>
+        <v>179</v>
       </c>
       <c r="L690" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M690" s="2"/>
       <c r="N690" s="2" t="s">
-        <v>349</v>
+        <v>554</v>
       </c>
       <c r="O690" s="2" t="s">
         <v>15</v>
@@ -45160,35 +45149,35 @@
         <v>1</v>
       </c>
       <c r="D691" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E691" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F691" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G691" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="H691" s="7" t="s">
-        <v>124</v>
+        <v>702</v>
+      </c>
+      <c r="H691" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="I691" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J691" s="2">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="K691" s="7">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="L691" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M691" s="2"/>
       <c r="N691" s="2" t="s">
-        <v>347</v>
+        <v>554</v>
       </c>
       <c r="O691" s="2" t="s">
         <v>15</v>
@@ -45219,35 +45208,35 @@
         <v>1</v>
       </c>
       <c r="D692" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E692" s="2">
+        <v>29</v>
+      </c>
+      <c r="F692" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G692" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="H692" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I692" s="2">
         <v>3</v>
       </c>
-      <c r="F692" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="G692" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="H692" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I692" s="2">
-        <v>2</v>
-      </c>
       <c r="J692" s="2">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="K692" s="7">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="L692" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M692" s="2"/>
       <c r="N692" s="2" t="s">
-        <v>347</v>
+        <v>554</v>
       </c>
       <c r="O692" s="2" t="s">
         <v>15</v>
@@ -45278,35 +45267,35 @@
         <v>1</v>
       </c>
       <c r="D693" s="2" t="s">
-        <v>346</v>
+        <v>548</v>
       </c>
       <c r="E693" s="2">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="F693" s="2" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="G693" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="H693" s="7" t="s">
-        <v>125</v>
+        <v>702</v>
+      </c>
+      <c r="H693" s="2" t="s">
+        <v>550</v>
       </c>
       <c r="I693" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J693" s="2">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="K693" s="7">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="L693" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M693" s="2"/>
       <c r="N693" s="2" t="s">
-        <v>347</v>
+        <v>554</v>
       </c>
       <c r="O693" s="2" t="s">
         <v>15</v>
@@ -45346,26 +45335,26 @@
         <v>621</v>
       </c>
       <c r="G694" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H694" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I694" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J694" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K694" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L694" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M694" s="2"/>
       <c r="N694" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O694" s="2" t="s">
         <v>15</v>
@@ -45405,26 +45394,26 @@
         <v>621</v>
       </c>
       <c r="G695" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H695" s="2" t="s">
-        <v>287</v>
+        <v>549</v>
       </c>
       <c r="I695" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J695" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K695" s="7">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="L695" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M695" s="2"/>
       <c r="N695" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O695" s="2" t="s">
         <v>15</v>
@@ -45464,26 +45453,26 @@
         <v>621</v>
       </c>
       <c r="G696" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H696" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I696" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J696" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K696" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L696" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M696" s="2"/>
       <c r="N696" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O696" s="2" t="s">
         <v>15</v>
@@ -45523,26 +45512,26 @@
         <v>621</v>
       </c>
       <c r="G697" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H697" s="2" t="s">
-        <v>550</v>
+        <v>289</v>
       </c>
       <c r="I697" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J697" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K697" s="7">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L697" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M697" s="2"/>
       <c r="N697" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O697" s="2" t="s">
         <v>15</v>
@@ -45582,26 +45571,26 @@
         <v>621</v>
       </c>
       <c r="G698" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H698" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I698" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J698" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K698" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L698" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M698" s="2"/>
       <c r="N698" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O698" s="2" t="s">
         <v>15</v>
@@ -45641,26 +45630,26 @@
         <v>621</v>
       </c>
       <c r="G699" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I699" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J699" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K699" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L699" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M699" s="2"/>
       <c r="N699" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O699" s="2" t="s">
         <v>15</v>
@@ -45700,26 +45689,26 @@
         <v>621</v>
       </c>
       <c r="G700" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H700" s="2" t="s">
-        <v>287</v>
+        <v>549</v>
       </c>
       <c r="I700" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J700" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K700" s="7">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="L700" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M700" s="2"/>
       <c r="N700" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O700" s="2" t="s">
         <v>15</v>
@@ -45759,26 +45748,26 @@
         <v>621</v>
       </c>
       <c r="G701" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H701" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I701" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J701" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K701" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L701" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M701" s="2"/>
       <c r="N701" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O701" s="2" t="s">
         <v>15</v>
@@ -45818,26 +45807,26 @@
         <v>621</v>
       </c>
       <c r="G702" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H702" s="2" t="s">
-        <v>550</v>
+        <v>289</v>
       </c>
       <c r="I702" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J702" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K702" s="7">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L702" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M702" s="2"/>
       <c r="N702" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O702" s="2" t="s">
         <v>15</v>
@@ -45877,26 +45866,26 @@
         <v>621</v>
       </c>
       <c r="G703" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H703" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I703" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J703" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K703" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L703" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M703" s="2"/>
       <c r="N703" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O703" s="2" t="s">
         <v>15</v>
@@ -45936,26 +45925,26 @@
         <v>621</v>
       </c>
       <c r="G704" s="2" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I704" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J704" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K704" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L704" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M704" s="2"/>
       <c r="N704" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O704" s="2" t="s">
         <v>15</v>
@@ -45995,26 +45984,26 @@
         <v>621</v>
       </c>
       <c r="G705" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>287</v>
+        <v>549</v>
       </c>
       <c r="I705" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J705" s="2">
+        <v>181</v>
+      </c>
+      <c r="K705" s="7">
         <v>179</v>
-      </c>
-      <c r="K705" s="7">
-        <v>135</v>
       </c>
       <c r="L705" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M705" s="2"/>
       <c r="N705" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O705" s="2" t="s">
         <v>15</v>
@@ -46054,26 +46043,26 @@
         <v>621</v>
       </c>
       <c r="G706" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H706" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I706" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J706" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K706" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L706" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M706" s="2"/>
       <c r="N706" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O706" s="2" t="s">
         <v>15</v>
@@ -46113,26 +46102,26 @@
         <v>621</v>
       </c>
       <c r="G707" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>550</v>
+        <v>289</v>
       </c>
       <c r="I707" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J707" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K707" s="7">
-        <v>180</v>
+        <v>134</v>
       </c>
       <c r="L707" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M707" s="2"/>
       <c r="N707" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O707" s="2" t="s">
         <v>15</v>
@@ -46172,26 +46161,26 @@
         <v>621</v>
       </c>
       <c r="G708" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H708" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I708" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J708" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K708" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L708" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M708" s="2"/>
       <c r="N708" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="O708" s="2" t="s">
         <v>15</v>
@@ -46231,26 +46220,26 @@
         <v>621</v>
       </c>
       <c r="G709" s="2" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H709" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I709" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J709" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K709" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L709" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M709" s="2"/>
       <c r="N709" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O709" s="2" t="s">
         <v>15</v>
@@ -46278,38 +46267,38 @@
         <v>0</v>
       </c>
       <c r="C710" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D710" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E710" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F710" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G710" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H710" s="2" t="s">
-        <v>287</v>
+        <v>528</v>
       </c>
       <c r="I710" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J710" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K710" s="7">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="L710" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M710" s="2"/>
       <c r="N710" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O710" s="2" t="s">
         <v>15</v>
@@ -46340,35 +46329,35 @@
         <v>1</v>
       </c>
       <c r="D711" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E711" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F711" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G711" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H711" s="2" t="s">
-        <v>289</v>
+        <v>25</v>
       </c>
       <c r="I711" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J711" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K711" s="7">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="L711" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M711" s="2"/>
       <c r="N711" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O711" s="2" t="s">
         <v>15</v>
@@ -46399,35 +46388,35 @@
         <v>1</v>
       </c>
       <c r="D712" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E712" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F712" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G712" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H712" s="2" t="s">
-        <v>550</v>
+        <v>24</v>
       </c>
       <c r="I712" s="2">
         <v>2</v>
       </c>
       <c r="J712" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K712" s="7">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="L712" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M712" s="2"/>
       <c r="N712" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O712" s="2" t="s">
         <v>15</v>
@@ -46458,35 +46447,35 @@
         <v>1</v>
       </c>
       <c r="D713" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E713" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F713" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G713" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H713" s="2" t="s">
-        <v>551</v>
+        <v>23</v>
       </c>
       <c r="I713" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J713" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="K713" s="7">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="L713" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M713" s="2"/>
       <c r="N713" s="2" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O713" s="2" t="s">
         <v>15</v>
@@ -46517,35 +46506,35 @@
         <v>1</v>
       </c>
       <c r="D714" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E714" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F714" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G714" s="2" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H714" s="2" t="s">
-        <v>549</v>
+        <v>21</v>
       </c>
       <c r="I714" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J714" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K714" s="7">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="L714" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M714" s="2"/>
       <c r="N714" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O714" s="2" t="s">
         <v>15</v>
@@ -46573,38 +46562,38 @@
         <v>0</v>
       </c>
       <c r="C715" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D715" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E715" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F715" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G715" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H715" s="2" t="s">
-        <v>287</v>
+        <v>561</v>
       </c>
       <c r="I715" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J715" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K715" s="7">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="L715" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M715" s="2"/>
       <c r="N715" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="O715" s="2" t="s">
         <v>15</v>
@@ -46635,35 +46624,35 @@
         <v>1</v>
       </c>
       <c r="D716" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E716" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F716" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G716" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H716" s="2" t="s">
-        <v>289</v>
+        <v>25</v>
       </c>
       <c r="I716" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J716" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K716" s="7">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="L716" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M716" s="2"/>
       <c r="N716" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="O716" s="2" t="s">
         <v>15</v>
@@ -46694,35 +46683,35 @@
         <v>1</v>
       </c>
       <c r="D717" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E717" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F717" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G717" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H717" s="2" t="s">
-        <v>550</v>
+        <v>24</v>
       </c>
       <c r="I717" s="2">
         <v>2</v>
       </c>
       <c r="J717" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K717" s="7">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="L717" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M717" s="2"/>
       <c r="N717" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="O717" s="2" t="s">
         <v>15</v>
@@ -46753,35 +46742,35 @@
         <v>1</v>
       </c>
       <c r="D718" s="2" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="E718" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F718" s="2" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G718" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>551</v>
+        <v>23</v>
       </c>
       <c r="I718" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J718" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K718" s="7">
-        <v>181</v>
+        <v>3</v>
       </c>
       <c r="L718" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M718" s="2"/>
       <c r="N718" s="2" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="O718" s="2" t="s">
         <v>15</v>
@@ -46809,7 +46798,7 @@
         <v>0</v>
       </c>
       <c r="C719" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D719" s="2" t="s">
         <v>558</v>
@@ -46821,26 +46810,26 @@
         <v>622</v>
       </c>
       <c r="G719" s="2" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H719" s="2" t="s">
-        <v>528</v>
+        <v>21</v>
       </c>
       <c r="I719" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J719" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K719" s="7">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L719" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M719" s="2"/>
       <c r="N719" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O719" s="2" t="s">
         <v>15</v>
@@ -46871,38 +46860,34 @@
         <v>1</v>
       </c>
       <c r="D720" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E720" s="2">
-        <v>30</v>
-      </c>
-      <c r="F720" s="2" t="s">
-        <v>622</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="E720" s="2"/>
+      <c r="F720" s="2"/>
       <c r="G720" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H720" s="2" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="I720" s="2">
         <v>1</v>
       </c>
       <c r="J720" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K720" s="7">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="L720" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M720" s="2"/>
       <c r="N720" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="O720" s="2" t="s">
-        <v>15</v>
+        <v>509</v>
       </c>
       <c r="P720" s="6" t="s">
         <v>521</v>
@@ -46930,38 +46915,34 @@
         <v>1</v>
       </c>
       <c r="D721" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E721" s="2">
-        <v>30</v>
-      </c>
-      <c r="F721" s="2" t="s">
-        <v>622</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="E721" s="2"/>
+      <c r="F721" s="2"/>
       <c r="G721" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H721" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="I721" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J721" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K721" s="7">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="L721" s="2" t="b">
         <v>1</v>
       </c>
       <c r="M721" s="2"/>
       <c r="N721" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="O721" s="2" t="s">
-        <v>15</v>
+        <v>509</v>
       </c>
       <c r="P721" s="6" t="s">
         <v>521</v>
@@ -46980,611 +46961,83 @@
         <v>4</v>
       </c>
     </row>
-    <row r="722" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A722" s="2"/>
-      <c r="B722" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C722" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D722" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E722" s="2">
-        <v>30</v>
-      </c>
-      <c r="F722" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G722" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="H722" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I722" s="2">
-        <v>3</v>
-      </c>
-      <c r="J722" s="2">
-        <v>182</v>
-      </c>
-      <c r="K722" s="7">
-        <v>3</v>
-      </c>
-      <c r="L722" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M722" s="2"/>
-      <c r="N722" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="O722" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P722" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q722" s="2"/>
-      <c r="R722" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S722" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T722" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U722" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="723" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A723" s="2"/>
-      <c r="B723" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C723" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D723" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E723" s="2">
-        <v>30</v>
-      </c>
-      <c r="F723" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G723" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="H723" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I723" s="2">
-        <v>4</v>
-      </c>
-      <c r="J723" s="2">
-        <v>182</v>
-      </c>
-      <c r="K723" s="7">
-        <v>4</v>
-      </c>
-      <c r="L723" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M723" s="2"/>
-      <c r="N723" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="O723" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P723" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q723" s="2"/>
-      <c r="R723" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S723" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T723" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U723" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="724" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A724" s="2"/>
-      <c r="B724" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C724" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="D724" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E724" s="2">
-        <v>30</v>
-      </c>
-      <c r="F724" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G724" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H724" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="I724" s="2">
-        <v>0</v>
-      </c>
-      <c r="J724" s="2">
-        <v>183</v>
-      </c>
-      <c r="K724" s="7">
-        <v>16</v>
-      </c>
-      <c r="L724" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M724" s="2"/>
-      <c r="N724" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O724" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P724" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q724" s="2"/>
-      <c r="R724" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S724" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T724" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U724" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="725" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A725" s="2"/>
-      <c r="B725" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C725" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D725" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E725" s="2">
-        <v>30</v>
-      </c>
-      <c r="F725" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G725" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H725" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I725" s="2">
-        <v>1</v>
-      </c>
-      <c r="J725" s="2">
-        <v>183</v>
-      </c>
-      <c r="K725" s="7">
-        <v>1</v>
-      </c>
-      <c r="L725" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M725" s="2"/>
-      <c r="N725" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O725" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P725" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q725" s="2"/>
-      <c r="R725" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S725" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T725" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U725" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="726" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A726" s="2"/>
-      <c r="B726" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C726" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D726" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E726" s="2">
-        <v>30</v>
-      </c>
-      <c r="F726" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G726" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H726" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I726" s="2">
-        <v>2</v>
-      </c>
-      <c r="J726" s="2">
-        <v>183</v>
-      </c>
-      <c r="K726" s="7">
-        <v>2</v>
-      </c>
-      <c r="L726" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M726" s="2"/>
-      <c r="N726" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O726" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P726" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q726" s="2"/>
-      <c r="R726" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S726" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T726" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U726" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="727" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A727" s="2"/>
-      <c r="B727" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C727" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D727" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E727" s="2">
-        <v>30</v>
-      </c>
-      <c r="F727" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G727" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H727" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I727" s="2">
-        <v>3</v>
-      </c>
-      <c r="J727" s="2">
-        <v>183</v>
-      </c>
-      <c r="K727" s="7">
-        <v>3</v>
-      </c>
-      <c r="L727" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M727" s="2"/>
-      <c r="N727" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O727" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P727" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q727" s="2"/>
-      <c r="R727" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S727" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T727" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U727" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="728" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A728" s="2"/>
-      <c r="B728" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C728" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D728" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E728" s="2">
-        <v>30</v>
-      </c>
-      <c r="F728" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="G728" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="H728" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I728" s="2">
-        <v>4</v>
-      </c>
-      <c r="J728" s="2">
-        <v>183</v>
-      </c>
-      <c r="K728" s="7">
-        <v>4</v>
-      </c>
-      <c r="L728" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M728" s="2"/>
-      <c r="N728" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="O728" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P728" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q728" s="2"/>
-      <c r="R728" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S728" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T728" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U728" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="729" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A729" s="2"/>
-      <c r="B729" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C729" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D729" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E729" s="2"/>
-      <c r="F729" s="2"/>
-      <c r="G729" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="H729" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I729" s="2">
-        <v>1</v>
-      </c>
-      <c r="J729" s="2">
-        <v>184</v>
-      </c>
-      <c r="K729" s="7">
-        <v>36</v>
-      </c>
-      <c r="L729" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M729" s="2"/>
-      <c r="N729" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="O729" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="P729" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q729" s="2"/>
-      <c r="R729" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S729" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T729" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U729" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="730" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A730" s="2"/>
-      <c r="B730" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C730" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D730" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="E730" s="2"/>
-      <c r="F730" s="2"/>
-      <c r="G730" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="H730" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I730" s="2">
-        <v>0</v>
-      </c>
-      <c r="J730" s="2">
-        <v>184</v>
-      </c>
-      <c r="K730" s="7">
-        <v>37</v>
-      </c>
-      <c r="L730" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M730" s="2"/>
-      <c r="N730" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="O730" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="P730" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="Q730" s="2"/>
-      <c r="R730" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="S730" s="9">
-        <v>45658</v>
-      </c>
-      <c r="T730" s="14">
-        <v>72686</v>
-      </c>
-      <c r="U730" s="16">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T730" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:T721" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
+    <filterColumn colId="13">
       <filters>
-        <filter val="62"/>
+        <filter val="At_Risk_Losing_Home:Needs_In_Past_12_Months"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T642">
     <sortCondition ref="A2:A642"/>
   </sortState>
-  <conditionalFormatting sqref="A1:T1 T1:U730 A2:F305 I653:J653 G660:J730">
-    <cfRule type="expression" dxfId="14" priority="4">
+  <conditionalFormatting sqref="A1:T1 A2:F305 I653:J653 R653:T684 O653:O684 L651:L684 M654:N684 T1:U721 G660:J721 K2:K721 C306:C721 A493:B721 D661:F721 O685:P721">
+    <cfRule type="expression" dxfId="13" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D665:E684">
-    <cfRule type="expression" dxfId="13" priority="42">
+    <cfRule type="expression" dxfId="12" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D306:F652">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G671:G674">
-    <cfRule type="expression" dxfId="11" priority="41">
+    <cfRule type="expression" dxfId="10" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:J652">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H675">
-    <cfRule type="expression" dxfId="9" priority="39">
+    <cfRule type="expression" dxfId="8" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H680">
-    <cfRule type="expression" dxfId="8" priority="36">
+    <cfRule type="expression" dxfId="7" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670:I673">
-    <cfRule type="expression" dxfId="7" priority="35">
+    <cfRule type="expression" dxfId="6" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I675:I678">
-    <cfRule type="expression" dxfId="6" priority="34">
+    <cfRule type="expression" dxfId="5" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I680:I683">
-    <cfRule type="expression" dxfId="5" priority="33">
+    <cfRule type="expression" dxfId="4" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K730">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 C306:C730 A493:B730 D653:H660 G659:I659 D661:F730">
+  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 D653:H660 G659:I659">
     <cfRule type="expression" dxfId="3" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 R653:T693 L694:N730 Q694:T730">
+  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 L685:N721 Q685:T721">
     <cfRule type="expression" dxfId="2" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P653:Q685">
+  <conditionalFormatting sqref="P653:Q684">
     <cfRule type="expression" dxfId="1" priority="20">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q288:Q291 R288:R293 Q293 B490:B491 A490:A492 M627:P628 L627:L630 L651:L693 M653:O653 O653:O730 I654:I658 J654:J659 M654:N693 Q686:Q693 P686:P730">
+  <conditionalFormatting sqref="Q288:Q291 R288:R293 Q293 B490:B491 A490:A492 M627:P628 L627:L630 M653:O653 I654:I658 J654:J659">
     <cfRule type="expression" dxfId="0" priority="46">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
+++ b/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\2_responsibilities\nvi_etl\nvi_etl\survey\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9010E939-80D2-41E7-B9BD-3279ACA84ACB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5B19DE-4816-4DEF-9047-43101A987B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3220" yWindow="3220" windowWidth="19200" windowHeight="11710" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
@@ -2417,23 +2417,27 @@
       <sz val="13"/>
       <color theme="1"/>
       <name val="IBM Plex Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="1"/>
       <name val="IBM Plex Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="IBM Plex Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="IBM Plex Sans"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2869,15 +2873,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF3F3F3"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3312,9 +3308,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
-  <sheetPr codeName="Sheet1" filterMode="1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U721"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17.5" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="2" width="25.453125" style="3" customWidth="1"/>
     <col min="3" max="3" width="29" style="3" customWidth="1"/>
@@ -3336,7 +3332,7 @@
     <col min="22" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
         <v>511</v>
       </c>
@@ -3401,7 +3397,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3464,7 +3460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3527,7 +3523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3590,7 +3586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -3653,7 +3649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -3716,7 +3712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -3779,7 +3775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -3842,7 +3838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -3905,7 +3901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>2</v>
       </c>
@@ -3968,7 +3964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -4031,7 +4027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -4094,7 +4090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2">
         <v>2</v>
       </c>
@@ -4157,7 +4153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -4220,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -4283,7 +4279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -4346,7 +4342,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
         <v>3</v>
       </c>
@@ -4409,7 +4405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -4472,7 +4468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
         <v>3</v>
       </c>
@@ -4535,7 +4531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -4598,7 +4594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2">
         <v>3</v>
       </c>
@@ -4661,7 +4657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -4724,7 +4720,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2">
         <v>3</v>
       </c>
@@ -4787,7 +4783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2">
         <v>3</v>
       </c>
@@ -4850,7 +4846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2">
         <v>3</v>
       </c>
@@ -4913,7 +4909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2">
         <v>3</v>
       </c>
@@ -4976,7 +4972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2">
         <v>3</v>
       </c>
@@ -5039,7 +5035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2">
         <v>3</v>
       </c>
@@ -5102,7 +5098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2">
         <v>3</v>
       </c>
@@ -5165,7 +5161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2">
         <v>3</v>
       </c>
@@ -5228,7 +5224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2">
         <v>3</v>
       </c>
@@ -5291,7 +5287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2">
         <v>3</v>
       </c>
@@ -5354,7 +5350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="2">
         <v>3</v>
       </c>
@@ -5417,7 +5413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="2">
         <v>3</v>
       </c>
@@ -5480,7 +5476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -5543,7 +5539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="2">
         <v>3</v>
       </c>
@@ -5606,7 +5602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="2">
         <v>3</v>
       </c>
@@ -5669,7 +5665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="2">
         <v>3</v>
       </c>
@@ -5732,7 +5728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="2">
         <v>3</v>
       </c>
@@ -5795,7 +5791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="2">
         <v>3</v>
       </c>
@@ -5858,7 +5854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="2">
         <v>3</v>
       </c>
@@ -5921,7 +5917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -5984,7 +5980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="2">
         <v>3</v>
       </c>
@@ -6047,7 +6043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="2">
         <v>3</v>
       </c>
@@ -6110,7 +6106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="2">
         <v>3</v>
       </c>
@@ -6173,7 +6169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="2">
         <v>5</v>
       </c>
@@ -6236,7 +6232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="2">
         <v>5</v>
       </c>
@@ -6299,7 +6295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="2">
         <v>5</v>
       </c>
@@ -6362,14 +6358,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="2">
         <v>5</v>
       </c>
       <c r="B49" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C49" s="2" t="b">
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -6397,7 +6393,7 @@
         <v>8</v>
       </c>
       <c r="L49" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2" t="s">
@@ -6425,7 +6421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="2">
         <v>6</v>
       </c>
@@ -6484,7 +6480,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="2">
         <v>6</v>
       </c>
@@ -6543,7 +6539,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="2">
         <v>6</v>
       </c>
@@ -6602,7 +6598,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="2">
         <v>6</v>
       </c>
@@ -6661,7 +6657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="2">
         <v>6</v>
       </c>
@@ -6720,7 +6716,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="2">
         <v>6</v>
       </c>
@@ -6779,7 +6775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="2">
         <v>6</v>
       </c>
@@ -6838,7 +6834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="2">
         <v>9</v>
       </c>
@@ -6897,7 +6893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="2">
         <v>9</v>
       </c>
@@ -6956,7 +6952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="2">
         <v>9</v>
       </c>
@@ -7015,7 +7011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="2">
         <v>9</v>
       </c>
@@ -7074,7 +7070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="2">
         <v>9</v>
       </c>
@@ -7133,7 +7129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="2">
         <v>16</v>
       </c>
@@ -7192,7 +7188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="2">
         <v>16</v>
       </c>
@@ -7251,7 +7247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="2">
         <v>18</v>
       </c>
@@ -7314,7 +7310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="2">
         <v>18</v>
       </c>
@@ -7377,7 +7373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="2">
         <v>18</v>
       </c>
@@ -7440,7 +7436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="2">
         <v>18</v>
       </c>
@@ -7503,7 +7499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="2">
         <v>19</v>
       </c>
@@ -7566,7 +7562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="2">
         <v>19</v>
       </c>
@@ -7629,7 +7625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="2">
         <v>19</v>
       </c>
@@ -7692,7 +7688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="2">
         <v>20</v>
       </c>
@@ -7751,7 +7747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="2">
         <v>20</v>
       </c>
@@ -7810,7 +7806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="2">
         <v>20</v>
       </c>
@@ -7869,7 +7865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="2">
         <v>20</v>
       </c>
@@ -7928,7 +7924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="2">
         <v>20</v>
       </c>
@@ -7987,7 +7983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="2">
         <v>22</v>
       </c>
@@ -8050,7 +8046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="2">
         <v>22</v>
       </c>
@@ -8113,7 +8109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="2">
         <v>22</v>
       </c>
@@ -8176,7 +8172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="2">
         <v>22</v>
       </c>
@@ -8239,7 +8235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="2">
         <v>22</v>
       </c>
@@ -8302,7 +8298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="2">
         <v>23</v>
       </c>
@@ -8365,7 +8361,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="2">
         <v>23</v>
       </c>
@@ -8428,7 +8424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="2">
         <v>23</v>
       </c>
@@ -8491,7 +8487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="2">
         <v>23</v>
       </c>
@@ -8554,7 +8550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="2">
         <v>23</v>
       </c>
@@ -8617,7 +8613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="2">
         <v>23</v>
       </c>
@@ -8680,7 +8676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="2">
         <v>25</v>
       </c>
@@ -8743,7 +8739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="2">
         <v>25</v>
       </c>
@@ -8806,7 +8802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="2">
         <v>25</v>
       </c>
@@ -8869,7 +8865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="2">
         <v>25</v>
       </c>
@@ -8932,7 +8928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="2">
         <v>25</v>
       </c>
@@ -8995,7 +8991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="2">
         <v>25</v>
       </c>
@@ -9058,7 +9054,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="2">
         <v>26</v>
       </c>
@@ -9121,7 +9117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="2">
         <v>26</v>
       </c>
@@ -9184,7 +9180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="2">
         <v>26</v>
       </c>
@@ -9247,7 +9243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="2">
         <v>26</v>
       </c>
@@ -9310,7 +9306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="2">
         <v>26</v>
       </c>
@@ -9373,7 +9369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="2">
         <v>26</v>
       </c>
@@ -9436,7 +9432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="2">
         <v>27</v>
       </c>
@@ -9499,7 +9495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="2">
         <v>27</v>
       </c>
@@ -9562,7 +9558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="2">
         <v>27</v>
       </c>
@@ -9625,7 +9621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="2">
         <v>27</v>
       </c>
@@ -9688,7 +9684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -9751,7 +9747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="2">
         <v>27</v>
       </c>
@@ -9814,7 +9810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="2">
         <v>29</v>
       </c>
@@ -9877,7 +9873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="2">
         <v>29</v>
       </c>
@@ -9940,7 +9936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="2">
         <v>29</v>
       </c>
@@ -10003,7 +9999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="2">
         <v>29</v>
       </c>
@@ -10066,7 +10062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="2">
         <v>29</v>
       </c>
@@ -10129,7 +10125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="2">
         <v>33</v>
       </c>
@@ -10192,7 +10188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="2">
         <v>33</v>
       </c>
@@ -10255,7 +10251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="2">
         <v>33</v>
       </c>
@@ -10318,7 +10314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="2">
         <v>33</v>
       </c>
@@ -10381,7 +10377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="2">
         <v>33</v>
       </c>
@@ -10444,7 +10440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="2">
         <v>33</v>
       </c>
@@ -10507,7 +10503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="2">
         <v>33</v>
       </c>
@@ -10570,7 +10566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="2">
         <v>33</v>
       </c>
@@ -10633,7 +10629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="2">
         <v>33</v>
       </c>
@@ -10696,7 +10692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="2">
         <v>33</v>
       </c>
@@ -10759,7 +10755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="2">
         <v>33</v>
       </c>
@@ -10822,7 +10818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="2">
         <v>33</v>
       </c>
@@ -10885,7 +10881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="2">
         <v>33</v>
       </c>
@@ -10948,7 +10944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="2">
         <v>33</v>
       </c>
@@ -11011,7 +11007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="2">
         <v>33</v>
       </c>
@@ -11074,7 +11070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="2">
         <v>33</v>
       </c>
@@ -11137,7 +11133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="2">
         <v>33</v>
       </c>
@@ -11200,7 +11196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="2">
         <v>33</v>
       </c>
@@ -11263,7 +11259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="2">
         <v>33</v>
       </c>
@@ -11326,7 +11322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="2">
         <v>33</v>
       </c>
@@ -11389,7 +11385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="2">
         <v>33</v>
       </c>
@@ -11452,7 +11448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="2">
         <v>33</v>
       </c>
@@ -11515,7 +11511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="2">
         <v>33</v>
       </c>
@@ -11578,7 +11574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="2">
         <v>33</v>
       </c>
@@ -11641,7 +11637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="2">
         <v>34</v>
       </c>
@@ -11704,7 +11700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="2">
         <v>34</v>
       </c>
@@ -11767,7 +11763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="2">
         <v>34</v>
       </c>
@@ -11830,7 +11826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="2">
         <v>34</v>
       </c>
@@ -11893,7 +11889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="2">
         <v>34</v>
       </c>
@@ -11956,7 +11952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="2">
         <v>34</v>
       </c>
@@ -12019,7 +12015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="2">
         <v>35</v>
       </c>
@@ -12082,7 +12078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="2">
         <v>35</v>
       </c>
@@ -12145,7 +12141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="2">
         <v>35</v>
       </c>
@@ -12208,7 +12204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="2">
         <v>35</v>
       </c>
@@ -12271,7 +12267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="2">
         <v>35</v>
       </c>
@@ -12334,7 +12330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="2">
         <v>35</v>
       </c>
@@ -12397,7 +12393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="2">
         <v>36</v>
       </c>
@@ -12460,7 +12456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="2">
         <v>36</v>
       </c>
@@ -12523,7 +12519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="2">
         <v>36</v>
       </c>
@@ -12586,7 +12582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="2">
         <v>36</v>
       </c>
@@ -12649,7 +12645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="2">
         <v>36</v>
       </c>
@@ -12712,7 +12708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="2">
         <v>36</v>
       </c>
@@ -12775,7 +12771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="2">
         <v>37</v>
       </c>
@@ -12838,7 +12834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="2">
         <v>37</v>
       </c>
@@ -12901,7 +12897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="2">
         <v>37</v>
       </c>
@@ -12964,7 +12960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="2">
         <v>37</v>
       </c>
@@ -13027,7 +13023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="2">
         <v>37</v>
       </c>
@@ -13090,7 +13086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="2">
         <v>37</v>
       </c>
@@ -13153,7 +13149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="2">
         <v>37</v>
       </c>
@@ -13216,7 +13212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="2">
         <v>37</v>
       </c>
@@ -13279,7 +13275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="2">
         <v>37</v>
       </c>
@@ -13342,7 +13338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="2">
         <v>37</v>
       </c>
@@ -13405,7 +13401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="2">
         <v>38</v>
       </c>
@@ -13468,7 +13464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="2">
         <v>38</v>
       </c>
@@ -13531,7 +13527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="2">
         <v>38</v>
       </c>
@@ -13594,7 +13590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="2">
         <v>38</v>
       </c>
@@ -13657,7 +13653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="2">
         <v>38</v>
       </c>
@@ -13720,7 +13716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="2">
         <v>39</v>
       </c>
@@ -13779,7 +13775,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="2">
         <v>39</v>
       </c>
@@ -13838,7 +13834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="2">
         <v>39</v>
       </c>
@@ -13897,7 +13893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="2">
         <v>39</v>
       </c>
@@ -13956,7 +13952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="2">
         <v>39</v>
       </c>
@@ -14015,7 +14011,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="2">
         <v>40</v>
       </c>
@@ -14078,7 +14074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="2">
         <v>40</v>
       </c>
@@ -14141,7 +14137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="2">
         <v>40</v>
       </c>
@@ -14204,7 +14200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="2">
         <v>40</v>
       </c>
@@ -14267,7 +14263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="2">
         <v>40</v>
       </c>
@@ -14330,7 +14326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="2">
         <v>41</v>
       </c>
@@ -14393,7 +14389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="2">
         <v>41</v>
       </c>
@@ -14456,7 +14452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="2">
         <v>41</v>
       </c>
@@ -14519,7 +14515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="2">
         <v>41</v>
       </c>
@@ -14582,7 +14578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="2">
         <v>41</v>
       </c>
@@ -14645,7 +14641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="2">
         <v>42</v>
       </c>
@@ -14708,7 +14704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="2">
         <v>42</v>
       </c>
@@ -14771,7 +14767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="2">
         <v>42</v>
       </c>
@@ -14834,7 +14830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="2">
         <v>42</v>
       </c>
@@ -14897,7 +14893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="2">
         <v>42</v>
       </c>
@@ -14960,7 +14956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="2">
         <v>43</v>
       </c>
@@ -15023,7 +15019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="2">
         <v>43</v>
       </c>
@@ -15086,7 +15082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="2">
         <v>43</v>
       </c>
@@ -15149,7 +15145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="2">
         <v>43</v>
       </c>
@@ -15212,7 +15208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="2">
         <v>44</v>
       </c>
@@ -15271,7 +15267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="2">
         <v>44</v>
       </c>
@@ -15330,7 +15326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="2">
         <v>44</v>
       </c>
@@ -15389,7 +15385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="2">
         <v>44</v>
       </c>
@@ -15448,7 +15444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="2">
         <v>44</v>
       </c>
@@ -15507,7 +15503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="2">
         <v>45</v>
       </c>
@@ -15570,7 +15566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="2">
         <v>45</v>
       </c>
@@ -15633,7 +15629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="2">
         <v>45</v>
       </c>
@@ -15696,7 +15692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="2">
         <v>45</v>
       </c>
@@ -15759,7 +15755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="2">
         <v>45</v>
       </c>
@@ -15822,7 +15818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="2">
         <v>45</v>
       </c>
@@ -15885,7 +15881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="2">
         <v>46</v>
       </c>
@@ -15948,7 +15944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="2">
         <v>46</v>
       </c>
@@ -16011,7 +16007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="2">
         <v>46</v>
       </c>
@@ -16074,7 +16070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="2">
         <v>47</v>
       </c>
@@ -16137,7 +16133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="2">
         <v>47</v>
       </c>
@@ -16200,7 +16196,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="2">
         <v>47</v>
       </c>
@@ -16263,7 +16259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="2">
         <v>47</v>
       </c>
@@ -16326,7 +16322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="2">
         <v>47</v>
       </c>
@@ -16389,7 +16385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="2">
         <v>47</v>
       </c>
@@ -16452,7 +16448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="2">
         <v>47</v>
       </c>
@@ -16515,7 +16511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="2">
         <v>47</v>
       </c>
@@ -16578,7 +16574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="2">
         <v>47</v>
       </c>
@@ -16641,7 +16637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="2">
         <v>47</v>
       </c>
@@ -16704,7 +16700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -16767,7 +16763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="2">
         <v>47</v>
       </c>
@@ -16830,7 +16826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="2">
         <v>47</v>
       </c>
@@ -16893,7 +16889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="2">
         <v>47</v>
       </c>
@@ -16956,7 +16952,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="2">
         <v>47</v>
       </c>
@@ -17019,7 +17015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="2">
         <v>47</v>
       </c>
@@ -17082,7 +17078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="2">
         <v>47</v>
       </c>
@@ -17145,7 +17141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="2">
         <v>47</v>
       </c>
@@ -17208,7 +17204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="2">
         <v>47</v>
       </c>
@@ -17271,7 +17267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="2">
         <v>47</v>
       </c>
@@ -17334,7 +17330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="2">
         <v>47</v>
       </c>
@@ -17397,7 +17393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="2">
         <v>47</v>
       </c>
@@ -17460,7 +17456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="2">
         <v>47</v>
       </c>
@@ -17523,7 +17519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="2">
         <v>47</v>
       </c>
@@ -17586,7 +17582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="2">
         <v>47</v>
       </c>
@@ -17649,7 +17645,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="2">
         <v>47</v>
       </c>
@@ -17712,7 +17708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="2">
         <v>47</v>
       </c>
@@ -17775,7 +17771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="2">
         <v>47</v>
       </c>
@@ -17838,7 +17834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="2">
         <v>47</v>
       </c>
@@ -17901,7 +17897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="2">
         <v>47</v>
       </c>
@@ -17964,7 +17960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="2">
         <v>47</v>
       </c>
@@ -18027,7 +18023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="2">
         <v>47</v>
       </c>
@@ -18090,7 +18086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="2">
         <v>47</v>
       </c>
@@ -18153,7 +18149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="2">
         <v>47</v>
       </c>
@@ -18216,7 +18212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="2">
         <v>47</v>
       </c>
@@ -18279,7 +18275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="2">
         <v>47</v>
       </c>
@@ -18342,7 +18338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="2">
         <v>47</v>
       </c>
@@ -18405,7 +18401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="2">
         <v>47</v>
       </c>
@@ -18468,7 +18464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="2">
         <v>47</v>
       </c>
@@ -18531,7 +18527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="2">
         <v>47</v>
       </c>
@@ -18594,7 +18590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="2">
         <v>47</v>
       </c>
@@ -18657,7 +18653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="2">
         <v>47</v>
       </c>
@@ -18720,7 +18716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="2">
         <v>47</v>
       </c>
@@ -18783,7 +18779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="2">
         <v>47</v>
       </c>
@@ -18846,7 +18842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="2">
         <v>47</v>
       </c>
@@ -18909,7 +18905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="2">
         <v>48</v>
       </c>
@@ -18966,7 +18962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="2">
         <v>48</v>
       </c>
@@ -19023,7 +19019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="2">
         <v>48</v>
       </c>
@@ -19080,7 +19076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="2">
         <v>48</v>
       </c>
@@ -19137,7 +19133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="2">
         <v>48</v>
       </c>
@@ -19194,7 +19190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="2">
         <v>48</v>
       </c>
@@ -19251,7 +19247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="2">
         <v>49</v>
       </c>
@@ -19310,7 +19306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="2">
         <v>49</v>
       </c>
@@ -19369,7 +19365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="2">
         <v>49</v>
       </c>
@@ -19428,7 +19424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="2">
         <v>49</v>
       </c>
@@ -19487,7 +19483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="2">
         <v>49</v>
       </c>
@@ -19546,7 +19542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="2">
         <v>50</v>
       </c>
@@ -19605,7 +19601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="2">
         <v>50</v>
       </c>
@@ -19664,7 +19660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="2">
         <v>50</v>
       </c>
@@ -19723,7 +19719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="2">
         <v>50</v>
       </c>
@@ -19782,7 +19778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="2">
         <v>51</v>
       </c>
@@ -19841,7 +19837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="2">
         <v>51</v>
       </c>
@@ -19900,7 +19896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="2">
         <v>51</v>
       </c>
@@ -19959,7 +19955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="2">
         <v>51</v>
       </c>
@@ -20018,7 +20014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="2">
         <v>52</v>
       </c>
@@ -20077,7 +20073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="2">
         <v>52</v>
       </c>
@@ -20136,7 +20132,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="2">
         <v>52</v>
       </c>
@@ -20195,7 +20191,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="2">
         <v>52</v>
       </c>
@@ -20254,7 +20250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="2">
         <v>52</v>
       </c>
@@ -20313,7 +20309,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="2">
         <v>53</v>
       </c>
@@ -20376,7 +20372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="2">
         <v>53</v>
       </c>
@@ -20439,7 +20435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="2">
         <v>53</v>
       </c>
@@ -20502,7 +20498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="2">
         <v>54</v>
       </c>
@@ -20561,7 +20557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="2">
         <v>54</v>
       </c>
@@ -20620,7 +20616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="2">
         <v>54</v>
       </c>
@@ -20679,7 +20675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="2">
         <v>54</v>
       </c>
@@ -20738,7 +20734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="2">
         <v>54</v>
       </c>
@@ -20797,7 +20793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="2">
         <v>54</v>
       </c>
@@ -20856,7 +20852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="2">
         <v>55</v>
       </c>
@@ -20919,7 +20915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="2">
         <v>55</v>
       </c>
@@ -20982,7 +20978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="2">
         <v>55</v>
       </c>
@@ -21045,7 +21041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="2">
         <v>56</v>
       </c>
@@ -21104,7 +21100,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="2">
         <v>56</v>
       </c>
@@ -21163,7 +21159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="2">
         <v>56</v>
       </c>
@@ -21222,7 +21218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="2">
         <v>56</v>
       </c>
@@ -21281,7 +21277,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="2">
         <v>56</v>
       </c>
@@ -21340,7 +21336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="2">
         <v>56</v>
       </c>
@@ -21399,7 +21395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="2">
         <v>56</v>
       </c>
@@ -21458,7 +21454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="2">
         <v>56</v>
       </c>
@@ -21517,7 +21513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="2">
         <v>57</v>
       </c>
@@ -21576,7 +21572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="2">
         <v>57</v>
       </c>
@@ -21635,7 +21631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="2">
         <v>57</v>
       </c>
@@ -21694,7 +21690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="2">
         <v>57</v>
       </c>
@@ -21753,7 +21749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="2">
         <v>57</v>
       </c>
@@ -21812,7 +21808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="2">
         <v>57</v>
       </c>
@@ -21871,7 +21867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="2">
         <v>57</v>
       </c>
@@ -21930,7 +21926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="2">
         <v>57</v>
       </c>
@@ -21989,7 +21985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="2">
         <v>58</v>
       </c>
@@ -22048,7 +22044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="2">
         <v>58</v>
       </c>
@@ -22107,7 +22103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="2">
         <v>62</v>
       </c>
@@ -22166,7 +22162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="2">
         <v>62</v>
       </c>
@@ -22225,7 +22221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="2">
         <v>59</v>
       </c>
@@ -22288,7 +22284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="2">
         <v>59</v>
       </c>
@@ -22351,7 +22347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="2">
         <v>59</v>
       </c>
@@ -22414,7 +22410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="2">
         <v>59</v>
       </c>
@@ -22477,7 +22473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="2">
         <v>59</v>
       </c>
@@ -22540,7 +22536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="2">
         <v>60</v>
       </c>
@@ -22603,7 +22599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="2">
         <v>60</v>
       </c>
@@ -22666,7 +22662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="2">
         <v>60</v>
       </c>
@@ -22729,7 +22725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="2">
         <v>60</v>
       </c>
@@ -22792,7 +22788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="2">
         <v>60</v>
       </c>
@@ -22855,7 +22851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="2">
         <v>61</v>
       </c>
@@ -22914,7 +22910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="2">
         <v>61</v>
       </c>
@@ -22973,7 +22969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="2">
         <v>61</v>
       </c>
@@ -23032,7 +23028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="2">
         <v>61</v>
       </c>
@@ -23091,7 +23087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="2">
         <v>61</v>
       </c>
@@ -23150,7 +23146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="2">
         <v>61</v>
       </c>
@@ -23209,7 +23205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="2">
         <v>62</v>
       </c>
@@ -23272,7 +23268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="2">
         <v>62</v>
       </c>
@@ -23335,7 +23331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="2">
         <v>64</v>
       </c>
@@ -23392,7 +23388,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="2">
         <v>64</v>
       </c>
@@ -23449,7 +23445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="2">
         <v>64</v>
       </c>
@@ -23506,7 +23502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="2">
         <v>64</v>
       </c>
@@ -23563,7 +23559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="2">
         <v>64</v>
       </c>
@@ -23620,7 +23616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="2">
         <v>89</v>
       </c>
@@ -23683,7 +23679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="2">
         <v>89</v>
       </c>
@@ -23746,7 +23742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="2">
         <v>89</v>
       </c>
@@ -23809,7 +23805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="2">
         <v>90</v>
       </c>
@@ -23872,7 +23868,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="2">
         <v>90</v>
       </c>
@@ -23935,7 +23931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="2">
         <v>90</v>
       </c>
@@ -23998,7 +23994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="2">
         <v>88</v>
       </c>
@@ -24061,7 +24057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="2">
         <v>88</v>
       </c>
@@ -24124,7 +24120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="2">
         <v>88</v>
       </c>
@@ -24185,7 +24181,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="b">
         <v>0</v>
@@ -24242,7 +24238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="b">
         <v>0</v>
@@ -24299,7 +24295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="b">
         <v>0</v>
@@ -24356,7 +24352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="b">
         <v>0</v>
@@ -24413,7 +24409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="b">
         <v>0</v>
@@ -24470,7 +24466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="b">
         <v>0</v>
@@ -24527,7 +24523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="b">
         <v>0</v>
@@ -24584,7 +24580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="2">
         <v>82</v>
       </c>
@@ -24647,7 +24643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="2">
         <v>82</v>
       </c>
@@ -24710,7 +24706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="2">
         <v>82</v>
       </c>
@@ -24773,7 +24769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="2">
         <v>82</v>
       </c>
@@ -24836,7 +24832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="2">
         <v>82</v>
       </c>
@@ -24899,7 +24895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="2">
         <v>82</v>
       </c>
@@ -24962,7 +24958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="2">
         <v>81</v>
       </c>
@@ -25025,7 +25021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="2">
         <v>81</v>
       </c>
@@ -25088,7 +25084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="2">
         <v>81</v>
       </c>
@@ -25151,7 +25147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="2">
         <v>81</v>
       </c>
@@ -25214,7 +25210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="2">
         <v>81</v>
       </c>
@@ -25277,7 +25273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="2">
         <v>81</v>
       </c>
@@ -25340,7 +25336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="2">
         <v>76</v>
       </c>
@@ -25403,7 +25399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="2">
         <v>76</v>
       </c>
@@ -25466,7 +25462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="2">
         <v>76</v>
       </c>
@@ -25529,7 +25525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="2">
         <v>76</v>
       </c>
@@ -25592,7 +25588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="2">
         <v>75</v>
       </c>
@@ -25655,7 +25651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="2">
         <v>75</v>
       </c>
@@ -25718,7 +25714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="2">
         <v>75</v>
       </c>
@@ -25781,7 +25777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="2">
         <v>75</v>
       </c>
@@ -25844,7 +25840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="2">
         <v>74</v>
       </c>
@@ -25903,7 +25899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="2">
         <v>74</v>
       </c>
@@ -25962,7 +25958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="2">
         <v>74</v>
       </c>
@@ -26021,7 +26017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="2">
         <v>74</v>
       </c>
@@ -26080,7 +26076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="2">
         <v>74</v>
       </c>
@@ -26139,7 +26135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="2">
         <v>87</v>
       </c>
@@ -26202,7 +26198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="2">
         <v>87</v>
       </c>
@@ -26265,7 +26261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="2">
         <v>94</v>
       </c>
@@ -26324,7 +26320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="2">
         <v>94</v>
       </c>
@@ -26383,7 +26379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="2">
         <v>94</v>
       </c>
@@ -26442,7 +26438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="2">
         <v>94</v>
       </c>
@@ -26501,7 +26497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="2">
         <v>94</v>
       </c>
@@ -26560,7 +26556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="2">
         <v>94</v>
       </c>
@@ -26619,7 +26615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="2">
         <v>94</v>
       </c>
@@ -26678,7 +26674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="2">
         <v>94</v>
       </c>
@@ -26737,7 +26733,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="2">
         <v>94</v>
       </c>
@@ -26796,7 +26792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="2">
         <v>94</v>
       </c>
@@ -26855,7 +26851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="2">
         <v>94</v>
       </c>
@@ -26914,7 +26910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="2">
         <v>94</v>
       </c>
@@ -26973,7 +26969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="2">
         <v>94</v>
       </c>
@@ -27032,7 +27028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="2"/>
       <c r="B385" s="2" t="b">
         <v>0</v>
@@ -27093,7 +27089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="2"/>
       <c r="B386" s="2" t="b">
         <v>0</v>
@@ -27154,7 +27150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="2"/>
       <c r="B387" s="2" t="b">
         <v>0</v>
@@ -27215,7 +27211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="2"/>
       <c r="B388" s="2" t="b">
         <v>0</v>
@@ -27276,7 +27272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="2"/>
       <c r="B389" s="2" t="b">
         <v>0</v>
@@ -27337,7 +27333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="2">
         <v>79</v>
       </c>
@@ -27400,7 +27396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="2">
         <v>79</v>
       </c>
@@ -27463,7 +27459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="2">
         <v>79</v>
       </c>
@@ -27526,7 +27522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="2">
         <v>79</v>
       </c>
@@ -27589,7 +27585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="2">
         <v>79</v>
       </c>
@@ -27652,7 +27648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="2">
         <v>78</v>
       </c>
@@ -27715,7 +27711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="2">
         <v>78</v>
       </c>
@@ -27778,7 +27774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="2">
         <v>78</v>
       </c>
@@ -27841,7 +27837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="2">
         <v>78</v>
       </c>
@@ -27904,7 +27900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="2">
         <v>78</v>
       </c>
@@ -27967,7 +27963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="2"/>
       <c r="B400" s="2" t="b">
         <v>0</v>
@@ -28028,7 +28024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="2"/>
       <c r="B401" s="2" t="b">
         <v>0</v>
@@ -28089,7 +28085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="2"/>
       <c r="B402" s="2" t="b">
         <v>0</v>
@@ -28150,7 +28146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="2"/>
       <c r="B403" s="2" t="b">
         <v>0</v>
@@ -28211,7 +28207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="2"/>
       <c r="B404" s="2" t="b">
         <v>0</v>
@@ -28272,7 +28268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="2"/>
       <c r="B405" s="2" t="b">
         <v>0</v>
@@ -28333,7 +28329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="2"/>
       <c r="B406" s="2" t="b">
         <v>0</v>
@@ -28394,7 +28390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="b">
         <v>0</v>
@@ -28455,7 +28451,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="2"/>
       <c r="B408" s="2" t="b">
         <v>0</v>
@@ -28516,7 +28512,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="2"/>
       <c r="B409" s="2" t="b">
         <v>0</v>
@@ -28577,7 +28573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="2"/>
       <c r="B410" s="2" t="b">
         <v>0</v>
@@ -28638,7 +28634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="2"/>
       <c r="B411" s="2" t="b">
         <v>0</v>
@@ -28699,7 +28695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="2"/>
       <c r="B412" s="2" t="b">
         <v>0</v>
@@ -28760,7 +28756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="2"/>
       <c r="B413" s="2" t="b">
         <v>0</v>
@@ -28821,7 +28817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="2"/>
       <c r="B414" s="2" t="b">
         <v>0</v>
@@ -28882,7 +28878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="2"/>
       <c r="B415" s="2" t="b">
         <v>0</v>
@@ -28943,7 +28939,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="2"/>
       <c r="B416" s="2" t="b">
         <v>0</v>
@@ -29004,7 +29000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="2"/>
       <c r="B417" s="2" t="b">
         <v>0</v>
@@ -29065,7 +29061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="2"/>
       <c r="B418" s="2" t="b">
         <v>0</v>
@@ -29126,7 +29122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="2"/>
       <c r="B419" s="2" t="b">
         <v>0</v>
@@ -29187,7 +29183,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" s="2"/>
       <c r="B420" s="2" t="b">
         <v>0</v>
@@ -29248,7 +29244,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="2"/>
       <c r="B421" s="2" t="b">
         <v>0</v>
@@ -29309,7 +29305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" s="2"/>
       <c r="B422" s="2" t="b">
         <v>0</v>
@@ -29370,7 +29366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="b">
         <v>0</v>
@@ -29431,7 +29427,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" s="2"/>
       <c r="B424" s="2" t="b">
         <v>0</v>
@@ -29492,7 +29488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" s="2"/>
       <c r="B425" s="2" t="b">
         <v>0</v>
@@ -29553,7 +29549,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" s="2"/>
       <c r="B426" s="2" t="b">
         <v>0</v>
@@ -29614,7 +29610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" s="2"/>
       <c r="B427" s="2" t="b">
         <v>0</v>
@@ -29675,7 +29671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" s="2"/>
       <c r="B428" s="2" t="b">
         <v>0</v>
@@ -29736,7 +29732,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" s="2"/>
       <c r="B429" s="2" t="b">
         <v>0</v>
@@ -29797,7 +29793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" s="2"/>
       <c r="B430" s="2" t="b">
         <v>0</v>
@@ -29858,7 +29854,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" s="2"/>
       <c r="B431" s="2" t="b">
         <v>0</v>
@@ -29919,7 +29915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" s="2"/>
       <c r="B432" s="2" t="b">
         <v>0</v>
@@ -29980,7 +29976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" s="2"/>
       <c r="B433" s="2" t="b">
         <v>0</v>
@@ -30041,7 +30037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" s="2"/>
       <c r="B434" s="2" t="b">
         <v>0</v>
@@ -30102,7 +30098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" s="2"/>
       <c r="B435" s="2" t="b">
         <v>0</v>
@@ -30163,7 +30159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" s="2"/>
       <c r="B436" s="2" t="b">
         <v>0</v>
@@ -30224,7 +30220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" s="2"/>
       <c r="B437" s="2" t="b">
         <v>0</v>
@@ -30285,7 +30281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" s="2"/>
       <c r="B438" s="2" t="b">
         <v>0</v>
@@ -30346,7 +30342,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="b">
         <v>0</v>
@@ -30407,7 +30403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" s="2"/>
       <c r="B440" s="2" t="b">
         <v>0</v>
@@ -30468,7 +30464,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" s="2"/>
       <c r="B441" s="2" t="b">
         <v>0</v>
@@ -30529,7 +30525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" s="2"/>
       <c r="B442" s="2" t="b">
         <v>0</v>
@@ -30590,7 +30586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" s="2"/>
       <c r="B443" s="2" t="b">
         <v>0</v>
@@ -30651,7 +30647,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" s="2"/>
       <c r="B444" s="2" t="b">
         <v>0</v>
@@ -30712,7 +30708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" s="2"/>
       <c r="B445" s="2" t="b">
         <v>0</v>
@@ -30773,7 +30769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" s="2"/>
       <c r="B446" s="2" t="b">
         <v>0</v>
@@ -30834,7 +30830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" s="2"/>
       <c r="B447" s="2" t="b">
         <v>0</v>
@@ -30895,7 +30891,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" s="2"/>
       <c r="B448" s="2" t="b">
         <v>0</v>
@@ -30956,7 +30952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" s="2"/>
       <c r="B449" s="2" t="b">
         <v>0</v>
@@ -31017,7 +31013,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" s="2"/>
       <c r="B450" s="2" t="b">
         <v>0</v>
@@ -31078,7 +31074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" s="2"/>
       <c r="B451" s="2" t="b">
         <v>0</v>
@@ -31139,7 +31135,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" s="2"/>
       <c r="B452" s="2" t="b">
         <v>0</v>
@@ -31200,7 +31196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" s="2"/>
       <c r="B453" s="2" t="b">
         <v>0</v>
@@ -31257,7 +31253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" s="2"/>
       <c r="B454" s="2" t="b">
         <v>0</v>
@@ -31314,7 +31310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="b">
         <v>0</v>
@@ -31371,7 +31367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="456" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" s="2"/>
       <c r="B456" s="2" t="b">
         <v>0</v>
@@ -31428,7 +31424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="457" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" s="2"/>
       <c r="B457" s="2" t="b">
         <v>0</v>
@@ -31485,7 +31481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" s="2"/>
       <c r="B458" s="2" t="b">
         <v>0</v>
@@ -31542,7 +31538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" s="2"/>
       <c r="B459" s="2" t="b">
         <v>0</v>
@@ -31599,7 +31595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" s="2"/>
       <c r="B460" s="2" t="b">
         <v>0</v>
@@ -31656,7 +31652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" s="2"/>
       <c r="B461" s="2" t="b">
         <v>0</v>
@@ -31713,7 +31709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" s="2"/>
       <c r="B462" s="2" t="b">
         <v>0</v>
@@ -31770,7 +31766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" s="2"/>
       <c r="B463" s="2" t="b">
         <v>0</v>
@@ -31827,7 +31823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" s="2"/>
       <c r="B464" s="2" t="b">
         <v>0</v>
@@ -31884,7 +31880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" s="2"/>
       <c r="B465" s="2" t="b">
         <v>0</v>
@@ -31941,7 +31937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" s="2"/>
       <c r="B466" s="2" t="b">
         <v>0</v>
@@ -31998,7 +31994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" s="2"/>
       <c r="B467" s="2" t="b">
         <v>0</v>
@@ -32055,7 +32051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="468" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" s="2"/>
       <c r="B468" s="2" t="b">
         <v>0</v>
@@ -32112,7 +32108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="469" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" s="2"/>
       <c r="B469" s="2" t="b">
         <v>0</v>
@@ -32169,7 +32165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" s="2"/>
       <c r="B470" s="2" t="b">
         <v>0</v>
@@ -32226,7 +32222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="b">
         <v>0</v>
@@ -32279,7 +32275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" s="2"/>
       <c r="B472" s="2" t="b">
         <v>0</v>
@@ -32334,7 +32330,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" s="2"/>
       <c r="B473" s="2" t="b">
         <v>0</v>
@@ -32389,7 +32385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="474" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" s="2"/>
       <c r="B474" s="2" t="b">
         <v>0</v>
@@ -32444,7 +32440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="475" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" s="2"/>
       <c r="B475" s="2" t="b">
         <v>0</v>
@@ -32499,7 +32495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="476" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" s="2"/>
       <c r="B476" s="2" t="b">
         <v>0</v>
@@ -32554,7 +32550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="477" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" s="2"/>
       <c r="B477" s="2" t="b">
         <v>0</v>
@@ -32609,7 +32605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" s="2"/>
       <c r="B478" s="2" t="b">
         <v>0</v>
@@ -32662,7 +32658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="479" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" s="2"/>
       <c r="B479" s="2" t="b">
         <v>0</v>
@@ -32717,7 +32713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" s="2"/>
       <c r="B480" s="2" t="b">
         <v>0</v>
@@ -32772,7 +32768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" s="2"/>
       <c r="B481" s="2" t="b">
         <v>0</v>
@@ -32827,7 +32823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" s="2"/>
       <c r="B482" s="2" t="b">
         <v>0</v>
@@ -32882,7 +32878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" s="2"/>
       <c r="B483" s="2" t="b">
         <v>0</v>
@@ -32937,7 +32933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" s="2"/>
       <c r="B484" s="2" t="b">
         <v>0</v>
@@ -32992,7 +32988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" s="2"/>
       <c r="B485" s="2" t="b">
         <v>0</v>
@@ -33047,7 +33043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" s="2"/>
       <c r="B486" s="2" t="b">
         <v>0</v>
@@ -33104,7 +33100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" s="2"/>
       <c r="B487" s="2" t="b">
         <v>0</v>
@@ -33161,7 +33157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" s="2"/>
       <c r="B488" s="2" t="b">
         <v>0</v>
@@ -33218,7 +33214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="489" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" s="2"/>
       <c r="B489" s="2" t="b">
         <v>0</v>
@@ -33275,7 +33271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="490" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" s="2"/>
       <c r="B490" s="2" t="b">
         <v>0</v>
@@ -33332,7 +33328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="491" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" s="2"/>
       <c r="B491" s="2" t="b">
         <v>0</v>
@@ -33389,7 +33385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="492" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" s="2"/>
       <c r="B492" s="2" t="b">
         <v>0</v>
@@ -33446,7 +33442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" s="2"/>
       <c r="B493" s="2" t="b">
         <v>0</v>
@@ -33503,7 +33499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="494" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" s="2"/>
       <c r="B494" s="2" t="b">
         <v>0</v>
@@ -33560,7 +33556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="495" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" s="2"/>
       <c r="B495" s="2" t="b">
         <v>0</v>
@@ -33617,7 +33613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" s="2"/>
       <c r="B496" s="2" t="b">
         <v>0</v>
@@ -33674,7 +33670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" s="2"/>
       <c r="B497" s="2" t="b">
         <v>0</v>
@@ -33731,7 +33727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" s="2"/>
       <c r="B498" s="2" t="b">
         <v>0</v>
@@ -33788,7 +33784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="499" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" s="2"/>
       <c r="B499" s="2" t="b">
         <v>0</v>
@@ -33845,7 +33841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" s="2"/>
       <c r="B500" s="2" t="b">
         <v>0</v>
@@ -33902,7 +33898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="501" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" s="2"/>
       <c r="B501" s="2" t="b">
         <v>0</v>
@@ -33959,7 +33955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="502" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" s="2"/>
       <c r="B502" s="2" t="b">
         <v>0</v>
@@ -34020,7 +34016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="503" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" s="2"/>
       <c r="B503" s="2" t="b">
         <v>0</v>
@@ -34081,7 +34077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" s="2"/>
       <c r="B504" s="2" t="b">
         <v>0</v>
@@ -34142,7 +34138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" s="2"/>
       <c r="B505" s="2" t="b">
         <v>0</v>
@@ -34203,7 +34199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" s="2"/>
       <c r="B506" s="2" t="b">
         <v>0</v>
@@ -34264,7 +34260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" s="2"/>
       <c r="B507" s="2" t="b">
         <v>0</v>
@@ -34325,7 +34321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" s="2"/>
       <c r="B508" s="2" t="b">
         <v>0</v>
@@ -34386,7 +34382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" s="2"/>
       <c r="B509" s="2" t="b">
         <v>0</v>
@@ -34447,7 +34443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" s="2"/>
       <c r="B510" s="2" t="b">
         <v>0</v>
@@ -34508,7 +34504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" s="2"/>
       <c r="B511" s="2" t="b">
         <v>0</v>
@@ -34569,7 +34565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" s="2"/>
       <c r="B512" s="2" t="b">
         <v>0</v>
@@ -34630,7 +34626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="513" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" s="2"/>
       <c r="B513" s="2" t="b">
         <v>0</v>
@@ -34691,7 +34687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" s="2"/>
       <c r="B514" s="2" t="b">
         <v>0</v>
@@ -34752,7 +34748,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="515" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" s="2"/>
       <c r="B515" s="2" t="b">
         <v>0</v>
@@ -34813,7 +34809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" s="2"/>
       <c r="B516" s="2" t="b">
         <v>0</v>
@@ -34874,7 +34870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" s="2"/>
       <c r="B517" s="2" t="b">
         <v>0</v>
@@ -34935,7 +34931,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" s="2"/>
       <c r="B518" s="2" t="b">
         <v>0</v>
@@ -34996,7 +34992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" s="2"/>
       <c r="B519" s="2" t="b">
         <v>0</v>
@@ -35057,7 +35053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" s="2"/>
       <c r="B520" s="2" t="b">
         <v>0</v>
@@ -35118,7 +35114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" s="2"/>
       <c r="B521" s="2" t="b">
         <v>0</v>
@@ -35179,7 +35175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" s="2"/>
       <c r="B522" s="2" t="b">
         <v>0</v>
@@ -35240,7 +35236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" s="2"/>
       <c r="B523" s="2" t="b">
         <v>0</v>
@@ -35301,7 +35297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" s="2"/>
       <c r="B524" s="2" t="b">
         <v>0</v>
@@ -35362,7 +35358,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" s="2"/>
       <c r="B525" s="2" t="b">
         <v>0</v>
@@ -35423,7 +35419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" s="2"/>
       <c r="B526" s="2" t="b">
         <v>0</v>
@@ -35484,7 +35480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" s="2"/>
       <c r="B527" s="2" t="b">
         <v>0</v>
@@ -35545,7 +35541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" s="2"/>
       <c r="B528" s="2" t="b">
         <v>0</v>
@@ -35606,7 +35602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" s="2"/>
       <c r="B529" s="2" t="b">
         <v>0</v>
@@ -35667,7 +35663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" s="2"/>
       <c r="B530" s="2" t="b">
         <v>0</v>
@@ -35728,7 +35724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" s="2"/>
       <c r="B531" s="2" t="b">
         <v>0</v>
@@ -35789,7 +35785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" s="2"/>
       <c r="B532" s="2" t="b">
         <v>0</v>
@@ -35850,7 +35846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" s="2"/>
       <c r="B533" s="2" t="b">
         <v>0</v>
@@ -35911,7 +35907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" s="2"/>
       <c r="B534" s="2" t="b">
         <v>0</v>
@@ -35972,7 +35968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" s="2"/>
       <c r="B535" s="2" t="b">
         <v>0</v>
@@ -36033,7 +36029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" s="2"/>
       <c r="B536" s="2" t="b">
         <v>0</v>
@@ -36094,7 +36090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" s="2"/>
       <c r="B537" s="2" t="b">
         <v>0</v>
@@ -36155,7 +36151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" s="2"/>
       <c r="B538" s="2" t="b">
         <v>0</v>
@@ -36216,7 +36212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" s="2"/>
       <c r="B539" s="2" t="b">
         <v>0</v>
@@ -36277,7 +36273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" s="2"/>
       <c r="B540" s="2" t="b">
         <v>0</v>
@@ -36338,7 +36334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" s="2"/>
       <c r="B541" s="2" t="b">
         <v>0</v>
@@ -36399,7 +36395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" s="2"/>
       <c r="B542" s="2" t="b">
         <v>0</v>
@@ -36460,7 +36456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" s="2"/>
       <c r="B543" s="2" t="b">
         <v>0</v>
@@ -36521,7 +36517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="544" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" s="2"/>
       <c r="B544" s="2" t="b">
         <v>0</v>
@@ -36582,7 +36578,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="545" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" s="2"/>
       <c r="B545" s="2" t="b">
         <v>0</v>
@@ -36643,7 +36639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" s="2"/>
       <c r="B546" s="2" t="b">
         <v>0</v>
@@ -36704,7 +36700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" s="2"/>
       <c r="B547" s="2" t="b">
         <v>0</v>
@@ -36765,7 +36761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" s="2"/>
       <c r="B548" s="2" t="b">
         <v>0</v>
@@ -36826,7 +36822,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" s="2"/>
       <c r="B549" s="2" t="b">
         <v>0</v>
@@ -36887,7 +36883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="550" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" s="2"/>
       <c r="B550" s="2" t="b">
         <v>0</v>
@@ -36948,7 +36944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" s="2"/>
       <c r="B551" s="2" t="b">
         <v>0</v>
@@ -37009,7 +37005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" s="2"/>
       <c r="B552" s="2" t="b">
         <v>0</v>
@@ -37070,7 +37066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="553" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" s="2"/>
       <c r="B553" s="2" t="b">
         <v>0</v>
@@ -37131,7 +37127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" s="2"/>
       <c r="B554" s="2" t="b">
         <v>0</v>
@@ -37192,7 +37188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" s="2"/>
       <c r="B555" s="2" t="b">
         <v>0</v>
@@ -37253,7 +37249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" s="2"/>
       <c r="B556" s="2" t="b">
         <v>0</v>
@@ -37314,7 +37310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="557" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" s="2"/>
       <c r="B557" s="2" t="b">
         <v>0</v>
@@ -37363,7 +37359,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="558" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" s="2"/>
       <c r="B558" s="2" t="b">
         <v>0</v>
@@ -37412,7 +37408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="559" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" s="2"/>
       <c r="B559" s="2" t="b">
         <v>0</v>
@@ -37461,7 +37457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" s="2">
         <v>83</v>
       </c>
@@ -37524,7 +37520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" s="2">
         <v>83</v>
       </c>
@@ -37587,7 +37583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" s="2">
         <v>83</v>
       </c>
@@ -37650,7 +37646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" s="2"/>
       <c r="B563" s="2" t="b">
         <v>0</v>
@@ -37711,7 +37707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="564" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" s="2"/>
       <c r="B564" s="2" t="b">
         <v>1</v>
@@ -37772,7 +37768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="565" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" s="2"/>
       <c r="B565" s="2" t="b">
         <v>0</v>
@@ -37833,7 +37829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" s="2">
         <v>85</v>
       </c>
@@ -37896,7 +37892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="567" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" s="2">
         <v>85</v>
       </c>
@@ -37959,7 +37955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="568" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" s="2">
         <v>85</v>
       </c>
@@ -38022,7 +38018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" s="2">
         <v>86</v>
       </c>
@@ -38085,7 +38081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" s="2">
         <v>86</v>
       </c>
@@ -38148,7 +38144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" s="2">
         <v>86</v>
       </c>
@@ -38211,7 +38207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" s="2">
         <v>84</v>
       </c>
@@ -38274,7 +38270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" s="2">
         <v>84</v>
       </c>
@@ -38337,7 +38333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="574" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" s="2">
         <v>84</v>
       </c>
@@ -38400,7 +38396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" s="2"/>
       <c r="B575" s="2" t="b">
         <v>0</v>
@@ -38449,7 +38445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" s="2">
         <v>80</v>
       </c>
@@ -38508,7 +38504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" s="2">
         <v>80</v>
       </c>
@@ -38567,7 +38563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="578" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" s="2">
         <v>80</v>
       </c>
@@ -38626,7 +38622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="579" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" s="2">
         <v>80</v>
       </c>
@@ -38685,7 +38681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" s="2">
         <v>80</v>
       </c>
@@ -38744,7 +38740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" s="2">
         <v>80</v>
       </c>
@@ -38803,7 +38799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="582" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" s="2">
         <v>80</v>
       </c>
@@ -38862,7 +38858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" s="2">
         <v>80</v>
       </c>
@@ -38921,7 +38917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="584" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" s="2">
         <v>80</v>
       </c>
@@ -38980,7 +38976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="585" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" s="2"/>
       <c r="B585" s="2" t="b">
         <v>0</v>
@@ -39031,7 +39027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="586" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" s="2">
         <v>91</v>
       </c>
@@ -39090,7 +39086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" s="2">
         <v>91</v>
       </c>
@@ -39149,7 +39145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" s="2">
         <v>91</v>
       </c>
@@ -39208,7 +39204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" s="2">
         <v>91</v>
       </c>
@@ -39267,7 +39263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" s="2">
         <v>91</v>
       </c>
@@ -39326,7 +39322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" s="2">
         <v>91</v>
       </c>
@@ -39385,7 +39381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="592" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" s="2">
         <v>91</v>
       </c>
@@ -39444,7 +39440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="593" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" s="2"/>
       <c r="B593" s="2" t="b">
         <v>0</v>
@@ -39501,7 +39497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="594" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" s="2"/>
       <c r="B594" s="2" t="b">
         <v>0</v>
@@ -39558,7 +39554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" s="2"/>
       <c r="B595" s="2" t="b">
         <v>0</v>
@@ -39615,7 +39611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" s="2"/>
       <c r="B596" s="2" t="b">
         <v>0</v>
@@ -39672,7 +39668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" s="2"/>
       <c r="B597" s="2" t="b">
         <v>0</v>
@@ -39729,7 +39725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="598" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" s="2"/>
       <c r="B598" s="2" t="b">
         <v>0</v>
@@ -39786,7 +39782,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="599" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" s="2"/>
       <c r="B599" s="2" t="b">
         <v>0</v>
@@ -39843,7 +39839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="600" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" s="2"/>
       <c r="B600" s="2" t="b">
         <v>0</v>
@@ -39900,7 +39896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="601" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" s="2"/>
       <c r="B601" s="2" t="b">
         <v>0</v>
@@ -39957,7 +39953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="602" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" s="2"/>
       <c r="B602" s="2" t="b">
         <v>0</v>
@@ -40012,7 +40008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="603" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" s="2"/>
       <c r="B603" s="2" t="b">
         <v>0</v>
@@ -40067,7 +40063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="604" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" s="2"/>
       <c r="B604" s="2" t="b">
         <v>0</v>
@@ -40122,7 +40118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="605" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A605" s="2"/>
       <c r="B605" s="2" t="b">
         <v>0</v>
@@ -40177,7 +40173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="606" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A606" s="2"/>
       <c r="B606" s="2" t="b">
         <v>0</v>
@@ -40232,7 +40228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A607" s="2"/>
       <c r="B607" s="2" t="b">
         <v>0</v>
@@ -40287,7 +40283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="608" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A608" s="2"/>
       <c r="B608" s="2" t="b">
         <v>0</v>
@@ -40342,7 +40338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="609" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" s="2"/>
       <c r="B609" s="2" t="b">
         <v>0</v>
@@ -40397,7 +40393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A610" s="2"/>
       <c r="B610" s="2" t="b">
         <v>0</v>
@@ -40452,7 +40448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="611" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A611" s="2"/>
       <c r="B611" s="2" t="b">
         <v>0</v>
@@ -40507,7 +40503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="612" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A612" s="2"/>
       <c r="B612" s="2" t="b">
         <v>0</v>
@@ -40560,7 +40556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="613" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A613" s="2"/>
       <c r="B613" s="2" t="b">
         <v>0</v>
@@ -40613,7 +40609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A614" s="2"/>
       <c r="B614" s="2" t="b">
         <v>0</v>
@@ -40664,7 +40660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="615" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A615" s="2">
         <v>67</v>
       </c>
@@ -40727,7 +40723,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="616" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A616" s="2">
         <v>67</v>
       </c>
@@ -40790,7 +40786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="617" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A617" s="2">
         <v>67</v>
       </c>
@@ -40853,7 +40849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A618" s="2">
         <v>67</v>
       </c>
@@ -40916,7 +40912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="619" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A619" s="2">
         <v>67</v>
       </c>
@@ -40979,7 +40975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A620" s="2"/>
       <c r="B620" s="2" t="b">
         <v>0</v>
@@ -41036,7 +41032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A621" s="2"/>
       <c r="B621" s="2" t="b">
         <v>0</v>
@@ -41093,7 +41089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="622" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A622" s="2"/>
       <c r="B622" s="2" t="b">
         <v>0</v>
@@ -41150,7 +41146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="623" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A623" s="2"/>
       <c r="B623" s="2" t="b">
         <v>0</v>
@@ -41207,7 +41203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="624" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A624" s="2"/>
       <c r="B624" s="2" t="b">
         <v>0</v>
@@ -41264,7 +41260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A625" s="2"/>
       <c r="B625" s="2" t="b">
         <v>0</v>
@@ -41321,7 +41317,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="626" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A626" s="2"/>
       <c r="B626" s="2" t="b">
         <v>0</v>
@@ -41378,7 +41374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A627" s="2"/>
       <c r="B627" s="2" t="b">
         <v>0</v>
@@ -41435,7 +41431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A628" s="2"/>
       <c r="B628" s="2" t="b">
         <v>0</v>
@@ -41492,7 +41488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A629" s="2"/>
       <c r="B629" s="2" t="b">
         <v>0</v>
@@ -41549,7 +41545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A630" s="2"/>
       <c r="B630" s="2" t="b">
         <v>0</v>
@@ -41606,7 +41602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="631" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A631" s="2"/>
       <c r="B631" s="2" t="b">
         <v>0</v>
@@ -41663,7 +41659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A632" s="2"/>
       <c r="B632" s="2" t="b">
         <v>0</v>
@@ -41720,7 +41716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="633" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A633" s="2"/>
       <c r="B633" s="2" t="b">
         <v>0</v>
@@ -41777,7 +41773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="634" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A634" s="2">
         <v>77</v>
       </c>
@@ -41836,7 +41832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A635" s="2">
         <v>77</v>
       </c>
@@ -41895,7 +41891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="636" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A636" s="2">
         <v>77</v>
       </c>
@@ -41954,7 +41950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="637" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A637" s="2">
         <v>77</v>
       </c>
@@ -42013,7 +42009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A638" s="2">
         <v>77</v>
       </c>
@@ -42072,7 +42068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A639" s="2"/>
       <c r="B639" s="2" t="b">
         <v>0</v>
@@ -42121,7 +42117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="640" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A640" s="2"/>
       <c r="B640" s="2" t="b">
         <v>0</v>
@@ -42170,7 +42166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="641" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A641" s="2"/>
       <c r="B641" s="2" t="b">
         <v>0</v>
@@ -42227,7 +42223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A642" s="2"/>
       <c r="B642" s="2" t="b">
         <v>0</v>
@@ -42284,7 +42280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="643" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A643" s="2">
         <v>65</v>
       </c>
@@ -42343,7 +42339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="644" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A644" s="2">
         <v>65</v>
       </c>
@@ -42402,7 +42398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A645" s="2">
         <v>65</v>
       </c>
@@ -42461,7 +42457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="646" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A646" s="2">
         <v>65</v>
       </c>
@@ -42520,7 +42516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A647" s="2">
         <v>65</v>
       </c>
@@ -42579,7 +42575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="648" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A648" s="2">
         <v>65</v>
       </c>
@@ -42638,7 +42634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="649" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A649" s="2"/>
       <c r="B649" s="2" t="b">
         <v>0</v>
@@ -42693,7 +42689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="650" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A650" s="2"/>
       <c r="B650" s="2" t="b">
         <v>0</v>
@@ -42748,7 +42744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A651" s="2">
         <v>68</v>
       </c>
@@ -42805,7 +42801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="652" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A652" s="2">
         <v>68</v>
       </c>
@@ -42862,7 +42858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="653" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A653" s="2">
         <v>69</v>
       </c>
@@ -42919,7 +42915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A654" s="2">
         <v>69</v>
       </c>
@@ -42976,7 +42972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A655" s="2">
         <v>69</v>
       </c>
@@ -43033,7 +43029,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="656" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A656" s="2">
         <v>69</v>
       </c>
@@ -43090,7 +43086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A657" s="2">
         <v>69</v>
       </c>
@@ -43147,7 +43143,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A658" s="2">
         <v>69</v>
       </c>
@@ -43204,7 +43200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A659" s="2">
         <v>69</v>
       </c>
@@ -43261,7 +43257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A660" s="2">
         <v>70</v>
       </c>
@@ -43322,7 +43318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="661" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A661" s="2">
         <v>70</v>
       </c>
@@ -43383,7 +43379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="662" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A662" s="2">
         <v>70</v>
       </c>
@@ -43444,7 +43440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="663" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A663" s="2">
         <v>70</v>
       </c>
@@ -43505,7 +43501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="664" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A664" s="2">
         <v>70</v>
       </c>
@@ -43566,7 +43562,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="665" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A665" s="2">
         <v>66</v>
       </c>
@@ -43627,7 +43623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="666" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A666" s="2">
         <v>66</v>
       </c>
@@ -43688,7 +43684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="667" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A667" s="2">
         <v>66</v>
       </c>
@@ -43749,7 +43745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="668" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A668" s="2">
         <v>66</v>
       </c>
@@ -43810,7 +43806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="669" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A669" s="2">
         <v>66</v>
       </c>
@@ -43871,7 +43867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="670" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A670" s="2">
         <v>71</v>
       </c>
@@ -43932,7 +43928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="671" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A671" s="2">
         <v>71</v>
       </c>
@@ -43993,7 +43989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="672" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A672" s="2">
         <v>71</v>
       </c>
@@ -44054,7 +44050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="673" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A673" s="2">
         <v>71</v>
       </c>
@@ -44115,7 +44111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="674" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A674" s="2">
         <v>71</v>
       </c>
@@ -44176,7 +44172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="675" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A675" s="2">
         <v>72</v>
       </c>
@@ -44237,7 +44233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="676" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A676" s="2">
         <v>72</v>
       </c>
@@ -44298,7 +44294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="677" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A677" s="2">
         <v>72</v>
       </c>
@@ -44359,7 +44355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="678" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A678" s="2">
         <v>72</v>
       </c>
@@ -44420,7 +44416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="679" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A679" s="2">
         <v>72</v>
       </c>
@@ -44481,7 +44477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="680" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A680" s="2">
         <v>73</v>
       </c>
@@ -44542,7 +44538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="681" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A681" s="2">
         <v>73</v>
       </c>
@@ -44603,7 +44599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="682" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A682" s="2">
         <v>73</v>
       </c>
@@ -44664,7 +44660,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="683" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A683" s="2">
         <v>73</v>
       </c>
@@ -44725,7 +44721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="684" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A684" s="2">
         <v>73</v>
       </c>
@@ -44786,7 +44782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="685" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A685" s="2"/>
       <c r="B685" s="2" t="b">
         <v>0</v>
@@ -44845,7 +44841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="686" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A686" s="2"/>
       <c r="B686" s="2" t="b">
         <v>0</v>
@@ -44904,7 +44900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="687" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A687" s="2"/>
       <c r="B687" s="2" t="b">
         <v>0</v>
@@ -44963,7 +44959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="688" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A688" s="2"/>
       <c r="B688" s="2" t="b">
         <v>0</v>
@@ -45022,7 +45018,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A689" s="2"/>
       <c r="B689" s="2" t="b">
         <v>0</v>
@@ -45081,7 +45077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A690" s="2"/>
       <c r="B690" s="2" t="b">
         <v>0</v>
@@ -45140,7 +45136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="691" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A691" s="2"/>
       <c r="B691" s="2" t="b">
         <v>0</v>
@@ -45199,7 +45195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="692" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A692" s="2"/>
       <c r="B692" s="2" t="b">
         <v>0</v>
@@ -45258,7 +45254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="693" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A693" s="2"/>
       <c r="B693" s="2" t="b">
         <v>0</v>
@@ -45317,7 +45313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="694" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A694" s="2"/>
       <c r="B694" s="2" t="b">
         <v>0</v>
@@ -45376,7 +45372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="695" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A695" s="2"/>
       <c r="B695" s="2" t="b">
         <v>0</v>
@@ -45435,7 +45431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="696" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A696" s="2"/>
       <c r="B696" s="2" t="b">
         <v>0</v>
@@ -45494,7 +45490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="697" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A697" s="2"/>
       <c r="B697" s="2" t="b">
         <v>0</v>
@@ -45553,7 +45549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="698" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A698" s="2"/>
       <c r="B698" s="2" t="b">
         <v>0</v>
@@ -45612,7 +45608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="699" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A699" s="2"/>
       <c r="B699" s="2" t="b">
         <v>0</v>
@@ -45671,7 +45667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="700" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A700" s="2"/>
       <c r="B700" s="2" t="b">
         <v>0</v>
@@ -45730,7 +45726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="701" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A701" s="2"/>
       <c r="B701" s="2" t="b">
         <v>0</v>
@@ -45789,7 +45785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="702" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A702" s="2"/>
       <c r="B702" s="2" t="b">
         <v>0</v>
@@ -45848,7 +45844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="703" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A703" s="2"/>
       <c r="B703" s="2" t="b">
         <v>0</v>
@@ -45907,7 +45903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="704" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A704" s="2"/>
       <c r="B704" s="2" t="b">
         <v>0</v>
@@ -45966,7 +45962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="705" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A705" s="2"/>
       <c r="B705" s="2" t="b">
         <v>0</v>
@@ -46025,7 +46021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="706" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A706" s="2"/>
       <c r="B706" s="2" t="b">
         <v>0</v>
@@ -46084,7 +46080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="707" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A707" s="2"/>
       <c r="B707" s="2" t="b">
         <v>0</v>
@@ -46143,7 +46139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="708" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A708" s="2"/>
       <c r="B708" s="2" t="b">
         <v>0</v>
@@ -46202,7 +46198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="709" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A709" s="2"/>
       <c r="B709" s="2" t="b">
         <v>0</v>
@@ -46261,7 +46257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="710" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A710" s="2"/>
       <c r="B710" s="2" t="b">
         <v>0</v>
@@ -46320,7 +46316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="711" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A711" s="2"/>
       <c r="B711" s="2" t="b">
         <v>0</v>
@@ -46379,7 +46375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="712" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A712" s="2"/>
       <c r="B712" s="2" t="b">
         <v>0</v>
@@ -46438,7 +46434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="713" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A713" s="2"/>
       <c r="B713" s="2" t="b">
         <v>0</v>
@@ -46497,7 +46493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="714" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A714" s="2"/>
       <c r="B714" s="2" t="b">
         <v>0</v>
@@ -46556,7 +46552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="715" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A715" s="2"/>
       <c r="B715" s="2" t="b">
         <v>0</v>
@@ -46615,7 +46611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="716" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A716" s="2"/>
       <c r="B716" s="2" t="b">
         <v>0</v>
@@ -46674,7 +46670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="717" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A717" s="2"/>
       <c r="B717" s="2" t="b">
         <v>0</v>
@@ -46733,7 +46729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="718" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A718" s="2"/>
       <c r="B718" s="2" t="b">
         <v>0</v>
@@ -46792,7 +46788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="719" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A719" s="2"/>
       <c r="B719" s="2" t="b">
         <v>0</v>
@@ -46851,7 +46847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="720" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A720" s="2"/>
       <c r="B720" s="2" t="b">
         <v>0</v>
@@ -46906,7 +46902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="721" spans="1:21" ht="18" hidden="1" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
       <c r="A721" s="2"/>
       <c r="B721" s="2" t="b">
         <v>0</v>
@@ -46962,78 +46958,67 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T721" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
-    <filterColumn colId="13">
-      <filters>
-        <filter val="At_Risk_Losing_Home:Needs_In_Past_12_Months"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T721" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T642">
     <sortCondition ref="A2:A642"/>
   </sortState>
-  <conditionalFormatting sqref="A1:T1 A2:F305 I653:J653 R653:T684 O653:O684 L651:L684 M654:N684 T1:U721 G660:J721 K2:K721 C306:C721 A493:B721 D661:F721 O685:P721">
-    <cfRule type="expression" dxfId="13" priority="4">
+  <conditionalFormatting sqref="A1:T1 T1:U721 A2:F305 K2:K721 C306:C721 A493:B721 L651:L684 I653:J653 O653:T684 M654:N684 G660:J721 D661:F721 L685:T721">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D665:E684">
-    <cfRule type="expression" dxfId="12" priority="42">
+    <cfRule type="expression" dxfId="11" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D306:F652">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G671:G674">
-    <cfRule type="expression" dxfId="10" priority="41">
+    <cfRule type="expression" dxfId="9" priority="41">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:J652">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H675">
-    <cfRule type="expression" dxfId="8" priority="39">
+    <cfRule type="expression" dxfId="7" priority="39">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H680">
-    <cfRule type="expression" dxfId="7" priority="36">
+    <cfRule type="expression" dxfId="6" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670:I673">
-    <cfRule type="expression" dxfId="6" priority="35">
+    <cfRule type="expression" dxfId="5" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I675:I678">
-    <cfRule type="expression" dxfId="5" priority="34">
+    <cfRule type="expression" dxfId="4" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I680:I683">
-    <cfRule type="expression" dxfId="4" priority="33">
+    <cfRule type="expression" dxfId="3" priority="33">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 D653:H660 G659:I659">
-    <cfRule type="expression" dxfId="3" priority="27">
+    <cfRule type="expression" dxfId="2" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 L685:N721 Q685:T721">
-    <cfRule type="expression" dxfId="2" priority="44">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P653:Q684">
-    <cfRule type="expression" dxfId="1" priority="20">
+  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652">
+    <cfRule type="expression" dxfId="1" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
+++ b/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\2_responsibilities\nvi_etl\nvi_etl\survey\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5B19DE-4816-4DEF-9047-43101A987B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A26E532-8081-4DF7-B17E-3BF71F1028B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6149" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6149" uniqueCount="743">
   <si>
     <t>indicator_include</t>
   </si>
@@ -2020,9 +2020,6 @@
     <t>The condition of housing in your neighborhood</t>
   </si>
   <si>
-    <t>Do you have a family member who is or has been incarcerated in the last 12 months?</t>
-  </si>
-  <si>
     <t>Poor air quality</t>
   </si>
   <si>
@@ -2272,6 +2269,12 @@
   </si>
   <si>
     <t>Other (please describe)::Community_Engagement_Process_Participation...140</t>
+  </si>
+  <si>
+    <t>Do you have a family member who is or has been incarcerated in the last three years?</t>
+  </si>
+  <si>
+    <t>Youth_in_Household_Under5 == 1</t>
   </si>
 </sst>
 </file>
@@ -3346,7 +3349,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>577</v>
@@ -3394,7 +3397,7 @@
         <v>11</v>
       </c>
       <c r="U1" s="15" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
@@ -6397,7 +6400,7 @@
       </c>
       <c r="M49" s="2"/>
       <c r="N49" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>508</v>
@@ -6515,7 +6518,7 @@
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>508</v>
@@ -6574,7 +6577,7 @@
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>508</v>
@@ -14661,7 +14664,7 @@
         <v>590</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>36</v>
@@ -14724,7 +14727,7 @@
         <v>590</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>38</v>
@@ -14787,7 +14790,7 @@
         <v>590</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>39</v>
@@ -14850,7 +14853,7 @@
         <v>590</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>40</v>
@@ -14913,7 +14916,7 @@
         <v>590</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>41</v>
@@ -15901,7 +15904,7 @@
         <v>592</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>658</v>
+        <v>741</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>122</v>
@@ -15938,7 +15941,7 @@
         <v>44927</v>
       </c>
       <c r="T202" s="14">
-        <v>45657</v>
+        <v>73050</v>
       </c>
       <c r="U202" s="16">
         <v>4</v>
@@ -15964,7 +15967,7 @@
         <v>592</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>658</v>
+        <v>741</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>124</v>
@@ -16001,7 +16004,7 @@
         <v>44927</v>
       </c>
       <c r="T203" s="14">
-        <v>45657</v>
+        <v>73050</v>
       </c>
       <c r="U203" s="16">
         <v>4</v>
@@ -16027,7 +16030,7 @@
         <v>592</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>658</v>
+        <v>741</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>125</v>
@@ -16064,7 +16067,7 @@
         <v>44927</v>
       </c>
       <c r="T204" s="14">
-        <v>45657</v>
+        <v>73050</v>
       </c>
       <c r="U204" s="16">
         <v>4</v>
@@ -16090,7 +16093,7 @@
         <v>593</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>362</v>
@@ -16153,7 +16156,7 @@
         <v>593</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>364</v>
@@ -16216,7 +16219,7 @@
         <v>593</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>365</v>
@@ -16279,7 +16282,7 @@
         <v>593</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>366</v>
@@ -16342,7 +16345,7 @@
         <v>593</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>367</v>
@@ -16405,7 +16408,7 @@
         <v>593</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>362</v>
@@ -16468,7 +16471,7 @@
         <v>593</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>364</v>
@@ -16531,7 +16534,7 @@
         <v>593</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>365</v>
@@ -16594,7 +16597,7 @@
         <v>593</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>366</v>
@@ -16657,7 +16660,7 @@
         <v>593</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>367</v>
@@ -17035,7 +17038,7 @@
         <v>593</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>362</v>
@@ -17098,7 +17101,7 @@
         <v>593</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>364</v>
@@ -17161,7 +17164,7 @@
         <v>593</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>365</v>
@@ -17224,7 +17227,7 @@
         <v>593</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>366</v>
@@ -17287,7 +17290,7 @@
         <v>593</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>367</v>
@@ -17350,7 +17353,7 @@
         <v>593</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>362</v>
@@ -17413,7 +17416,7 @@
         <v>593</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>364</v>
@@ -17476,7 +17479,7 @@
         <v>593</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>365</v>
@@ -17539,7 +17542,7 @@
         <v>593</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>366</v>
@@ -17602,7 +17605,7 @@
         <v>593</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>367</v>
@@ -17980,7 +17983,7 @@
         <v>593</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>362</v>
@@ -18043,7 +18046,7 @@
         <v>593</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>364</v>
@@ -18106,7 +18109,7 @@
         <v>593</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>365</v>
@@ -18169,7 +18172,7 @@
         <v>593</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>366</v>
@@ -18232,7 +18235,7 @@
         <v>593</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>367</v>
@@ -18295,7 +18298,7 @@
         <v>593</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>362</v>
@@ -18358,7 +18361,7 @@
         <v>593</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>364</v>
@@ -18421,7 +18424,7 @@
         <v>593</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>365</v>
@@ -18484,7 +18487,7 @@
         <v>593</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>366</v>
@@ -18547,7 +18550,7 @@
         <v>593</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>367</v>
@@ -18610,7 +18613,7 @@
         <v>593</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>362</v>
@@ -18673,7 +18676,7 @@
         <v>593</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>364</v>
@@ -18736,7 +18739,7 @@
         <v>593</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>365</v>
@@ -18799,7 +18802,7 @@
         <v>593</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>366</v>
@@ -18862,7 +18865,7 @@
         <v>593</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>367</v>
@@ -20167,7 +20170,7 @@
       </c>
       <c r="M271" s="2"/>
       <c r="N271" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="O271" s="2" t="s">
         <v>508</v>
@@ -20329,7 +20332,7 @@
         <v>598</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>122</v>
@@ -20392,7 +20395,7 @@
         <v>598</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>124</v>
@@ -20455,7 +20458,7 @@
         <v>598</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>125</v>
@@ -20533,7 +20536,7 @@
       </c>
       <c r="M277" s="2"/>
       <c r="N277" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="O277" s="2" t="s">
         <v>508</v>
@@ -20872,7 +20875,7 @@
         <v>592</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>122</v>
@@ -20935,7 +20938,7 @@
         <v>592</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>124</v>
@@ -20998,7 +21001,7 @@
         <v>592</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>125</v>
@@ -21194,7 +21197,7 @@
       </c>
       <c r="M288" s="2"/>
       <c r="N288" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="O288" s="2" t="s">
         <v>508</v>
@@ -22001,7 +22004,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>122</v>
@@ -22020,7 +22023,7 @@
       </c>
       <c r="M302" s="2"/>
       <c r="N302" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="O302" s="2" t="s">
         <v>15</v>
@@ -22060,7 +22063,7 @@
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>124</v>
@@ -22079,7 +22082,7 @@
       </c>
       <c r="M303" s="2"/>
       <c r="N303" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="O303" s="2" t="s">
         <v>15</v>
@@ -22119,7 +22122,7 @@
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>122</v>
@@ -22138,7 +22141,7 @@
       </c>
       <c r="M304" s="2"/>
       <c r="N304" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O304" s="2" t="s">
         <v>15</v>
@@ -22178,7 +22181,7 @@
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>124</v>
@@ -22197,7 +22200,7 @@
       </c>
       <c r="M305" s="2"/>
       <c r="N305" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O305" s="2" t="s">
         <v>15</v>
@@ -22241,7 +22244,7 @@
         <v>602</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>384</v>
@@ -22304,7 +22307,7 @@
         <v>602</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>386</v>
@@ -22367,7 +22370,7 @@
         <v>602</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>387</v>
@@ -22430,7 +22433,7 @@
         <v>602</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>388</v>
@@ -22493,7 +22496,7 @@
         <v>602</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>529</v>
@@ -22867,7 +22870,7 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>36</v>
@@ -22926,7 +22929,7 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>38</v>
@@ -22985,7 +22988,7 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>39</v>
@@ -23044,7 +23047,7 @@
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
       <c r="G319" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>40</v>
@@ -23103,7 +23106,7 @@
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
       <c r="G320" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>41</v>
@@ -23162,7 +23165,7 @@
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>125</v>
@@ -23225,7 +23228,7 @@
         <v>603</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>122</v>
@@ -23288,7 +23291,7 @@
         <v>603</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>124</v>
@@ -23636,7 +23639,7 @@
         <v>604</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>13</v>
@@ -23699,7 +23702,7 @@
         <v>604</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>16</v>
@@ -23762,7 +23765,7 @@
         <v>604</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>17</v>
@@ -23825,7 +23828,7 @@
         <v>604</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>13</v>
@@ -23888,7 +23891,7 @@
         <v>604</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>16</v>
@@ -23951,7 +23954,7 @@
         <v>604</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>17</v>
@@ -24014,7 +24017,7 @@
         <v>604</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H335" s="2" t="s">
         <v>13</v>
@@ -24077,7 +24080,7 @@
         <v>604</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H336" s="2" t="s">
         <v>16</v>
@@ -24140,7 +24143,7 @@
         <v>604</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H337" s="2" t="s">
         <v>17</v>
@@ -24600,7 +24603,7 @@
         <v>578</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H345" s="2" t="s">
         <v>36</v>
@@ -24663,7 +24666,7 @@
         <v>578</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H346" s="2" t="s">
         <v>38</v>
@@ -24726,7 +24729,7 @@
         <v>578</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H347" s="2" t="s">
         <v>39</v>
@@ -24789,7 +24792,7 @@
         <v>578</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H348" s="2" t="s">
         <v>40</v>
@@ -24852,7 +24855,7 @@
         <v>578</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H349" s="2" t="s">
         <v>41</v>
@@ -24915,7 +24918,7 @@
         <v>578</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H350" s="2" t="s">
         <v>125</v>
@@ -24978,7 +24981,7 @@
         <v>578</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H351" s="2" t="s">
         <v>36</v>
@@ -25041,7 +25044,7 @@
         <v>578</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H352" s="2" t="s">
         <v>38</v>
@@ -25104,7 +25107,7 @@
         <v>578</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H353" s="2" t="s">
         <v>39</v>
@@ -25167,7 +25170,7 @@
         <v>578</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H354" s="2" t="s">
         <v>40</v>
@@ -25230,7 +25233,7 @@
         <v>578</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H355" s="2" t="s">
         <v>41</v>
@@ -25293,7 +25296,7 @@
         <v>578</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H356" s="2" t="s">
         <v>125</v>
@@ -25356,7 +25359,7 @@
         <v>605</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H357" s="2" t="s">
         <v>21</v>
@@ -25419,7 +25422,7 @@
         <v>605</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H358" s="2" t="s">
         <v>23</v>
@@ -25482,7 +25485,7 @@
         <v>605</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H359" s="2" t="s">
         <v>24</v>
@@ -25545,7 +25548,7 @@
         <v>605</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H360" s="2" t="s">
         <v>25</v>
@@ -25608,7 +25611,7 @@
         <v>605</v>
       </c>
       <c r="G361" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H361" s="2" t="s">
         <v>21</v>
@@ -25671,7 +25674,7 @@
         <v>605</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H362" s="2" t="s">
         <v>23</v>
@@ -25734,7 +25737,7 @@
         <v>605</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H363" s="2" t="s">
         <v>24</v>
@@ -25797,7 +25800,7 @@
         <v>605</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>25</v>
@@ -25856,7 +25859,7 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H365" s="2" t="s">
         <v>55</v>
@@ -25915,7 +25918,7 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H366" s="2" t="s">
         <v>56</v>
@@ -25974,7 +25977,7 @@
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
       <c r="G367" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H367" s="2" t="s">
         <v>57</v>
@@ -26033,7 +26036,7 @@
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
       <c r="G368" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H368" s="2" t="s">
         <v>58</v>
@@ -26092,7 +26095,7 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H369" s="2" t="s">
         <v>59</v>
@@ -26308,7 +26311,7 @@
         <v>513</v>
       </c>
       <c r="R372" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S372" s="9">
         <v>44927</v>
@@ -26367,7 +26370,7 @@
         <v>513</v>
       </c>
       <c r="R373" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S373" s="9">
         <v>44927</v>
@@ -26426,7 +26429,7 @@
         <v>513</v>
       </c>
       <c r="R374" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S374" s="9">
         <v>44927</v>
@@ -26485,7 +26488,7 @@
         <v>513</v>
       </c>
       <c r="R375" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S375" s="9">
         <v>44927</v>
@@ -26544,7 +26547,7 @@
         <v>513</v>
       </c>
       <c r="R376" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S376" s="9">
         <v>44927</v>
@@ -26603,7 +26606,7 @@
         <v>513</v>
       </c>
       <c r="R377" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S377" s="9">
         <v>44927</v>
@@ -26662,7 +26665,7 @@
         <v>513</v>
       </c>
       <c r="R378" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S378" s="9">
         <v>44927</v>
@@ -26721,7 +26724,7 @@
         <v>513</v>
       </c>
       <c r="R379" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S379" s="9">
         <v>44927</v>
@@ -26780,7 +26783,7 @@
         <v>513</v>
       </c>
       <c r="R380" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S380" s="9">
         <v>44927</v>
@@ -26839,7 +26842,7 @@
         <v>513</v>
       </c>
       <c r="R381" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S381" s="9">
         <v>44927</v>
@@ -26898,7 +26901,7 @@
         <v>513</v>
       </c>
       <c r="R382" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S382" s="9">
         <v>44927</v>
@@ -26957,7 +26960,7 @@
         <v>513</v>
       </c>
       <c r="R383" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S383" s="9">
         <v>44927</v>
@@ -27016,7 +27019,7 @@
         <v>513</v>
       </c>
       <c r="R384" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="S384" s="9">
         <v>44927</v>
@@ -27046,7 +27049,7 @@
         <v>590</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H385" s="2" t="s">
         <v>36</v>
@@ -27107,7 +27110,7 @@
         <v>590</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H386" s="2" t="s">
         <v>38</v>
@@ -27168,7 +27171,7 @@
         <v>590</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H387" s="2" t="s">
         <v>39</v>
@@ -27229,7 +27232,7 @@
         <v>590</v>
       </c>
       <c r="G388" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H388" s="2" t="s">
         <v>40</v>
@@ -27290,7 +27293,7 @@
         <v>590</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H389" s="2" t="s">
         <v>41</v>
@@ -27353,7 +27356,7 @@
         <v>590</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H390" s="2" t="s">
         <v>36</v>
@@ -27416,7 +27419,7 @@
         <v>590</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H391" s="2" t="s">
         <v>38</v>
@@ -27479,7 +27482,7 @@
         <v>590</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H392" s="2" t="s">
         <v>39</v>
@@ -27542,7 +27545,7 @@
         <v>590</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H393" s="2" t="s">
         <v>40</v>
@@ -27605,7 +27608,7 @@
         <v>590</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H394" s="2" t="s">
         <v>41</v>
@@ -27668,7 +27671,7 @@
         <v>590</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H395" s="2" t="s">
         <v>36</v>
@@ -27731,7 +27734,7 @@
         <v>590</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H396" s="2" t="s">
         <v>38</v>
@@ -27794,7 +27797,7 @@
         <v>590</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H397" s="2" t="s">
         <v>39</v>
@@ -27857,7 +27860,7 @@
         <v>590</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H398" s="2" t="s">
         <v>40</v>
@@ -27920,7 +27923,7 @@
         <v>590</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H399" s="2" t="s">
         <v>41</v>
@@ -27981,7 +27984,7 @@
         <v>590</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H400" s="2" t="s">
         <v>36</v>
@@ -28042,7 +28045,7 @@
         <v>590</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H401" s="2" t="s">
         <v>38</v>
@@ -28103,7 +28106,7 @@
         <v>590</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H402" s="2" t="s">
         <v>39</v>
@@ -28164,7 +28167,7 @@
         <v>590</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H403" s="2" t="s">
         <v>40</v>
@@ -28225,7 +28228,7 @@
         <v>590</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H404" s="2" t="s">
         <v>41</v>
@@ -28671,7 +28674,7 @@
       </c>
       <c r="M411" s="2"/>
       <c r="N411" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="O411" s="2" t="s">
         <v>508</v>
@@ -28732,7 +28735,7 @@
       </c>
       <c r="M412" s="2"/>
       <c r="N412" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="O412" s="2" t="s">
         <v>508</v>
@@ -28793,7 +28796,7 @@
       </c>
       <c r="M413" s="2"/>
       <c r="N413" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="O413" s="2" t="s">
         <v>508</v>
@@ -28854,7 +28857,7 @@
       </c>
       <c r="M414" s="2"/>
       <c r="N414" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="O414" s="2" t="s">
         <v>508</v>
@@ -28915,7 +28918,7 @@
       </c>
       <c r="M415" s="2"/>
       <c r="N415" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="O415" s="2" t="s">
         <v>508</v>
@@ -28976,7 +28979,7 @@
       </c>
       <c r="M416" s="2"/>
       <c r="N416" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="O416" s="2" t="s">
         <v>508</v>
@@ -29769,7 +29772,7 @@
       </c>
       <c r="M429" s="2"/>
       <c r="N429" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="O429" s="2" t="s">
         <v>508</v>
@@ -29830,7 +29833,7 @@
       </c>
       <c r="M430" s="2"/>
       <c r="N430" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="O430" s="2" t="s">
         <v>508</v>
@@ -29891,7 +29894,7 @@
       </c>
       <c r="M431" s="2"/>
       <c r="N431" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="O431" s="2" t="s">
         <v>508</v>
@@ -29952,7 +29955,7 @@
       </c>
       <c r="M432" s="2"/>
       <c r="N432" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="O432" s="2" t="s">
         <v>508</v>
@@ -30013,7 +30016,7 @@
       </c>
       <c r="M433" s="2"/>
       <c r="N433" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="O433" s="2" t="s">
         <v>508</v>
@@ -30074,7 +30077,7 @@
       </c>
       <c r="M434" s="2"/>
       <c r="N434" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="O434" s="2" t="s">
         <v>508</v>
@@ -32672,7 +32675,7 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H479" s="2" t="s">
         <v>245</v>
@@ -32727,7 +32730,7 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H480" s="2" t="s">
         <v>247</v>
@@ -32782,7 +32785,7 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H481" s="2" t="s">
         <v>249</v>
@@ -32837,7 +32840,7 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H482" s="2" t="s">
         <v>251</v>
@@ -32892,7 +32895,7 @@
       <c r="E483" s="2"/>
       <c r="F483" s="2"/>
       <c r="G483" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H483" s="2" t="s">
         <v>253</v>
@@ -32947,7 +32950,7 @@
       <c r="E484" s="2"/>
       <c r="F484" s="2"/>
       <c r="G484" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H484" s="2" t="s">
         <v>255</v>
@@ -33002,7 +33005,7 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H485" s="2" t="s">
         <v>257</v>
@@ -33973,7 +33976,7 @@
         <v>612</v>
       </c>
       <c r="G502" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H502" s="2" t="s">
         <v>287</v>
@@ -34034,7 +34037,7 @@
         <v>612</v>
       </c>
       <c r="G503" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H503" s="2" t="s">
         <v>289</v>
@@ -34095,7 +34098,7 @@
         <v>612</v>
       </c>
       <c r="G504" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H504" s="2" t="s">
         <v>290</v>
@@ -34156,7 +34159,7 @@
         <v>612</v>
       </c>
       <c r="G505" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H505" s="2" t="s">
         <v>291</v>
@@ -34217,7 +34220,7 @@
         <v>612</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H506" s="2" t="s">
         <v>292</v>
@@ -34278,7 +34281,7 @@
         <v>612</v>
       </c>
       <c r="G507" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H507" s="2" t="s">
         <v>287</v>
@@ -34339,7 +34342,7 @@
         <v>612</v>
       </c>
       <c r="G508" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H508" s="2" t="s">
         <v>289</v>
@@ -34400,7 +34403,7 @@
         <v>612</v>
       </c>
       <c r="G509" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H509" s="2" t="s">
         <v>290</v>
@@ -34461,7 +34464,7 @@
         <v>612</v>
       </c>
       <c r="G510" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H510" s="2" t="s">
         <v>291</v>
@@ -34522,7 +34525,7 @@
         <v>612</v>
       </c>
       <c r="G511" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H511" s="2" t="s">
         <v>292</v>
@@ -34583,7 +34586,7 @@
         <v>612</v>
       </c>
       <c r="G512" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H512" s="2" t="s">
         <v>287</v>
@@ -34644,7 +34647,7 @@
         <v>612</v>
       </c>
       <c r="G513" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H513" s="2" t="s">
         <v>289</v>
@@ -34705,7 +34708,7 @@
         <v>612</v>
       </c>
       <c r="G514" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H514" s="2" t="s">
         <v>290</v>
@@ -34766,7 +34769,7 @@
         <v>612</v>
       </c>
       <c r="G515" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H515" s="2" t="s">
         <v>291</v>
@@ -34827,7 +34830,7 @@
         <v>612</v>
       </c>
       <c r="G516" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H516" s="2" t="s">
         <v>292</v>
@@ -34888,7 +34891,7 @@
         <v>612</v>
       </c>
       <c r="G517" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H517" s="2" t="s">
         <v>287</v>
@@ -34949,7 +34952,7 @@
         <v>612</v>
       </c>
       <c r="G518" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H518" s="2" t="s">
         <v>289</v>
@@ -35010,7 +35013,7 @@
         <v>612</v>
       </c>
       <c r="G519" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H519" s="2" t="s">
         <v>290</v>
@@ -35071,7 +35074,7 @@
         <v>612</v>
       </c>
       <c r="G520" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H520" s="2" t="s">
         <v>291</v>
@@ -35132,7 +35135,7 @@
         <v>612</v>
       </c>
       <c r="G521" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H521" s="2" t="s">
         <v>292</v>
@@ -35193,7 +35196,7 @@
         <v>612</v>
       </c>
       <c r="G522" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H522" s="2" t="s">
         <v>287</v>
@@ -35254,7 +35257,7 @@
         <v>612</v>
       </c>
       <c r="G523" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H523" s="2" t="s">
         <v>289</v>
@@ -35315,7 +35318,7 @@
         <v>612</v>
       </c>
       <c r="G524" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H524" s="2" t="s">
         <v>290</v>
@@ -35376,7 +35379,7 @@
         <v>612</v>
       </c>
       <c r="G525" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H525" s="2" t="s">
         <v>291</v>
@@ -35437,7 +35440,7 @@
         <v>612</v>
       </c>
       <c r="G526" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H526" s="2" t="s">
         <v>292</v>
@@ -35498,7 +35501,7 @@
         <v>612</v>
       </c>
       <c r="G527" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H527" s="2" t="s">
         <v>287</v>
@@ -35559,7 +35562,7 @@
         <v>612</v>
       </c>
       <c r="G528" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H528" s="2" t="s">
         <v>289</v>
@@ -35620,7 +35623,7 @@
         <v>612</v>
       </c>
       <c r="G529" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H529" s="2" t="s">
         <v>290</v>
@@ -35681,7 +35684,7 @@
         <v>612</v>
       </c>
       <c r="G530" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H530" s="2" t="s">
         <v>291</v>
@@ -35742,7 +35745,7 @@
         <v>612</v>
       </c>
       <c r="G531" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H531" s="2" t="s">
         <v>292</v>
@@ -35803,7 +35806,7 @@
         <v>612</v>
       </c>
       <c r="G532" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H532" s="2" t="s">
         <v>287</v>
@@ -35864,7 +35867,7 @@
         <v>612</v>
       </c>
       <c r="G533" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H533" s="2" t="s">
         <v>289</v>
@@ -35925,7 +35928,7 @@
         <v>612</v>
       </c>
       <c r="G534" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H534" s="2" t="s">
         <v>290</v>
@@ -35986,7 +35989,7 @@
         <v>612</v>
       </c>
       <c r="G535" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H535" s="2" t="s">
         <v>291</v>
@@ -36047,7 +36050,7 @@
         <v>612</v>
       </c>
       <c r="G536" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H536" s="2" t="s">
         <v>292</v>
@@ -36108,7 +36111,7 @@
         <v>612</v>
       </c>
       <c r="G537" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H537" s="2" t="s">
         <v>287</v>
@@ -36169,7 +36172,7 @@
         <v>612</v>
       </c>
       <c r="G538" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H538" s="2" t="s">
         <v>289</v>
@@ -36230,7 +36233,7 @@
         <v>612</v>
       </c>
       <c r="G539" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H539" s="2" t="s">
         <v>290</v>
@@ -36291,7 +36294,7 @@
         <v>612</v>
       </c>
       <c r="G540" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H540" s="2" t="s">
         <v>291</v>
@@ -36352,7 +36355,7 @@
         <v>612</v>
       </c>
       <c r="G541" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H541" s="2" t="s">
         <v>292</v>
@@ -36413,7 +36416,7 @@
         <v>612</v>
       </c>
       <c r="G542" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H542" s="2" t="s">
         <v>287</v>
@@ -36474,7 +36477,7 @@
         <v>612</v>
       </c>
       <c r="G543" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H543" s="2" t="s">
         <v>289</v>
@@ -36535,7 +36538,7 @@
         <v>612</v>
       </c>
       <c r="G544" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H544" s="2" t="s">
         <v>290</v>
@@ -36596,7 +36599,7 @@
         <v>612</v>
       </c>
       <c r="G545" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H545" s="2" t="s">
         <v>291</v>
@@ -36657,7 +36660,7 @@
         <v>612</v>
       </c>
       <c r="G546" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H546" s="2" t="s">
         <v>292</v>
@@ -36718,7 +36721,7 @@
         <v>612</v>
       </c>
       <c r="G547" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H547" s="2" t="s">
         <v>287</v>
@@ -36779,7 +36782,7 @@
         <v>612</v>
       </c>
       <c r="G548" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H548" s="2" t="s">
         <v>289</v>
@@ -36840,7 +36843,7 @@
         <v>612</v>
       </c>
       <c r="G549" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H549" s="2" t="s">
         <v>290</v>
@@ -36901,7 +36904,7 @@
         <v>612</v>
       </c>
       <c r="G550" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H550" s="2" t="s">
         <v>291</v>
@@ -36962,7 +36965,7 @@
         <v>612</v>
       </c>
       <c r="G551" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H551" s="2" t="s">
         <v>292</v>
@@ -37023,7 +37026,7 @@
         <v>612</v>
       </c>
       <c r="G552" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H552" s="2" t="s">
         <v>287</v>
@@ -37084,7 +37087,7 @@
         <v>612</v>
       </c>
       <c r="G553" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H553" s="2" t="s">
         <v>289</v>
@@ -37145,7 +37148,7 @@
         <v>612</v>
       </c>
       <c r="G554" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H554" s="2" t="s">
         <v>290</v>
@@ -37206,7 +37209,7 @@
         <v>612</v>
       </c>
       <c r="G555" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H555" s="2" t="s">
         <v>291</v>
@@ -37267,7 +37270,7 @@
         <v>612</v>
       </c>
       <c r="G556" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H556" s="2" t="s">
         <v>292</v>
@@ -37477,7 +37480,7 @@
         <v>591</v>
       </c>
       <c r="G560" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H560" s="2" t="s">
         <v>125</v>
@@ -37540,7 +37543,7 @@
         <v>591</v>
       </c>
       <c r="G561" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H561" s="2" t="s">
         <v>122</v>
@@ -37603,7 +37606,7 @@
         <v>591</v>
       </c>
       <c r="G562" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H562" s="2" t="s">
         <v>124</v>
@@ -37664,7 +37667,7 @@
         <v>591</v>
       </c>
       <c r="G563" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H563" s="2" t="s">
         <v>125</v>
@@ -37725,7 +37728,7 @@
         <v>591</v>
       </c>
       <c r="G564" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H564" s="2" t="s">
         <v>122</v>
@@ -37786,7 +37789,7 @@
         <v>591</v>
       </c>
       <c r="G565" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H565" s="2" t="s">
         <v>124</v>
@@ -38038,7 +38041,7 @@
         <v>598</v>
       </c>
       <c r="G569" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H569" s="2" t="s">
         <v>122</v>
@@ -38101,7 +38104,7 @@
         <v>598</v>
       </c>
       <c r="G570" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H570" s="2" t="s">
         <v>124</v>
@@ -38164,7 +38167,7 @@
         <v>598</v>
       </c>
       <c r="G571" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H571" s="2" t="s">
         <v>125</v>
@@ -38461,7 +38464,7 @@
       <c r="E576" s="2"/>
       <c r="F576" s="2"/>
       <c r="G576" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H576" s="2" t="s">
         <v>404</v>
@@ -38520,7 +38523,7 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H577" s="2" t="s">
         <v>405</v>
@@ -38579,7 +38582,7 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H578" s="2" t="s">
         <v>406</v>
@@ -38638,7 +38641,7 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H579" s="2" t="s">
         <v>407</v>
@@ -38697,7 +38700,7 @@
       <c r="E580" s="2"/>
       <c r="F580" s="2"/>
       <c r="G580" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H580" s="2" t="s">
         <v>408</v>
@@ -38756,7 +38759,7 @@
       <c r="E581" s="2"/>
       <c r="F581" s="2"/>
       <c r="G581" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H581" s="2" t="s">
         <v>409</v>
@@ -38815,7 +38818,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H582" s="2" t="s">
         <v>410</v>
@@ -38874,7 +38877,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H583" s="2" t="s">
         <v>411</v>
@@ -38933,7 +38936,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H584" s="2" t="s">
         <v>412</v>
@@ -39416,7 +39419,7 @@
       </c>
       <c r="M592" s="2"/>
       <c r="N592" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="O592" s="2" t="s">
         <v>508</v>
@@ -40680,7 +40683,7 @@
         <v>584</v>
       </c>
       <c r="G615" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H615" s="2" t="s">
         <v>462</v>
@@ -40743,7 +40746,7 @@
         <v>584</v>
       </c>
       <c r="G616" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H616" s="2" t="s">
         <v>464</v>
@@ -40806,7 +40809,7 @@
         <v>584</v>
       </c>
       <c r="G617" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H617" s="2" t="s">
         <v>465</v>
@@ -40869,7 +40872,7 @@
         <v>584</v>
       </c>
       <c r="G618" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H618" s="2" t="s">
         <v>466</v>
@@ -40932,7 +40935,7 @@
         <v>584</v>
       </c>
       <c r="G619" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H619" s="2" t="s">
         <v>467</v>
@@ -42180,7 +42183,7 @@
       <c r="E641" s="2"/>
       <c r="F641" s="2"/>
       <c r="G641" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H641" s="2" t="s">
         <v>122</v>
@@ -42237,7 +42240,7 @@
       <c r="E642" s="2"/>
       <c r="F642" s="2"/>
       <c r="G642" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H642" s="2" t="s">
         <v>124</v>
@@ -42296,7 +42299,7 @@
       <c r="E643" s="2"/>
       <c r="F643" s="2"/>
       <c r="G643" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H643" s="2" t="s">
         <v>207</v>
@@ -42355,7 +42358,7 @@
       <c r="E644" s="2"/>
       <c r="F644" s="2"/>
       <c r="G644" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H644" s="2" t="s">
         <v>208</v>
@@ -42414,7 +42417,7 @@
       <c r="E645" s="2"/>
       <c r="F645" s="2"/>
       <c r="G645" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H645" s="2" t="s">
         <v>527</v>
@@ -42473,7 +42476,7 @@
       <c r="E646" s="2"/>
       <c r="F646" s="2"/>
       <c r="G646" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>209</v>
@@ -42532,7 +42535,7 @@
       <c r="E647" s="2"/>
       <c r="F647" s="2"/>
       <c r="G647" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H647" s="2" t="s">
         <v>210</v>
@@ -42591,7 +42594,7 @@
       <c r="E648" s="2"/>
       <c r="F648" s="2"/>
       <c r="G648" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H648" s="2" t="s">
         <v>211</v>
@@ -42648,7 +42651,7 @@
       <c r="E649" s="2"/>
       <c r="F649" s="2"/>
       <c r="G649" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H649" s="7" t="s">
         <v>124</v>
@@ -42703,7 +42706,7 @@
       <c r="E650" s="2"/>
       <c r="F650" s="2"/>
       <c r="G650" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H650" s="7" t="s">
         <v>122</v>
@@ -42760,7 +42763,7 @@
       <c r="E651" s="2"/>
       <c r="F651" s="2"/>
       <c r="G651" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H651" s="7" t="s">
         <v>124</v>
@@ -42817,7 +42820,7 @@
       <c r="E652" s="2"/>
       <c r="F652" s="2"/>
       <c r="G652" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H652" s="7" t="s">
         <v>122</v>
@@ -42899,7 +42902,7 @@
         <v>508</v>
       </c>
       <c r="P653" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q653" s="2"/>
       <c r="R653" s="2" t="s">
@@ -42956,7 +42959,7 @@
         <v>508</v>
       </c>
       <c r="P654" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q654" s="2"/>
       <c r="R654" s="2" t="s">
@@ -43013,7 +43016,7 @@
         <v>508</v>
       </c>
       <c r="P655" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q655" s="2"/>
       <c r="R655" s="2" t="s">
@@ -43070,7 +43073,7 @@
         <v>508</v>
       </c>
       <c r="P656" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q656" s="2"/>
       <c r="R656" s="2" t="s">
@@ -43127,7 +43130,7 @@
         <v>508</v>
       </c>
       <c r="P657" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q657" s="2"/>
       <c r="R657" s="2" t="s">
@@ -43184,7 +43187,7 @@
         <v>508</v>
       </c>
       <c r="P658" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q658" s="2"/>
       <c r="R658" s="2" t="s">
@@ -43241,7 +43244,7 @@
         <v>508</v>
       </c>
       <c r="P659" s="2" t="s">
-        <v>520</v>
+        <v>742</v>
       </c>
       <c r="Q659" s="2"/>
       <c r="R659" s="2" t="s">
@@ -43277,7 +43280,7 @@
         <v>620</v>
       </c>
       <c r="G660" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H660" s="2" t="s">
         <v>547</v>
@@ -43338,7 +43341,7 @@
         <v>620</v>
       </c>
       <c r="G661" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H661" s="2" t="s">
         <v>546</v>
@@ -43399,7 +43402,7 @@
         <v>620</v>
       </c>
       <c r="G662" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H662" s="2" t="s">
         <v>545</v>
@@ -43460,7 +43463,7 @@
         <v>620</v>
       </c>
       <c r="G663" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H663" s="2" t="s">
         <v>544</v>
@@ -43521,7 +43524,7 @@
         <v>620</v>
       </c>
       <c r="G664" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H664" s="2" t="s">
         <v>543</v>
@@ -43582,7 +43585,7 @@
         <v>620</v>
       </c>
       <c r="G665" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H665" s="2" t="s">
         <v>547</v>
@@ -43643,7 +43646,7 @@
         <v>620</v>
       </c>
       <c r="G666" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H666" s="2" t="s">
         <v>546</v>
@@ -43704,7 +43707,7 @@
         <v>620</v>
       </c>
       <c r="G667" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H667" s="2" t="s">
         <v>545</v>
@@ -43765,7 +43768,7 @@
         <v>620</v>
       </c>
       <c r="G668" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H668" s="2" t="s">
         <v>544</v>
@@ -43826,7 +43829,7 @@
         <v>620</v>
       </c>
       <c r="G669" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H669" s="2" t="s">
         <v>543</v>
@@ -43887,7 +43890,7 @@
         <v>620</v>
       </c>
       <c r="G670" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H670" s="2" t="s">
         <v>547</v>
@@ -43948,7 +43951,7 @@
         <v>620</v>
       </c>
       <c r="G671" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H671" s="2" t="s">
         <v>546</v>
@@ -44009,7 +44012,7 @@
         <v>620</v>
       </c>
       <c r="G672" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H672" s="2" t="s">
         <v>545</v>
@@ -44070,7 +44073,7 @@
         <v>620</v>
       </c>
       <c r="G673" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H673" s="2" t="s">
         <v>544</v>
@@ -44131,7 +44134,7 @@
         <v>620</v>
       </c>
       <c r="G674" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H674" s="2" t="s">
         <v>543</v>
@@ -44192,7 +44195,7 @@
         <v>620</v>
       </c>
       <c r="G675" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H675" s="2" t="s">
         <v>547</v>
@@ -44253,7 +44256,7 @@
         <v>620</v>
       </c>
       <c r="G676" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H676" s="2" t="s">
         <v>546</v>
@@ -44314,7 +44317,7 @@
         <v>620</v>
       </c>
       <c r="G677" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H677" s="2" t="s">
         <v>545</v>
@@ -44375,7 +44378,7 @@
         <v>620</v>
       </c>
       <c r="G678" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H678" s="2" t="s">
         <v>544</v>
@@ -44436,7 +44439,7 @@
         <v>620</v>
       </c>
       <c r="G679" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H679" s="2" t="s">
         <v>543</v>
@@ -44497,7 +44500,7 @@
         <v>620</v>
       </c>
       <c r="G680" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H680" s="2" t="s">
         <v>547</v>
@@ -44558,7 +44561,7 @@
         <v>620</v>
       </c>
       <c r="G681" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H681" s="2" t="s">
         <v>546</v>
@@ -44619,7 +44622,7 @@
         <v>620</v>
       </c>
       <c r="G682" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H682" s="2" t="s">
         <v>545</v>
@@ -44680,7 +44683,7 @@
         <v>620</v>
       </c>
       <c r="G683" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H683" s="2" t="s">
         <v>544</v>
@@ -44741,7 +44744,7 @@
         <v>620</v>
       </c>
       <c r="G684" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H684" s="2" t="s">
         <v>543</v>
@@ -44800,7 +44803,7 @@
         <v>621</v>
       </c>
       <c r="G685" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H685" s="2" t="s">
         <v>549</v>
@@ -44859,7 +44862,7 @@
         <v>621</v>
       </c>
       <c r="G686" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H686" s="2" t="s">
         <v>287</v>
@@ -44918,7 +44921,7 @@
         <v>621</v>
       </c>
       <c r="G687" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H687" s="2" t="s">
         <v>289</v>
@@ -44977,7 +44980,7 @@
         <v>621</v>
       </c>
       <c r="G688" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H688" s="2" t="s">
         <v>550</v>
@@ -45036,7 +45039,7 @@
         <v>621</v>
       </c>
       <c r="G689" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H689" s="2" t="s">
         <v>551</v>
@@ -45095,7 +45098,7 @@
         <v>621</v>
       </c>
       <c r="G690" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H690" s="2" t="s">
         <v>549</v>
@@ -45154,7 +45157,7 @@
         <v>621</v>
       </c>
       <c r="G691" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H691" s="2" t="s">
         <v>287</v>
@@ -45213,7 +45216,7 @@
         <v>621</v>
       </c>
       <c r="G692" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H692" s="2" t="s">
         <v>289</v>
@@ -45272,7 +45275,7 @@
         <v>621</v>
       </c>
       <c r="G693" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H693" s="2" t="s">
         <v>550</v>
@@ -45331,7 +45334,7 @@
         <v>621</v>
       </c>
       <c r="G694" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H694" s="2" t="s">
         <v>551</v>
@@ -45390,7 +45393,7 @@
         <v>621</v>
       </c>
       <c r="G695" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H695" s="2" t="s">
         <v>549</v>
@@ -45449,7 +45452,7 @@
         <v>621</v>
       </c>
       <c r="G696" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H696" s="2" t="s">
         <v>287</v>
@@ -45508,7 +45511,7 @@
         <v>621</v>
       </c>
       <c r="G697" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H697" s="2" t="s">
         <v>289</v>
@@ -45567,7 +45570,7 @@
         <v>621</v>
       </c>
       <c r="G698" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H698" s="2" t="s">
         <v>550</v>
@@ -45626,7 +45629,7 @@
         <v>621</v>
       </c>
       <c r="G699" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H699" s="2" t="s">
         <v>551</v>
@@ -45685,7 +45688,7 @@
         <v>621</v>
       </c>
       <c r="G700" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H700" s="2" t="s">
         <v>549</v>
@@ -45744,7 +45747,7 @@
         <v>621</v>
       </c>
       <c r="G701" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H701" s="2" t="s">
         <v>287</v>
@@ -45803,7 +45806,7 @@
         <v>621</v>
       </c>
       <c r="G702" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H702" s="2" t="s">
         <v>289</v>
@@ -45862,7 +45865,7 @@
         <v>621</v>
       </c>
       <c r="G703" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H703" s="2" t="s">
         <v>550</v>
@@ -45921,7 +45924,7 @@
         <v>621</v>
       </c>
       <c r="G704" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H704" s="2" t="s">
         <v>551</v>
@@ -45980,7 +45983,7 @@
         <v>621</v>
       </c>
       <c r="G705" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H705" s="2" t="s">
         <v>549</v>
@@ -46039,7 +46042,7 @@
         <v>621</v>
       </c>
       <c r="G706" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H706" s="2" t="s">
         <v>287</v>
@@ -46098,7 +46101,7 @@
         <v>621</v>
       </c>
       <c r="G707" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H707" s="2" t="s">
         <v>289</v>
@@ -46157,7 +46160,7 @@
         <v>621</v>
       </c>
       <c r="G708" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H708" s="2" t="s">
         <v>550</v>
@@ -46216,7 +46219,7 @@
         <v>621</v>
       </c>
       <c r="G709" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H709" s="2" t="s">
         <v>551</v>
@@ -46275,7 +46278,7 @@
         <v>622</v>
       </c>
       <c r="G710" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H710" s="2" t="s">
         <v>528</v>
@@ -46334,7 +46337,7 @@
         <v>622</v>
       </c>
       <c r="G711" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H711" s="2" t="s">
         <v>25</v>
@@ -46393,7 +46396,7 @@
         <v>622</v>
       </c>
       <c r="G712" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H712" s="2" t="s">
         <v>24</v>
@@ -46452,7 +46455,7 @@
         <v>622</v>
       </c>
       <c r="G713" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H713" s="2" t="s">
         <v>23</v>
@@ -46511,7 +46514,7 @@
         <v>622</v>
       </c>
       <c r="G714" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H714" s="2" t="s">
         <v>21</v>
@@ -46570,7 +46573,7 @@
         <v>622</v>
       </c>
       <c r="G715" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H715" s="2" t="s">
         <v>561</v>
@@ -46629,7 +46632,7 @@
         <v>622</v>
       </c>
       <c r="G716" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H716" s="2" t="s">
         <v>25</v>
@@ -46688,7 +46691,7 @@
         <v>622</v>
       </c>
       <c r="G717" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H717" s="2" t="s">
         <v>24</v>
@@ -46747,7 +46750,7 @@
         <v>622</v>
       </c>
       <c r="G718" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H718" s="2" t="s">
         <v>23</v>
@@ -46806,7 +46809,7 @@
         <v>622</v>
       </c>
       <c r="G719" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H719" s="2" t="s">
         <v>21</v>
@@ -46861,7 +46864,7 @@
       <c r="E720" s="2"/>
       <c r="F720" s="2"/>
       <c r="G720" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H720" s="2" t="s">
         <v>124</v>
@@ -46916,7 +46919,7 @@
       <c r="E721" s="2"/>
       <c r="F721" s="2"/>
       <c r="G721" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H721" s="2" t="s">
         <v>122</v>
@@ -46962,7 +46965,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T642">
     <sortCondition ref="A2:A642"/>
   </sortState>
-  <conditionalFormatting sqref="A1:T1 T1:U721 A2:F305 K2:K721 C306:C721 A493:B721 L651:L684 I653:J653 O653:T684 M654:N684 G660:J721 D661:F721 L685:T721">
+  <conditionalFormatting sqref="A1:T1 A2:F305 K2:K721 C306:C721 A493:B721 L651:L684 I653:J653 M654:N684 G660:J721 D661:F721 L685:T721 T1:U721 O653:T684">
     <cfRule type="expression" dxfId="12" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -47012,12 +47015,12 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 D653:H660 G659:I659">
+  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 L306:P626 S306:T642 D653:H660 G659:I659 Q306:R565">
     <cfRule type="expression" dxfId="2" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652">
+  <conditionalFormatting sqref="L2:T2 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 Q3:T255">
     <cfRule type="expression" dxfId="1" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>

--- a/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
+++ b/nvi_etl/survey/conf/nvi_answer_key_20260316.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mike\2_responsibilities\nvi_etl\nvi_etl\survey\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A26E532-8081-4DF7-B17E-3BF71F1028B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C85B9EAB-8C37-4415-AECD-9DF4836E841E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indicator_main!$A$1:$T$721</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3313,29 +3314,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U721"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="17.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="25.453125" style="3" customWidth="1"/>
+    <col min="1" max="2" width="25.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="29" style="3" customWidth="1"/>
-    <col min="4" max="5" width="34.1796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="52.1796875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="51.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="25.453125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.453125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="25.453125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="52.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="51.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="25.42578125" style="3" customWidth="1"/>
     <col min="14" max="14" width="118" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.453125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="43.81640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="35.81640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="25.453125" style="3" customWidth="1"/>
-    <col min="19" max="20" width="25.453125" style="11" customWidth="1"/>
-    <col min="21" max="21" width="36.36328125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.7265625" style="1"/>
+    <col min="15" max="15" width="25.42578125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="43.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="25.42578125" style="3" customWidth="1"/>
+    <col min="19" max="20" width="25.42578125" style="11" customWidth="1"/>
+    <col min="21" max="21" width="36.42578125" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>511</v>
       </c>
@@ -3400,7 +3402,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3463,7 +3465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3526,7 +3528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3589,7 +3591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -3652,7 +3654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -3715,7 +3717,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -3778,7 +3780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -3841,7 +3843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -3904,7 +3906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>2</v>
       </c>
@@ -3967,7 +3969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -4030,7 +4032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -4093,7 +4095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>2</v>
       </c>
@@ -4156,7 +4158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -4219,7 +4221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -4282,7 +4284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -4345,7 +4347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>3</v>
       </c>
@@ -4408,7 +4410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -4471,7 +4473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>3</v>
       </c>
@@ -4534,7 +4536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -4597,7 +4599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>3</v>
       </c>
@@ -4660,7 +4662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -4723,7 +4725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>3</v>
       </c>
@@ -4786,7 +4788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>3</v>
       </c>
@@ -4849,7 +4851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>3</v>
       </c>
@@ -4912,7 +4914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>3</v>
       </c>
@@ -4975,7 +4977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>3</v>
       </c>
@@ -5038,7 +5040,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>3</v>
       </c>
@@ -5101,7 +5103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>3</v>
       </c>
@@ -5164,7 +5166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>3</v>
       </c>
@@ -5227,7 +5229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>3</v>
       </c>
@@ -5290,7 +5292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>3</v>
       </c>
@@ -5353,7 +5355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>3</v>
       </c>
@@ -5416,7 +5418,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>3</v>
       </c>
@@ -5479,7 +5481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -5542,7 +5544,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>3</v>
       </c>
@@ -5605,7 +5607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>3</v>
       </c>
@@ -5668,7 +5670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>3</v>
       </c>
@@ -5731,7 +5733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>3</v>
       </c>
@@ -5794,7 +5796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>3</v>
       </c>
@@ -5857,7 +5859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>3</v>
       </c>
@@ -5920,7 +5922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -5983,7 +5985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>3</v>
       </c>
@@ -6046,7 +6048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>3</v>
       </c>
@@ -6109,7 +6111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>3</v>
       </c>
@@ -6172,7 +6174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>5</v>
       </c>
@@ -6235,7 +6237,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>5</v>
       </c>
@@ -6298,7 +6300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>5</v>
       </c>
@@ -6361,7 +6363,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>5</v>
       </c>
@@ -6424,7 +6426,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>6</v>
       </c>
@@ -6483,7 +6485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>6</v>
       </c>
@@ -6542,7 +6544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>6</v>
       </c>
@@ -6601,7 +6603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>6</v>
       </c>
@@ -6660,7 +6662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>6</v>
       </c>
@@ -6719,7 +6721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>6</v>
       </c>
@@ -6778,7 +6780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>6</v>
       </c>
@@ -6837,7 +6839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>9</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>9</v>
       </c>
@@ -6955,7 +6957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>9</v>
       </c>
@@ -7014,7 +7016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>9</v>
       </c>
@@ -7073,7 +7075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>9</v>
       </c>
@@ -7132,7 +7134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>16</v>
       </c>
@@ -7191,7 +7193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>16</v>
       </c>
@@ -7250,7 +7252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>18</v>
       </c>
@@ -7313,7 +7315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>18</v>
       </c>
@@ -7376,7 +7378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>18</v>
       </c>
@@ -7439,7 +7441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>18</v>
       </c>
@@ -7502,7 +7504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>19</v>
       </c>
@@ -7565,7 +7567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>19</v>
       </c>
@@ -7628,7 +7630,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>19</v>
       </c>
@@ -7691,7 +7693,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>20</v>
       </c>
@@ -7750,7 +7752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>20</v>
       </c>
@@ -7809,7 +7811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <v>20</v>
       </c>
@@ -7868,7 +7870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>20</v>
       </c>
@@ -7927,7 +7929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <v>20</v>
       </c>
@@ -7986,7 +7988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>22</v>
       </c>
@@ -8049,7 +8051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <v>22</v>
       </c>
@@ -8112,7 +8114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <v>22</v>
       </c>
@@ -8175,7 +8177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <v>22</v>
       </c>
@@ -8238,7 +8240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>22</v>
       </c>
@@ -8301,7 +8303,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <v>23</v>
       </c>
@@ -8364,7 +8366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <v>23</v>
       </c>
@@ -8427,7 +8429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <v>23</v>
       </c>
@@ -8490,7 +8492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <v>23</v>
       </c>
@@ -8553,7 +8555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <v>23</v>
       </c>
@@ -8616,7 +8618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <v>23</v>
       </c>
@@ -8679,7 +8681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <v>25</v>
       </c>
@@ -8742,7 +8744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <v>25</v>
       </c>
@@ -8805,7 +8807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <v>25</v>
       </c>
@@ -8868,7 +8870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <v>25</v>
       </c>
@@ -8931,7 +8933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <v>25</v>
       </c>
@@ -8994,7 +8996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <v>25</v>
       </c>
@@ -9057,7 +9059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <v>26</v>
       </c>
@@ -9120,7 +9122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <v>26</v>
       </c>
@@ -9183,7 +9185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <v>26</v>
       </c>
@@ -9246,7 +9248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <v>26</v>
       </c>
@@ -9309,7 +9311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <v>26</v>
       </c>
@@ -9372,7 +9374,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <v>26</v>
       </c>
@@ -9435,7 +9437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <v>27</v>
       </c>
@@ -9498,7 +9500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <v>27</v>
       </c>
@@ -9561,7 +9563,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <v>27</v>
       </c>
@@ -9624,7 +9626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <v>27</v>
       </c>
@@ -9687,7 +9689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -9750,7 +9752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <v>27</v>
       </c>
@@ -9813,7 +9815,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <v>29</v>
       </c>
@@ -9876,7 +9878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A106" s="2">
         <v>29</v>
       </c>
@@ -9939,7 +9941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A107" s="2">
         <v>29</v>
       </c>
@@ -10002,7 +10004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A108" s="2">
         <v>29</v>
       </c>
@@ -10065,7 +10067,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A109" s="2">
         <v>29</v>
       </c>
@@ -10128,7 +10130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <v>33</v>
       </c>
@@ -10191,7 +10193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A111" s="2">
         <v>33</v>
       </c>
@@ -10254,7 +10256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <v>33</v>
       </c>
@@ -10317,7 +10319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <v>33</v>
       </c>
@@ -10380,7 +10382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <v>33</v>
       </c>
@@ -10443,7 +10445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <v>33</v>
       </c>
@@ -10506,7 +10508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <v>33</v>
       </c>
@@ -10569,7 +10571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <v>33</v>
       </c>
@@ -10632,7 +10634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <v>33</v>
       </c>
@@ -10695,7 +10697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <v>33</v>
       </c>
@@ -10758,7 +10760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <v>33</v>
       </c>
@@ -10821,7 +10823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <v>33</v>
       </c>
@@ -10884,7 +10886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <v>33</v>
       </c>
@@ -10947,7 +10949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <v>33</v>
       </c>
@@ -11010,7 +11012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <v>33</v>
       </c>
@@ -11073,7 +11075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <v>33</v>
       </c>
@@ -11136,7 +11138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <v>33</v>
       </c>
@@ -11199,7 +11201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <v>33</v>
       </c>
@@ -11262,7 +11264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <v>33</v>
       </c>
@@ -11325,7 +11327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A129" s="2">
         <v>33</v>
       </c>
@@ -11388,7 +11390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <v>33</v>
       </c>
@@ -11451,7 +11453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A131" s="2">
         <v>33</v>
       </c>
@@ -11514,7 +11516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A132" s="2">
         <v>33</v>
       </c>
@@ -11577,7 +11579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A133" s="2">
         <v>33</v>
       </c>
@@ -11640,7 +11642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <v>34</v>
       </c>
@@ -11703,7 +11705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <v>34</v>
       </c>
@@ -11766,7 +11768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <v>34</v>
       </c>
@@ -11829,7 +11831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <v>34</v>
       </c>
@@ -11892,7 +11894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <v>34</v>
       </c>
@@ -11955,7 +11957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <v>34</v>
       </c>
@@ -12018,7 +12020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <v>35</v>
       </c>
@@ -12081,7 +12083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <v>35</v>
       </c>
@@ -12144,7 +12146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <v>35</v>
       </c>
@@ -12207,7 +12209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <v>35</v>
       </c>
@@ -12270,7 +12272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <v>35</v>
       </c>
@@ -12333,7 +12335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <v>35</v>
       </c>
@@ -12396,7 +12398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <v>36</v>
       </c>
@@ -12459,7 +12461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <v>36</v>
       </c>
@@ -12522,7 +12524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <v>36</v>
       </c>
@@ -12585,7 +12587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <v>36</v>
       </c>
@@ -12648,7 +12650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <v>36</v>
       </c>
@@ -12711,7 +12713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <v>36</v>
       </c>
@@ -12774,7 +12776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <v>37</v>
       </c>
@@ -12837,7 +12839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <v>37</v>
       </c>
@@ -12900,7 +12902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <v>37</v>
       </c>
@@ -12963,7 +12965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <v>37</v>
       </c>
@@ -13026,7 +13028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <v>37</v>
       </c>
@@ -13089,7 +13091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <v>37</v>
       </c>
@@ -13152,7 +13154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <v>37</v>
       </c>
@@ -13215,7 +13217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <v>37</v>
       </c>
@@ -13278,7 +13280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <v>37</v>
       </c>
@@ -13341,7 +13343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <v>37</v>
       </c>
@@ -13404,7 +13406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <v>38</v>
       </c>
@@ -13467,7 +13469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <v>38</v>
       </c>
@@ -13530,7 +13532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <v>38</v>
       </c>
@@ -13593,7 +13595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <v>38</v>
       </c>
@@ -13656,7 +13658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <v>38</v>
       </c>
@@ -13719,7 +13721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <v>39</v>
       </c>
@@ -13778,7 +13780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <v>39</v>
       </c>
@@ -13837,7 +13839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <v>39</v>
       </c>
@@ -13896,7 +13898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <v>39</v>
       </c>
@@ -13955,7 +13957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <v>39</v>
       </c>
@@ -14014,7 +14016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <v>40</v>
       </c>
@@ -14077,7 +14079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <v>40</v>
       </c>
@@ -14140,7 +14142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <v>40</v>
       </c>
@@ -14203,7 +14205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <v>40</v>
       </c>
@@ -14266,7 +14268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <v>40</v>
       </c>
@@ -14329,7 +14331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A177" s="2">
         <v>41</v>
       </c>
@@ -14392,7 +14394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <v>41</v>
       </c>
@@ -14455,7 +14457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A179" s="2">
         <v>41</v>
       </c>
@@ -14518,7 +14520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <v>41</v>
       </c>
@@ -14581,7 +14583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A181" s="2">
         <v>41</v>
       </c>
@@ -14644,7 +14646,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <v>42</v>
       </c>
@@ -14707,7 +14709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A183" s="2">
         <v>42</v>
       </c>
@@ -14770,7 +14772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <v>42</v>
       </c>
@@ -14833,7 +14835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A185" s="2">
         <v>42</v>
       </c>
@@ -14896,7 +14898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <v>42</v>
       </c>
@@ -14959,7 +14961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A187" s="2">
         <v>43</v>
       </c>
@@ -15022,7 +15024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <v>43</v>
       </c>
@@ -15085,7 +15087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A189" s="2">
         <v>43</v>
       </c>
@@ -15148,7 +15150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <v>43</v>
       </c>
@@ -15211,7 +15213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A191" s="2">
         <v>44</v>
       </c>
@@ -15270,7 +15272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <v>44</v>
       </c>
@@ -15329,7 +15331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A193" s="2">
         <v>44</v>
       </c>
@@ -15388,7 +15390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A194" s="2">
         <v>44</v>
       </c>
@@ -15447,7 +15449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A195" s="2">
         <v>44</v>
       </c>
@@ -15506,7 +15508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <v>45</v>
       </c>
@@ -15569,7 +15571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A197" s="2">
         <v>45</v>
       </c>
@@ -15632,7 +15634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A198" s="2">
         <v>45</v>
       </c>
@@ -15695,7 +15697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A199" s="2">
         <v>45</v>
       </c>
@@ -15758,7 +15760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <v>45</v>
       </c>
@@ -15821,7 +15823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A201" s="2">
         <v>45</v>
       </c>
@@ -15884,7 +15886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <v>46</v>
       </c>
@@ -15947,7 +15949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A203" s="2">
         <v>46</v>
       </c>
@@ -16010,7 +16012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <v>46</v>
       </c>
@@ -16073,7 +16075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A205" s="2">
         <v>47</v>
       </c>
@@ -16136,7 +16138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <v>47</v>
       </c>
@@ -16199,7 +16201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="207" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A207" s="2">
         <v>47</v>
       </c>
@@ -16262,7 +16264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="208" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <v>47</v>
       </c>
@@ -16325,7 +16327,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="209" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <v>47</v>
       </c>
@@ -16388,7 +16390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="210" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <v>47</v>
       </c>
@@ -16451,7 +16453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="211" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <v>47</v>
       </c>
@@ -16514,7 +16516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="212" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <v>47</v>
       </c>
@@ -16577,7 +16579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="213" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <v>47</v>
       </c>
@@ -16640,7 +16642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="214" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <v>47</v>
       </c>
@@ -16703,7 +16705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="215" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -16766,7 +16768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="216" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <v>47</v>
       </c>
@@ -16829,7 +16831,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="217" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <v>47</v>
       </c>
@@ -16892,7 +16894,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="218" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <v>47</v>
       </c>
@@ -16955,7 +16957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="219" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <v>47</v>
       </c>
@@ -17018,7 +17020,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="220" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <v>47</v>
       </c>
@@ -17081,7 +17083,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="221" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <v>47</v>
       </c>
@@ -17144,7 +17146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <v>47</v>
       </c>
@@ -17207,7 +17209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <v>47</v>
       </c>
@@ -17270,7 +17272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <v>47</v>
       </c>
@@ -17333,7 +17335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="225" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <v>47</v>
       </c>
@@ -17396,7 +17398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="226" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <v>47</v>
       </c>
@@ -17459,7 +17461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="227" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <v>47</v>
       </c>
@@ -17522,7 +17524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="228" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <v>47</v>
       </c>
@@ -17585,7 +17587,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="229" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <v>47</v>
       </c>
@@ -17648,7 +17650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="230" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <v>47</v>
       </c>
@@ -17711,7 +17713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="231" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <v>47</v>
       </c>
@@ -17774,7 +17776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="232" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <v>47</v>
       </c>
@@ -17837,7 +17839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="233" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <v>47</v>
       </c>
@@ -17900,7 +17902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="234" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <v>47</v>
       </c>
@@ -17963,7 +17965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="235" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <v>47</v>
       </c>
@@ -18026,7 +18028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <v>47</v>
       </c>
@@ -18089,7 +18091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="237" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <v>47</v>
       </c>
@@ -18152,7 +18154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="238" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <v>47</v>
       </c>
@@ -18215,7 +18217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="239" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <v>47</v>
       </c>
@@ -18278,7 +18280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="240" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <v>47</v>
       </c>
@@ -18341,7 +18343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="241" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <v>47</v>
       </c>
@@ -18404,7 +18406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="242" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <v>47</v>
       </c>
@@ -18467,7 +18469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="243" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <v>47</v>
       </c>
@@ -18530,7 +18532,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="244" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <v>47</v>
       </c>
@@ -18593,7 +18595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="245" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <v>47</v>
       </c>
@@ -18656,7 +18658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="246" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <v>47</v>
       </c>
@@ -18719,7 +18721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="247" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <v>47</v>
       </c>
@@ -18782,7 +18784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="248" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <v>47</v>
       </c>
@@ -18845,7 +18847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <v>47</v>
       </c>
@@ -18908,7 +18910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <v>48</v>
       </c>
@@ -18965,7 +18967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <v>48</v>
       </c>
@@ -19022,7 +19024,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <v>48</v>
       </c>
@@ -19079,7 +19081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="253" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <v>48</v>
       </c>
@@ -19136,7 +19138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="254" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <v>48</v>
       </c>
@@ -19193,7 +19195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="255" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <v>48</v>
       </c>
@@ -19250,7 +19252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="256" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <v>49</v>
       </c>
@@ -19309,7 +19311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="257" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A257" s="2">
         <v>49</v>
       </c>
@@ -19368,7 +19370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A258" s="2">
         <v>49</v>
       </c>
@@ -19427,7 +19429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="259" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A259" s="2">
         <v>49</v>
       </c>
@@ -19486,7 +19488,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="260" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A260" s="2">
         <v>49</v>
       </c>
@@ -19545,7 +19547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="261" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A261" s="2">
         <v>50</v>
       </c>
@@ -19604,7 +19606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="262" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A262" s="2">
         <v>50</v>
       </c>
@@ -19663,7 +19665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="263" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A263" s="2">
         <v>50</v>
       </c>
@@ -19722,7 +19724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="264" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A264" s="2">
         <v>50</v>
       </c>
@@ -19781,7 +19783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="265" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A265" s="2">
         <v>51</v>
       </c>
@@ -19840,7 +19842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="266" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A266" s="2">
         <v>51</v>
       </c>
@@ -19899,7 +19901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="267" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A267" s="2">
         <v>51</v>
       </c>
@@ -19958,7 +19960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="268" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A268" s="2">
         <v>51</v>
       </c>
@@ -20017,7 +20019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="269" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A269" s="2">
         <v>52</v>
       </c>
@@ -20076,7 +20078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="270" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A270" s="2">
         <v>52</v>
       </c>
@@ -20135,7 +20137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="271" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A271" s="2">
         <v>52</v>
       </c>
@@ -20194,7 +20196,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="272" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A272" s="2">
         <v>52</v>
       </c>
@@ -20253,7 +20255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="273" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A273" s="2">
         <v>52</v>
       </c>
@@ -20312,7 +20314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="274" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A274" s="2">
         <v>53</v>
       </c>
@@ -20375,7 +20377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="275" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A275" s="2">
         <v>53</v>
       </c>
@@ -20438,7 +20440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="276" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A276" s="2">
         <v>53</v>
       </c>
@@ -20501,7 +20503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A277" s="2">
         <v>54</v>
       </c>
@@ -20560,7 +20562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="278" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A278" s="2">
         <v>54</v>
       </c>
@@ -20619,7 +20621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="279" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A279" s="2">
         <v>54</v>
       </c>
@@ -20678,7 +20680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="280" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A280" s="2">
         <v>54</v>
       </c>
@@ -20737,7 +20739,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="281" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A281" s="2">
         <v>54</v>
       </c>
@@ -20796,7 +20798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="282" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A282" s="2">
         <v>54</v>
       </c>
@@ -20855,7 +20857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="283" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A283" s="2">
         <v>55</v>
       </c>
@@ -20918,7 +20920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="284" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A284" s="2">
         <v>55</v>
       </c>
@@ -20981,7 +20983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="285" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A285" s="2">
         <v>55</v>
       </c>
@@ -21044,7 +21046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="286" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A286" s="2">
         <v>56</v>
       </c>
@@ -21103,7 +21105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="287" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A287" s="2">
         <v>56</v>
       </c>
@@ -21162,7 +21164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="288" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A288" s="2">
         <v>56</v>
       </c>
@@ -21221,7 +21223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A289" s="2">
         <v>56</v>
       </c>
@@ -21280,7 +21282,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A290" s="2">
         <v>56</v>
       </c>
@@ -21339,7 +21341,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A291" s="2">
         <v>56</v>
       </c>
@@ -21398,7 +21400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="292" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A292" s="2">
         <v>56</v>
       </c>
@@ -21457,7 +21459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="293" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A293" s="2">
         <v>56</v>
       </c>
@@ -21516,7 +21518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="294" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A294" s="2">
         <v>57</v>
       </c>
@@ -21575,7 +21577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="295" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A295" s="2">
         <v>57</v>
       </c>
@@ -21634,7 +21636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="296" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A296" s="2">
         <v>57</v>
       </c>
@@ -21693,7 +21695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="297" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A297" s="2">
         <v>57</v>
       </c>
@@ -21752,7 +21754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="298" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A298" s="2">
         <v>57</v>
       </c>
@@ -21811,7 +21813,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="299" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A299" s="2">
         <v>57</v>
       </c>
@@ -21870,7 +21872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="300" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A300" s="2">
         <v>57</v>
       </c>
@@ -21929,7 +21931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A301" s="2">
         <v>57</v>
       </c>
@@ -21988,7 +21990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="302" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A302" s="2">
         <v>58</v>
       </c>
@@ -22047,7 +22049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="303" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A303" s="2">
         <v>58</v>
       </c>
@@ -22106,7 +22108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="304" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A304" s="2">
         <v>62</v>
       </c>
@@ -22165,7 +22167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="305" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A305" s="2">
         <v>62</v>
       </c>
@@ -22224,7 +22226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="306" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A306" s="2">
         <v>59</v>
       </c>
@@ -22287,7 +22289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="307" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A307" s="2">
         <v>59</v>
       </c>
@@ -22350,7 +22352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="308" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A308" s="2">
         <v>59</v>
       </c>
@@ -22413,7 +22415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="309" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A309" s="2">
         <v>59</v>
       </c>
@@ -22476,7 +22478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="310" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A310" s="2">
         <v>59</v>
       </c>
@@ -22539,7 +22541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="311" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A311" s="2">
         <v>60</v>
       </c>
@@ -22602,7 +22604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="312" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A312" s="2">
         <v>60</v>
       </c>
@@ -22665,7 +22667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="313" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A313" s="2">
         <v>60</v>
       </c>
@@ -22728,7 +22730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="314" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A314" s="2">
         <v>60</v>
       </c>
@@ -22791,7 +22793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="315" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A315" s="2">
         <v>60</v>
       </c>
@@ -22854,7 +22856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="316" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A316" s="2">
         <v>61</v>
       </c>
@@ -22913,7 +22915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="317" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A317" s="2">
         <v>61</v>
       </c>
@@ -22972,7 +22974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="318" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A318" s="2">
         <v>61</v>
       </c>
@@ -23031,7 +23033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="319" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A319" s="2">
         <v>61</v>
       </c>
@@ -23090,7 +23092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="320" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A320" s="2">
         <v>61</v>
       </c>
@@ -23149,7 +23151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="321" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A321" s="2">
         <v>61</v>
       </c>
@@ -23208,7 +23210,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="322" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A322" s="2">
         <v>62</v>
       </c>
@@ -23271,7 +23273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="323" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A323" s="2">
         <v>62</v>
       </c>
@@ -23334,7 +23336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="324" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A324" s="2">
         <v>64</v>
       </c>
@@ -23391,7 +23393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="325" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A325" s="2">
         <v>64</v>
       </c>
@@ -23448,7 +23450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="326" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A326" s="2">
         <v>64</v>
       </c>
@@ -23505,7 +23507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="327" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A327" s="2">
         <v>64</v>
       </c>
@@ -23562,7 +23564,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="328" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A328" s="2">
         <v>64</v>
       </c>
@@ -23619,7 +23621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="329" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A329" s="2">
         <v>89</v>
       </c>
@@ -23682,7 +23684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A330" s="2">
         <v>89</v>
       </c>
@@ -23745,7 +23747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A331" s="2">
         <v>89</v>
       </c>
@@ -23808,7 +23810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A332" s="2">
         <v>90</v>
       </c>
@@ -23871,7 +23873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A333" s="2">
         <v>90</v>
       </c>
@@ -23934,7 +23936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="334" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A334" s="2">
         <v>90</v>
       </c>
@@ -23997,7 +23999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="335" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A335" s="2">
         <v>88</v>
       </c>
@@ -24060,7 +24062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="336" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A336" s="2">
         <v>88</v>
       </c>
@@ -24123,7 +24125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="337" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A337" s="2">
         <v>88</v>
       </c>
@@ -24184,7 +24186,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="338" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="b">
         <v>0</v>
@@ -24241,7 +24243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="339" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="b">
         <v>0</v>
@@ -24298,7 +24300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="340" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="b">
         <v>0</v>
@@ -24355,7 +24357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="341" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="b">
         <v>0</v>
@@ -24412,7 +24414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="342" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="b">
         <v>0</v>
@@ -24469,7 +24471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="343" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="b">
         <v>0</v>
@@ -24526,7 +24528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="344" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="b">
         <v>0</v>
@@ -24583,7 +24585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="345" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A345" s="2">
         <v>82</v>
       </c>
@@ -24646,7 +24648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="346" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A346" s="2">
         <v>82</v>
       </c>
@@ -24709,7 +24711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="347" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A347" s="2">
         <v>82</v>
       </c>
@@ -24772,7 +24774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="348" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A348" s="2">
         <v>82</v>
       </c>
@@ -24835,7 +24837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="349" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A349" s="2">
         <v>82</v>
       </c>
@@ -24898,7 +24900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="350" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
         <v>82</v>
       </c>
@@ -24961,7 +24963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="351" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
         <v>81</v>
       </c>
@@ -25024,7 +25026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="352" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A352" s="2">
         <v>81</v>
       </c>
@@ -25087,7 +25089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="353" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A353" s="2">
         <v>81</v>
       </c>
@@ -25150,7 +25152,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="354" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A354" s="2">
         <v>81</v>
       </c>
@@ -25213,7 +25215,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="355" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A355" s="2">
         <v>81</v>
       </c>
@@ -25276,7 +25278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A356" s="2">
         <v>81</v>
       </c>
@@ -25339,7 +25341,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="357" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A357" s="2">
         <v>76</v>
       </c>
@@ -25402,7 +25404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="358" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A358" s="2">
         <v>76</v>
       </c>
@@ -25465,7 +25467,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="359" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A359" s="2">
         <v>76</v>
       </c>
@@ -25528,7 +25530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="360" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A360" s="2">
         <v>76</v>
       </c>
@@ -25591,7 +25593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="361" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A361" s="2">
         <v>75</v>
       </c>
@@ -25654,7 +25656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="362" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A362" s="2">
         <v>75</v>
       </c>
@@ -25717,7 +25719,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="363" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A363" s="2">
         <v>75</v>
       </c>
@@ -25780,7 +25782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="364" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A364" s="2">
         <v>75</v>
       </c>
@@ -25843,7 +25845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A365" s="2">
         <v>74</v>
       </c>
@@ -25902,7 +25904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A366" s="2">
         <v>74</v>
       </c>
@@ -25961,7 +25963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="367" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A367" s="2">
         <v>74</v>
       </c>
@@ -26020,7 +26022,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="368" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A368" s="2">
         <v>74</v>
       </c>
@@ -26079,7 +26081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="369" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
         <v>74</v>
       </c>
@@ -26138,7 +26140,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="370" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
         <v>87</v>
       </c>
@@ -26201,7 +26203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="371" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
         <v>87</v>
       </c>
@@ -26264,7 +26266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="372" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
         <v>94</v>
       </c>
@@ -26323,7 +26325,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="373" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
         <v>94</v>
       </c>
@@ -26382,7 +26384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="374" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
         <v>94</v>
       </c>
@@ -26441,7 +26443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="375" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
         <v>94</v>
       </c>
@@ -26500,7 +26502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="376" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
         <v>94</v>
       </c>
@@ -26559,7 +26561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="377" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
         <v>94</v>
       </c>
@@ -26618,7 +26620,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="378" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
         <v>94</v>
       </c>
@@ -26677,7 +26679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="379" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A379" s="2">
         <v>94</v>
       </c>
@@ -26736,7 +26738,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="380" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A380" s="2">
         <v>94</v>
       </c>
@@ -26795,7 +26797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="381" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A381" s="2">
         <v>94</v>
       </c>
@@ -26854,7 +26856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="382" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A382" s="2">
         <v>94</v>
       </c>
@@ -26913,7 +26915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A383" s="2">
         <v>94</v>
       </c>
@@ -26972,7 +26974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A384" s="2">
         <v>94</v>
       </c>
@@ -27031,7 +27033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A385" s="2"/>
       <c r="B385" s="2" t="b">
         <v>0</v>
@@ -27092,7 +27094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A386" s="2"/>
       <c r="B386" s="2" t="b">
         <v>0</v>
@@ -27153,7 +27155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="387" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A387" s="2"/>
       <c r="B387" s="2" t="b">
         <v>0</v>
@@ -27214,7 +27216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="388" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A388" s="2"/>
       <c r="B388" s="2" t="b">
         <v>0</v>
@@ -27275,7 +27277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="389" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A389" s="2"/>
       <c r="B389" s="2" t="b">
         <v>0</v>
@@ -27336,7 +27338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="390" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A390" s="2">
         <v>79</v>
       </c>
@@ -27399,7 +27401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="391" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A391" s="2">
         <v>79</v>
       </c>
@@ -27462,7 +27464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="392" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A392" s="2">
         <v>79</v>
       </c>
@@ -27525,7 +27527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="393" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A393" s="2">
         <v>79</v>
       </c>
@@ -27588,7 +27590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="394" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A394" s="2">
         <v>79</v>
       </c>
@@ -27651,7 +27653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="395" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A395" s="2">
         <v>78</v>
       </c>
@@ -27714,7 +27716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="396" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A396" s="2">
         <v>78</v>
       </c>
@@ -27777,7 +27779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="397" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A397" s="2">
         <v>78</v>
       </c>
@@ -27840,7 +27842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="398" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A398" s="2">
         <v>78</v>
       </c>
@@ -27903,7 +27905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="399" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A399" s="2">
         <v>78</v>
       </c>
@@ -27966,7 +27968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="400" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A400" s="2"/>
       <c r="B400" s="2" t="b">
         <v>0</v>
@@ -28027,7 +28029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="401" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A401" s="2"/>
       <c r="B401" s="2" t="b">
         <v>0</v>
@@ -28088,7 +28090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="402" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A402" s="2"/>
       <c r="B402" s="2" t="b">
         <v>0</v>
@@ -28149,7 +28151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="403" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A403" s="2"/>
       <c r="B403" s="2" t="b">
         <v>0</v>
@@ -28210,7 +28212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="404" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A404" s="2"/>
       <c r="B404" s="2" t="b">
         <v>0</v>
@@ -28271,7 +28273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="405" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A405" s="2"/>
       <c r="B405" s="2" t="b">
         <v>0</v>
@@ -28332,7 +28334,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="406" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A406" s="2"/>
       <c r="B406" s="2" t="b">
         <v>0</v>
@@ -28393,7 +28395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="407" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="b">
         <v>0</v>
@@ -28454,7 +28456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="408" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A408" s="2"/>
       <c r="B408" s="2" t="b">
         <v>0</v>
@@ -28515,7 +28517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="409" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A409" s="2"/>
       <c r="B409" s="2" t="b">
         <v>0</v>
@@ -28576,7 +28578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A410" s="2"/>
       <c r="B410" s="2" t="b">
         <v>0</v>
@@ -28637,7 +28639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="411" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A411" s="2"/>
       <c r="B411" s="2" t="b">
         <v>0</v>
@@ -28698,7 +28700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="412" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A412" s="2"/>
       <c r="B412" s="2" t="b">
         <v>0</v>
@@ -28759,7 +28761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="413" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A413" s="2"/>
       <c r="B413" s="2" t="b">
         <v>0</v>
@@ -28820,7 +28822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="414" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A414" s="2"/>
       <c r="B414" s="2" t="b">
         <v>0</v>
@@ -28881,7 +28883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="415" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A415" s="2"/>
       <c r="B415" s="2" t="b">
         <v>0</v>
@@ -28942,7 +28944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="416" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A416" s="2"/>
       <c r="B416" s="2" t="b">
         <v>0</v>
@@ -29003,7 +29005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="417" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A417" s="2"/>
       <c r="B417" s="2" t="b">
         <v>0</v>
@@ -29064,7 +29066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="418" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A418" s="2"/>
       <c r="B418" s="2" t="b">
         <v>0</v>
@@ -29125,7 +29127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A419" s="2"/>
       <c r="B419" s="2" t="b">
         <v>0</v>
@@ -29186,7 +29188,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A420" s="2"/>
       <c r="B420" s="2" t="b">
         <v>0</v>
@@ -29247,7 +29249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A421" s="2"/>
       <c r="B421" s="2" t="b">
         <v>0</v>
@@ -29308,7 +29310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="422" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A422" s="2"/>
       <c r="B422" s="2" t="b">
         <v>0</v>
@@ -29369,7 +29371,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="423" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="b">
         <v>0</v>
@@ -29430,7 +29432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="424" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A424" s="2"/>
       <c r="B424" s="2" t="b">
         <v>0</v>
@@ -29491,7 +29493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="425" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A425" s="2"/>
       <c r="B425" s="2" t="b">
         <v>0</v>
@@ -29552,7 +29554,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="426" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A426" s="2"/>
       <c r="B426" s="2" t="b">
         <v>0</v>
@@ -29613,7 +29615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="427" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A427" s="2"/>
       <c r="B427" s="2" t="b">
         <v>0</v>
@@ -29674,7 +29676,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="428" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A428" s="2"/>
       <c r="B428" s="2" t="b">
         <v>0</v>
@@ -29735,7 +29737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="429" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A429" s="2"/>
       <c r="B429" s="2" t="b">
         <v>0</v>
@@ -29796,7 +29798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="430" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A430" s="2"/>
       <c r="B430" s="2" t="b">
         <v>0</v>
@@ -29857,7 +29859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="431" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A431" s="2"/>
       <c r="B431" s="2" t="b">
         <v>0</v>
@@ -29918,7 +29920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="432" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A432" s="2"/>
       <c r="B432" s="2" t="b">
         <v>0</v>
@@ -29979,7 +29981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="433" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A433" s="2"/>
       <c r="B433" s="2" t="b">
         <v>0</v>
@@ -30040,7 +30042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="434" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A434" s="2"/>
       <c r="B434" s="2" t="b">
         <v>0</v>
@@ -30101,7 +30103,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="435" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A435" s="2"/>
       <c r="B435" s="2" t="b">
         <v>0</v>
@@ -30162,7 +30164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A436" s="2"/>
       <c r="B436" s="2" t="b">
         <v>0</v>
@@ -30223,7 +30225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="437" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A437" s="2"/>
       <c r="B437" s="2" t="b">
         <v>0</v>
@@ -30284,7 +30286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="438" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A438" s="2"/>
       <c r="B438" s="2" t="b">
         <v>0</v>
@@ -30345,7 +30347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="439" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="b">
         <v>0</v>
@@ -30406,7 +30408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="440" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A440" s="2"/>
       <c r="B440" s="2" t="b">
         <v>0</v>
@@ -30467,7 +30469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="441" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A441" s="2"/>
       <c r="B441" s="2" t="b">
         <v>0</v>
@@ -30528,7 +30530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="442" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A442" s="2"/>
       <c r="B442" s="2" t="b">
         <v>0</v>
@@ -30589,7 +30591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="443" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A443" s="2"/>
       <c r="B443" s="2" t="b">
         <v>0</v>
@@ -30650,7 +30652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="444" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A444" s="2"/>
       <c r="B444" s="2" t="b">
         <v>0</v>
@@ -30711,7 +30713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="445" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A445" s="2"/>
       <c r="B445" s="2" t="b">
         <v>0</v>
@@ -30772,7 +30774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="446" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A446" s="2"/>
       <c r="B446" s="2" t="b">
         <v>0</v>
@@ -30833,7 +30835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="447" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A447" s="2"/>
       <c r="B447" s="2" t="b">
         <v>0</v>
@@ -30894,7 +30896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="448" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A448" s="2"/>
       <c r="B448" s="2" t="b">
         <v>0</v>
@@ -30955,7 +30957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="449" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A449" s="2"/>
       <c r="B449" s="2" t="b">
         <v>0</v>
@@ -31016,7 +31018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="450" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A450" s="2"/>
       <c r="B450" s="2" t="b">
         <v>0</v>
@@ -31077,7 +31079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="451" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A451" s="2"/>
       <c r="B451" s="2" t="b">
         <v>0</v>
@@ -31138,7 +31140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="452" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A452" s="2"/>
       <c r="B452" s="2" t="b">
         <v>0</v>
@@ -31199,7 +31201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="453" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A453" s="2"/>
       <c r="B453" s="2" t="b">
         <v>0</v>
@@ -31256,7 +31258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="454" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A454" s="2"/>
       <c r="B454" s="2" t="b">
         <v>0</v>
@@ -31313,7 +31315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="455" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="b">
         <v>0</v>
@@ -31370,7 +31372,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="456" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="456" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A456" s="2"/>
       <c r="B456" s="2" t="b">
         <v>0</v>
@@ -31427,7 +31429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="457" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="457" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A457" s="2"/>
       <c r="B457" s="2" t="b">
         <v>0</v>
@@ -31484,7 +31486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="458" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A458" s="2"/>
       <c r="B458" s="2" t="b">
         <v>0</v>
@@ -31541,7 +31543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="459" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A459" s="2"/>
       <c r="B459" s="2" t="b">
         <v>0</v>
@@ -31598,7 +31600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="460" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A460" s="2"/>
       <c r="B460" s="2" t="b">
         <v>0</v>
@@ -31655,7 +31657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="461" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A461" s="2"/>
       <c r="B461" s="2" t="b">
         <v>0</v>
@@ -31712,7 +31714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="462" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A462" s="2"/>
       <c r="B462" s="2" t="b">
         <v>0</v>
@@ -31769,7 +31771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="463" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A463" s="2"/>
       <c r="B463" s="2" t="b">
         <v>0</v>
@@ -31826,7 +31828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="464" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A464" s="2"/>
       <c r="B464" s="2" t="b">
         <v>0</v>
@@ -31883,7 +31885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="465" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A465" s="2"/>
       <c r="B465" s="2" t="b">
         <v>0</v>
@@ -31940,7 +31942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="466" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A466" s="2"/>
       <c r="B466" s="2" t="b">
         <v>0</v>
@@ -31997,7 +31999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="467" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A467" s="2"/>
       <c r="B467" s="2" t="b">
         <v>0</v>
@@ -32054,7 +32056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="468" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="468" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A468" s="2"/>
       <c r="B468" s="2" t="b">
         <v>0</v>
@@ -32111,7 +32113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="469" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A469" s="2"/>
       <c r="B469" s="2" t="b">
         <v>0</v>
@@ -32168,7 +32170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="470" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A470" s="2"/>
       <c r="B470" s="2" t="b">
         <v>0</v>
@@ -32225,7 +32227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="471" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="b">
         <v>0</v>
@@ -32278,7 +32280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="472" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A472" s="2"/>
       <c r="B472" s="2" t="b">
         <v>0</v>
@@ -32333,7 +32335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="473" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A473" s="2"/>
       <c r="B473" s="2" t="b">
         <v>0</v>
@@ -32388,7 +32390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="474" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="474" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A474" s="2"/>
       <c r="B474" s="2" t="b">
         <v>0</v>
@@ -32443,7 +32445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="475" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="475" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A475" s="2"/>
       <c r="B475" s="2" t="b">
         <v>0</v>
@@ -32498,7 +32500,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="476" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="476" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A476" s="2"/>
       <c r="B476" s="2" t="b">
         <v>0</v>
@@ -32553,7 +32555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="477" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="477" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A477" s="2"/>
       <c r="B477" s="2" t="b">
         <v>0</v>
@@ -32608,7 +32610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="478" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A478" s="2"/>
       <c r="B478" s="2" t="b">
         <v>0</v>
@@ -32661,7 +32663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="479" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="479" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A479" s="2"/>
       <c r="B479" s="2" t="b">
         <v>0</v>
@@ -32716,7 +32718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="480" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A480" s="2"/>
       <c r="B480" s="2" t="b">
         <v>0</v>
@@ -32771,7 +32773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="481" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A481" s="2"/>
       <c r="B481" s="2" t="b">
         <v>0</v>
@@ -32826,7 +32828,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="482" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A482" s="2"/>
       <c r="B482" s="2" t="b">
         <v>0</v>
@@ -32881,7 +32883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="483" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A483" s="2"/>
       <c r="B483" s="2" t="b">
         <v>0</v>
@@ -32936,7 +32938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="484" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A484" s="2"/>
       <c r="B484" s="2" t="b">
         <v>0</v>
@@ -32991,7 +32993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="485" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A485" s="2"/>
       <c r="B485" s="2" t="b">
         <v>0</v>
@@ -33046,7 +33048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="486" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A486" s="2"/>
       <c r="B486" s="2" t="b">
         <v>0</v>
@@ -33103,7 +33105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="487" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A487" s="2"/>
       <c r="B487" s="2" t="b">
         <v>0</v>
@@ -33160,7 +33162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="488" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A488" s="2"/>
       <c r="B488" s="2" t="b">
         <v>0</v>
@@ -33217,7 +33219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="489" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="489" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A489" s="2"/>
       <c r="B489" s="2" t="b">
         <v>0</v>
@@ -33274,7 +33276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="490" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="490" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A490" s="2"/>
       <c r="B490" s="2" t="b">
         <v>0</v>
@@ -33331,7 +33333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="491" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="491" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A491" s="2"/>
       <c r="B491" s="2" t="b">
         <v>0</v>
@@ -33388,7 +33390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="492" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="492" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A492" s="2"/>
       <c r="B492" s="2" t="b">
         <v>0</v>
@@ -33445,7 +33447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="493" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A493" s="2"/>
       <c r="B493" s="2" t="b">
         <v>0</v>
@@ -33502,7 +33504,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="494" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="494" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A494" s="2"/>
       <c r="B494" s="2" t="b">
         <v>0</v>
@@ -33559,7 +33561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="495" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="495" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A495" s="2"/>
       <c r="B495" s="2" t="b">
         <v>0</v>
@@ -33616,7 +33618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="496" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A496" s="2"/>
       <c r="B496" s="2" t="b">
         <v>0</v>
@@ -33673,7 +33675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="497" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A497" s="2"/>
       <c r="B497" s="2" t="b">
         <v>0</v>
@@ -33730,7 +33732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="498" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A498" s="2"/>
       <c r="B498" s="2" t="b">
         <v>0</v>
@@ -33787,7 +33789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="499" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="499" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A499" s="2"/>
       <c r="B499" s="2" t="b">
         <v>0</v>
@@ -33844,7 +33846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="500" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A500" s="2"/>
       <c r="B500" s="2" t="b">
         <v>0</v>
@@ -33901,7 +33903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="501" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="501" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A501" s="2"/>
       <c r="B501" s="2" t="b">
         <v>0</v>
@@ -33958,7 +33960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="502" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="502" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A502" s="2"/>
       <c r="B502" s="2" t="b">
         <v>0</v>
@@ -34019,7 +34021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="503" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="503" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A503" s="2"/>
       <c r="B503" s="2" t="b">
         <v>0</v>
@@ -34080,7 +34082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="504" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A504" s="2"/>
       <c r="B504" s="2" t="b">
         <v>0</v>
@@ -34141,7 +34143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="505" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A505" s="2"/>
       <c r="B505" s="2" t="b">
         <v>0</v>
@@ -34202,7 +34204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="506" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A506" s="2"/>
       <c r="B506" s="2" t="b">
         <v>0</v>
@@ -34263,7 +34265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="507" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A507" s="2"/>
       <c r="B507" s="2" t="b">
         <v>0</v>
@@ -34324,7 +34326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="508" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A508" s="2"/>
       <c r="B508" s="2" t="b">
         <v>0</v>
@@ -34385,7 +34387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="509" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A509" s="2"/>
       <c r="B509" s="2" t="b">
         <v>0</v>
@@ -34446,7 +34448,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="510" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A510" s="2"/>
       <c r="B510" s="2" t="b">
         <v>0</v>
@@ -34507,7 +34509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="511" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A511" s="2"/>
       <c r="B511" s="2" t="b">
         <v>0</v>
@@ -34568,7 +34570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="512" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A512" s="2"/>
       <c r="B512" s="2" t="b">
         <v>0</v>
@@ -34629,7 +34631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="513" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="513" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A513" s="2"/>
       <c r="B513" s="2" t="b">
         <v>0</v>
@@ -34690,7 +34692,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="514" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A514" s="2"/>
       <c r="B514" s="2" t="b">
         <v>0</v>
@@ -34751,7 +34753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="515" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="515" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A515" s="2"/>
       <c r="B515" s="2" t="b">
         <v>0</v>
@@ -34812,7 +34814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="516" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A516" s="2"/>
       <c r="B516" s="2" t="b">
         <v>0</v>
@@ -34873,7 +34875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="517" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A517" s="2"/>
       <c r="B517" s="2" t="b">
         <v>0</v>
@@ -34934,7 +34936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="518" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A518" s="2"/>
       <c r="B518" s="2" t="b">
         <v>0</v>
@@ -34995,7 +34997,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="519" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A519" s="2"/>
       <c r="B519" s="2" t="b">
         <v>0</v>
@@ -35056,7 +35058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="520" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A520" s="2"/>
       <c r="B520" s="2" t="b">
         <v>0</v>
@@ -35117,7 +35119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="521" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A521" s="2"/>
       <c r="B521" s="2" t="b">
         <v>0</v>
@@ -35178,7 +35180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="522" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A522" s="2"/>
       <c r="B522" s="2" t="b">
         <v>0</v>
@@ -35239,7 +35241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="523" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A523" s="2"/>
       <c r="B523" s="2" t="b">
         <v>0</v>
@@ -35300,7 +35302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="524" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A524" s="2"/>
       <c r="B524" s="2" t="b">
         <v>0</v>
@@ -35361,7 +35363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="525" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A525" s="2"/>
       <c r="B525" s="2" t="b">
         <v>0</v>
@@ -35422,7 +35424,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="526" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A526" s="2"/>
       <c r="B526" s="2" t="b">
         <v>0</v>
@@ -35483,7 +35485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="527" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A527" s="2"/>
       <c r="B527" s="2" t="b">
         <v>0</v>
@@ -35544,7 +35546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="528" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A528" s="2"/>
       <c r="B528" s="2" t="b">
         <v>0</v>
@@ -35605,7 +35607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="529" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A529" s="2"/>
       <c r="B529" s="2" t="b">
         <v>0</v>
@@ -35666,7 +35668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="530" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A530" s="2"/>
       <c r="B530" s="2" t="b">
         <v>0</v>
@@ -35727,7 +35729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="531" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A531" s="2"/>
       <c r="B531" s="2" t="b">
         <v>0</v>
@@ -35788,7 +35790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="532" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A532" s="2"/>
       <c r="B532" s="2" t="b">
         <v>0</v>
@@ -35849,7 +35851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="533" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A533" s="2"/>
       <c r="B533" s="2" t="b">
         <v>0</v>
@@ -35910,7 +35912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="534" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A534" s="2"/>
       <c r="B534" s="2" t="b">
         <v>0</v>
@@ -35971,7 +35973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="535" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A535" s="2"/>
       <c r="B535" s="2" t="b">
         <v>0</v>
@@ -36032,7 +36034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="536" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A536" s="2"/>
       <c r="B536" s="2" t="b">
         <v>0</v>
@@ -36093,7 +36095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="537" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A537" s="2"/>
       <c r="B537" s="2" t="b">
         <v>0</v>
@@ -36154,7 +36156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="538" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A538" s="2"/>
       <c r="B538" s="2" t="b">
         <v>0</v>
@@ -36215,7 +36217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="539" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A539" s="2"/>
       <c r="B539" s="2" t="b">
         <v>0</v>
@@ -36276,7 +36278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="540" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A540" s="2"/>
       <c r="B540" s="2" t="b">
         <v>0</v>
@@ -36337,7 +36339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="541" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A541" s="2"/>
       <c r="B541" s="2" t="b">
         <v>0</v>
@@ -36398,7 +36400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="542" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A542" s="2"/>
       <c r="B542" s="2" t="b">
         <v>0</v>
@@ -36459,7 +36461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="543" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A543" s="2"/>
       <c r="B543" s="2" t="b">
         <v>0</v>
@@ -36520,7 +36522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="544" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="544" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A544" s="2"/>
       <c r="B544" s="2" t="b">
         <v>0</v>
@@ -36581,7 +36583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="545" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="545" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A545" s="2"/>
       <c r="B545" s="2" t="b">
         <v>0</v>
@@ -36642,7 +36644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="546" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A546" s="2"/>
       <c r="B546" s="2" t="b">
         <v>0</v>
@@ -36703,7 +36705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="547" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A547" s="2"/>
       <c r="B547" s="2" t="b">
         <v>0</v>
@@ -36764,7 +36766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="548" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A548" s="2"/>
       <c r="B548" s="2" t="b">
         <v>0</v>
@@ -36825,7 +36827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="549" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A549" s="2"/>
       <c r="B549" s="2" t="b">
         <v>0</v>
@@ -36886,7 +36888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="550" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="550" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A550" s="2"/>
       <c r="B550" s="2" t="b">
         <v>0</v>
@@ -36947,7 +36949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="551" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A551" s="2"/>
       <c r="B551" s="2" t="b">
         <v>0</v>
@@ -37008,7 +37010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="552" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A552" s="2"/>
       <c r="B552" s="2" t="b">
         <v>0</v>
@@ -37069,7 +37071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="553" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="553" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A553" s="2"/>
       <c r="B553" s="2" t="b">
         <v>0</v>
@@ -37130,7 +37132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="554" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A554" s="2"/>
       <c r="B554" s="2" t="b">
         <v>0</v>
@@ -37191,7 +37193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="555" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A555" s="2"/>
       <c r="B555" s="2" t="b">
         <v>0</v>
@@ -37252,7 +37254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="556" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A556" s="2"/>
       <c r="B556" s="2" t="b">
         <v>0</v>
@@ -37313,7 +37315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="557" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="557" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A557" s="2"/>
       <c r="B557" s="2" t="b">
         <v>0</v>
@@ -37362,7 +37364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="558" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="558" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A558" s="2"/>
       <c r="B558" s="2" t="b">
         <v>0</v>
@@ -37411,7 +37413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="559" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="559" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A559" s="2"/>
       <c r="B559" s="2" t="b">
         <v>0</v>
@@ -37460,7 +37462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="560" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A560" s="2">
         <v>83</v>
       </c>
@@ -37523,7 +37525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="561" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A561" s="2">
         <v>83</v>
       </c>
@@ -37586,7 +37588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="562" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A562" s="2">
         <v>83</v>
       </c>
@@ -37649,7 +37651,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="563" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A563" s="2"/>
       <c r="B563" s="2" t="b">
         <v>0</v>
@@ -37710,7 +37712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="564" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="564" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A564" s="2"/>
       <c r="B564" s="2" t="b">
         <v>1</v>
@@ -37771,7 +37773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="565" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="565" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A565" s="2"/>
       <c r="B565" s="2" t="b">
         <v>0</v>
@@ -37832,7 +37834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="566" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A566" s="2">
         <v>85</v>
       </c>
@@ -37895,7 +37897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="567" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="567" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A567" s="2">
         <v>85</v>
       </c>
@@ -37958,7 +37960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="568" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="568" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A568" s="2">
         <v>85</v>
       </c>
@@ -38021,7 +38023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="569" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A569" s="2">
         <v>86</v>
       </c>
@@ -38084,7 +38086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="570" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A570" s="2">
         <v>86</v>
       </c>
@@ -38147,7 +38149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="571" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A571" s="2">
         <v>86</v>
       </c>
@@ -38210,7 +38212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="572" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A572" s="2">
         <v>84</v>
       </c>
@@ -38273,7 +38275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="573" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A573" s="2">
         <v>84</v>
       </c>
@@ -38336,7 +38338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="574" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="574" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A574" s="2">
         <v>84</v>
       </c>
@@ -38399,7 +38401,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="575" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A575" s="2"/>
       <c r="B575" s="2" t="b">
         <v>0</v>
@@ -38448,7 +38450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="576" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A576" s="2">
         <v>80</v>
       </c>
@@ -38507,7 +38509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="577" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A577" s="2">
         <v>80</v>
       </c>
@@ -38566,7 +38568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="578" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="578" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A578" s="2">
         <v>80</v>
       </c>
@@ -38625,7 +38627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="579" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="579" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A579" s="2">
         <v>80</v>
       </c>
@@ -38684,7 +38686,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="580" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A580" s="2">
         <v>80</v>
       </c>
@@ -38743,7 +38745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="581" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A581" s="2">
         <v>80</v>
       </c>
@@ -38802,7 +38804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="582" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="582" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A582" s="2">
         <v>80</v>
       </c>
@@ -38861,7 +38863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="583" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A583" s="2">
         <v>80</v>
       </c>
@@ -38920,7 +38922,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="584" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="584" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A584" s="2">
         <v>80</v>
       </c>
@@ -38979,7 +38981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="585" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="585" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A585" s="2"/>
       <c r="B585" s="2" t="b">
         <v>0</v>
@@ -39030,7 +39032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="586" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="586" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A586" s="2">
         <v>91</v>
       </c>
@@ -39089,7 +39091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="587" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A587" s="2">
         <v>91</v>
       </c>
@@ -39148,7 +39150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="588" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A588" s="2">
         <v>91</v>
       </c>
@@ -39207,7 +39209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="589" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A589" s="2">
         <v>91</v>
       </c>
@@ -39266,7 +39268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="590" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A590" s="2">
         <v>91</v>
       </c>
@@ -39325,7 +39327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="591" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A591" s="2">
         <v>91</v>
       </c>
@@ -39384,7 +39386,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="592" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="592" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A592" s="2">
         <v>91</v>
       </c>
@@ -39443,7 +39445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="593" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="593" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A593" s="2"/>
       <c r="B593" s="2" t="b">
         <v>0</v>
@@ -39500,7 +39502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="594" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="594" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A594" s="2"/>
       <c r="B594" s="2" t="b">
         <v>0</v>
@@ -39557,7 +39559,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="595" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A595" s="2"/>
       <c r="B595" s="2" t="b">
         <v>0</v>
@@ -39614,7 +39616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="596" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A596" s="2"/>
       <c r="B596" s="2" t="b">
         <v>0</v>
@@ -39671,7 +39673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="597" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A597" s="2"/>
       <c r="B597" s="2" t="b">
         <v>0</v>
@@ -39728,7 +39730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="598" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="598" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A598" s="2"/>
       <c r="B598" s="2" t="b">
         <v>0</v>
@@ -39785,7 +39787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="599" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="599" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A599" s="2"/>
       <c r="B599" s="2" t="b">
         <v>0</v>
@@ -39842,7 +39844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="600" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="600" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A600" s="2"/>
       <c r="B600" s="2" t="b">
         <v>0</v>
@@ -39899,7 +39901,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="601" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="601" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A601" s="2"/>
       <c r="B601" s="2" t="b">
         <v>0</v>
@@ -39956,7 +39958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="602" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="602" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A602" s="2"/>
       <c r="B602" s="2" t="b">
         <v>0</v>
@@ -40011,7 +40013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="603" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="603" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A603" s="2"/>
       <c r="B603" s="2" t="b">
         <v>0</v>
@@ -40066,7 +40068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="604" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="604" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A604" s="2"/>
       <c r="B604" s="2" t="b">
         <v>0</v>
@@ -40121,7 +40123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="605" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="605" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A605" s="2"/>
       <c r="B605" s="2" t="b">
         <v>0</v>
@@ -40176,7 +40178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="606" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="606" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A606" s="2"/>
       <c r="B606" s="2" t="b">
         <v>0</v>
@@ -40231,7 +40233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="607" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A607" s="2"/>
       <c r="B607" s="2" t="b">
         <v>0</v>
@@ -40286,7 +40288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="608" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="608" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A608" s="2"/>
       <c r="B608" s="2" t="b">
         <v>0</v>
@@ -40341,7 +40343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="609" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="609" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A609" s="2"/>
       <c r="B609" s="2" t="b">
         <v>0</v>
@@ -40396,7 +40398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="610" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A610" s="2"/>
       <c r="B610" s="2" t="b">
         <v>0</v>
@@ -40451,7 +40453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="611" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="611" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A611" s="2"/>
       <c r="B611" s="2" t="b">
         <v>0</v>
@@ -40506,7 +40508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="612" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="612" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A612" s="2"/>
       <c r="B612" s="2" t="b">
         <v>0</v>
@@ -40559,7 +40561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="613" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="613" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A613" s="2"/>
       <c r="B613" s="2" t="b">
         <v>0</v>
@@ -40612,7 +40614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="614" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A614" s="2"/>
       <c r="B614" s="2" t="b">
         <v>0</v>
@@ -40663,7 +40665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="615" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="615" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A615" s="2">
         <v>67</v>
       </c>
@@ -40726,7 +40728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="616" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="616" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A616" s="2">
         <v>67</v>
       </c>
@@ -40789,7 +40791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="617" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="617" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A617" s="2">
         <v>67</v>
       </c>
@@ -40852,7 +40854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="618" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A618" s="2">
         <v>67</v>
       </c>
@@ -40915,7 +40917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="619" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="619" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A619" s="2">
         <v>67</v>
       </c>
@@ -40978,7 +40980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="620" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A620" s="2"/>
       <c r="B620" s="2" t="b">
         <v>0</v>
@@ -41035,7 +41037,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="621" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A621" s="2"/>
       <c r="B621" s="2" t="b">
         <v>0</v>
@@ -41092,7 +41094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="622" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="622" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A622" s="2"/>
       <c r="B622" s="2" t="b">
         <v>0</v>
@@ -41149,7 +41151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="623" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="623" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A623" s="2"/>
       <c r="B623" s="2" t="b">
         <v>0</v>
@@ -41206,7 +41208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="624" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="624" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A624" s="2"/>
       <c r="B624" s="2" t="b">
         <v>0</v>
@@ -41263,7 +41265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="625" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A625" s="2"/>
       <c r="B625" s="2" t="b">
         <v>0</v>
@@ -41320,7 +41322,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="626" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="626" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A626" s="2"/>
       <c r="B626" s="2" t="b">
         <v>0</v>
@@ -41377,7 +41379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="627" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A627" s="2"/>
       <c r="B627" s="2" t="b">
         <v>0</v>
@@ -41434,7 +41436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="628" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A628" s="2"/>
       <c r="B628" s="2" t="b">
         <v>0</v>
@@ -41491,7 +41493,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="629" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A629" s="2"/>
       <c r="B629" s="2" t="b">
         <v>0</v>
@@ -41548,7 +41550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="630" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A630" s="2"/>
       <c r="B630" s="2" t="b">
         <v>0</v>
@@ -41605,7 +41607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="631" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="631" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A631" s="2"/>
       <c r="B631" s="2" t="b">
         <v>0</v>
@@ -41662,7 +41664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="632" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A632" s="2"/>
       <c r="B632" s="2" t="b">
         <v>0</v>
@@ -41719,7 +41721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="633" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="633" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A633" s="2"/>
       <c r="B633" s="2" t="b">
         <v>0</v>
@@ -41776,7 +41778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="634" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="634" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A634" s="2">
         <v>77</v>
       </c>
@@ -41835,7 +41837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="635" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A635" s="2">
         <v>77</v>
       </c>
@@ -41894,7 +41896,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="636" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="636" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A636" s="2">
         <v>77</v>
       </c>
@@ -41953,7 +41955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="637" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="637" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A637" s="2">
         <v>77</v>
       </c>
@@ -42012,7 +42014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="638" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A638" s="2">
         <v>77</v>
       </c>
@@ -42071,7 +42073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="639" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A639" s="2"/>
       <c r="B639" s="2" t="b">
         <v>0</v>
@@ -42120,7 +42122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="640" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="640" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A640" s="2"/>
       <c r="B640" s="2" t="b">
         <v>0</v>
@@ -42169,7 +42171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="641" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="641" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A641" s="2"/>
       <c r="B641" s="2" t="b">
         <v>0</v>
@@ -42226,7 +42228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="642" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A642" s="2"/>
       <c r="B642" s="2" t="b">
         <v>0</v>
@@ -42283,7 +42285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="643" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="643" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A643" s="2">
         <v>65</v>
       </c>
@@ -42342,7 +42344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="644" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="644" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A644" s="2">
         <v>65</v>
       </c>
@@ -42401,7 +42403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="645" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A645" s="2">
         <v>65</v>
       </c>
@@ -42460,7 +42462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="646" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="646" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A646" s="2">
         <v>65</v>
       </c>
@@ -42519,7 +42521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="647" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A647" s="2">
         <v>65</v>
       </c>
@@ -42578,7 +42580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="648" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="648" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A648" s="2">
         <v>65</v>
       </c>
@@ -42637,7 +42639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="649" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="649" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A649" s="2"/>
       <c r="B649" s="2" t="b">
         <v>0</v>
@@ -42692,7 +42694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="650" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="650" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A650" s="2"/>
       <c r="B650" s="2" t="b">
         <v>0</v>
@@ -42747,7 +42749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="651" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A651" s="2">
         <v>68</v>
       </c>
@@ -42804,7 +42806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="652" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="652" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A652" s="2">
         <v>68</v>
       </c>
@@ -42861,7 +42863,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="653" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="653" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A653" s="2">
         <v>69</v>
       </c>
@@ -42918,7 +42920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="654" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A654" s="2">
         <v>69</v>
       </c>
@@ -42975,7 +42977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="655" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A655" s="2">
         <v>69</v>
       </c>
@@ -43032,7 +43034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="656" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="656" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A656" s="2">
         <v>69</v>
       </c>
@@ -43089,7 +43091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="657" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A657" s="2">
         <v>69</v>
       </c>
@@ -43146,7 +43148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="658" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A658" s="2">
         <v>69</v>
       </c>
@@ -43203,7 +43205,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="659" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A659" s="2">
         <v>69</v>
       </c>
@@ -43260,7 +43262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="660" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A660" s="2">
         <v>70</v>
       </c>
@@ -43321,7 +43323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="661" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="661" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A661" s="2">
         <v>70</v>
       </c>
@@ -43382,7 +43384,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="662" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="662" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A662" s="2">
         <v>70</v>
       </c>
@@ -43443,7 +43445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="663" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="663" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A663" s="2">
         <v>70</v>
       </c>
@@ -43504,7 +43506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="664" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="664" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A664" s="2">
         <v>70</v>
       </c>
@@ -43565,7 +43567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="665" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="665" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A665" s="2">
         <v>66</v>
       </c>
@@ -43626,7 +43628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="666" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="666" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A666" s="2">
         <v>66</v>
       </c>
@@ -43687,7 +43689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="667" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="667" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A667" s="2">
         <v>66</v>
       </c>
@@ -43748,7 +43750,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="668" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="668" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A668" s="2">
         <v>66</v>
       </c>
@@ -43809,7 +43811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="669" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="669" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A669" s="2">
         <v>66</v>
       </c>
@@ -43870,7 +43872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="670" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="670" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A670" s="2">
         <v>71</v>
       </c>
@@ -43931,7 +43933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="671" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="671" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A671" s="2">
         <v>71</v>
       </c>
@@ -43992,7 +43994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="672" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="672" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A672" s="2">
         <v>71</v>
       </c>
@@ -44053,7 +44055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="673" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="673" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A673" s="2">
         <v>71</v>
       </c>
@@ -44114,7 +44116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="674" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="674" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A674" s="2">
         <v>71</v>
       </c>
@@ -44175,7 +44177,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="675" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="675" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A675" s="2">
         <v>72</v>
       </c>
@@ -44236,7 +44238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="676" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="676" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A676" s="2">
         <v>72</v>
       </c>
@@ -44297,7 +44299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="677" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="677" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A677" s="2">
         <v>72</v>
       </c>
@@ -44358,7 +44360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="678" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="678" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A678" s="2">
         <v>72</v>
       </c>
@@ -44419,7 +44421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="679" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="679" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A679" s="2">
         <v>72</v>
       </c>
@@ -44480,7 +44482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="680" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="680" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A680" s="2">
         <v>73</v>
       </c>
@@ -44541,7 +44543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="681" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="681" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A681" s="2">
         <v>73</v>
       </c>
@@ -44602,7 +44604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="682" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="682" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A682" s="2">
         <v>73</v>
       </c>
@@ -44663,7 +44665,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="683" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="683" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A683" s="2">
         <v>73</v>
       </c>
@@ -44724,7 +44726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="684" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="684" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A684" s="2">
         <v>73</v>
       </c>
@@ -44785,7 +44787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="685" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="685" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A685" s="2"/>
       <c r="B685" s="2" t="b">
         <v>0</v>
@@ -44844,7 +44846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="686" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="686" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A686" s="2"/>
       <c r="B686" s="2" t="b">
         <v>0</v>
@@ -44903,7 +44905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="687" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="687" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A687" s="2"/>
       <c r="B687" s="2" t="b">
         <v>0</v>
@@ -44962,7 +44964,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="688" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="688" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A688" s="2"/>
       <c r="B688" s="2" t="b">
         <v>0</v>
@@ -45021,7 +45023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="689" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A689" s="2"/>
       <c r="B689" s="2" t="b">
         <v>0</v>
@@ -45080,7 +45082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="690" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A690" s="2"/>
       <c r="B690" s="2" t="b">
         <v>0</v>
@@ -45139,7 +45141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="691" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="691" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A691" s="2"/>
       <c r="B691" s="2" t="b">
         <v>0</v>
@@ -45198,7 +45200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="692" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="692" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A692" s="2"/>
       <c r="B692" s="2" t="b">
         <v>0</v>
@@ -45257,7 +45259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="693" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="693" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A693" s="2"/>
       <c r="B693" s="2" t="b">
         <v>0</v>
@@ -45316,7 +45318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="694" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="694" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A694" s="2"/>
       <c r="B694" s="2" t="b">
         <v>0</v>
@@ -45375,7 +45377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="695" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="695" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A695" s="2"/>
       <c r="B695" s="2" t="b">
         <v>0</v>
@@ -45434,7 +45436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="696" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="696" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A696" s="2"/>
       <c r="B696" s="2" t="b">
         <v>0</v>
@@ -45493,7 +45495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="697" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="697" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A697" s="2"/>
       <c r="B697" s="2" t="b">
         <v>0</v>
@@ -45552,7 +45554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="698" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="698" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A698" s="2"/>
       <c r="B698" s="2" t="b">
         <v>0</v>
@@ -45611,7 +45613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="699" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="699" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A699" s="2"/>
       <c r="B699" s="2" t="b">
         <v>0</v>
@@ -45670,7 +45672,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="700" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="700" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A700" s="2"/>
       <c r="B700" s="2" t="b">
         <v>0</v>
@@ -45729,7 +45731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="701" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="701" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A701" s="2"/>
       <c r="B701" s="2" t="b">
         <v>0</v>
@@ -45788,7 +45790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="702" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="702" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A702" s="2"/>
       <c r="B702" s="2" t="b">
         <v>0</v>
@@ -45847,7 +45849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="703" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="703" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A703" s="2"/>
       <c r="B703" s="2" t="b">
         <v>0</v>
@@ -45906,7 +45908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="704" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="704" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A704" s="2"/>
       <c r="B704" s="2" t="b">
         <v>0</v>
@@ -45965,7 +45967,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="705" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="705" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A705" s="2"/>
       <c r="B705" s="2" t="b">
         <v>0</v>
@@ -46024,7 +46026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="706" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="706" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A706" s="2"/>
       <c r="B706" s="2" t="b">
         <v>0</v>
@@ -46083,7 +46085,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="707" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="707" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A707" s="2"/>
       <c r="B707" s="2" t="b">
         <v>0</v>
@@ -46142,7 +46144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="708" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="708" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A708" s="2"/>
       <c r="B708" s="2" t="b">
         <v>0</v>
@@ -46201,7 +46203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="709" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="709" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A709" s="2"/>
       <c r="B709" s="2" t="b">
         <v>0</v>
@@ -46260,7 +46262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="710" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="710" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A710" s="2"/>
       <c r="B710" s="2" t="b">
         <v>0</v>
@@ -46319,7 +46321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="711" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="711" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A711" s="2"/>
       <c r="B711" s="2" t="b">
         <v>0</v>
@@ -46378,7 +46380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="712" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="712" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A712" s="2"/>
       <c r="B712" s="2" t="b">
         <v>0</v>
@@ -46437,7 +46439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="713" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="713" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A713" s="2"/>
       <c r="B713" s="2" t="b">
         <v>0</v>
@@ -46496,7 +46498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="714" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="714" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A714" s="2"/>
       <c r="B714" s="2" t="b">
         <v>0</v>
@@ -46555,7 +46557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="715" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="715" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A715" s="2"/>
       <c r="B715" s="2" t="b">
         <v>0</v>
@@ -46614,7 +46616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="716" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="716" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A716" s="2"/>
       <c r="B716" s="2" t="b">
         <v>0</v>
@@ -46673,7 +46675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="717" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="717" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A717" s="2"/>
       <c r="B717" s="2" t="b">
         <v>0</v>
@@ -46732,7 +46734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="718" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="718" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A718" s="2"/>
       <c r="B718" s="2" t="b">
         <v>0</v>
@@ -46791,7 +46793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="719" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="719" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A719" s="2"/>
       <c r="B719" s="2" t="b">
         <v>0</v>
@@ -46850,7 +46852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="720" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="720" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A720" s="2"/>
       <c r="B720" s="2" t="b">
         <v>0</v>
@@ -46905,7 +46907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="721" spans="1:21" ht="20" x14ac:dyDescent="0.55000000000000004">
+    <row r="721" spans="1:21" ht="20.25" x14ac:dyDescent="0.4">
       <c r="A721" s="2"/>
       <c r="B721" s="2" t="b">
         <v>0</v>
@@ -46965,7 +46967,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T642">
     <sortCondition ref="A2:A642"/>
   </sortState>
-  <conditionalFormatting sqref="A1:T1 A2:F305 K2:K721 C306:C721 A493:B721 L651:L684 I653:J653 M654:N684 G660:J721 D661:F721 L685:T721 T1:U721 O653:T684">
+  <conditionalFormatting sqref="A1:T1 T1:U721 A2:F305 K2:K721 C306:C721 A493:B721 L651:L684 I653:J653 O653:T684 M654:N684 G660:J721 D661:F721 L685:T721">
     <cfRule type="expression" dxfId="12" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -47015,12 +47017,12 @@
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 L306:P626 S306:T642 D653:H660 G659:I659 Q306:R565">
+  <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 D653:H660 G659:I659">
     <cfRule type="expression" dxfId="2" priority="27">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:T2 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 Q3:T255">
+  <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652">
     <cfRule type="expression" dxfId="1" priority="44">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
